--- a/GrowthProjection.xlsx
+++ b/GrowthProjection.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Statistics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Projection" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Settings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Data" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Comparison" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Projection" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Settings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Data" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Methodology" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -210,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -272,6 +273,25 @@
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -287,11 +307,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -301,7 +317,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -654,6 +669,83 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Balance at end age — same contributions</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F3864"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Comparison'!$A$19:$A$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Comparison'!$D$19:$D$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -691,6 +783,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2255,6 +2374,699 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>COMPARISON — COMMON PORTFOLIOS VS THE GLIDE PATH</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Identical window (Jun 2007–Aug 2026), dividends included. Benchmark stats are data (blue); tier rows link to Statistics (green).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1 · Historical risk &amp; return</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Sortino</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Max DD</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 (SPY)</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D6" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>-0.5518999999999999</v>
+      </c>
+      <c r="F6" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>-0.368</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>-0.1818</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Nasdaq 100 (QQQ)</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>-0.534</v>
+      </c>
+      <c r="F7" s="32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G7" s="31" t="n">
+        <v>-0.4173</v>
+      </c>
+      <c r="H7" s="31" t="n">
+        <v>-0.3258</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Dow Jones (DIA)</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D8" s="32" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>-0.5187</v>
+      </c>
+      <c r="F8" s="32" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G8" s="31" t="n">
+        <v>-0.3214</v>
+      </c>
+      <c r="H8" s="31" t="n">
+        <v>-0.0702</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>60/40 (SPY/AGG)</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="n">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <v>-0.347</v>
+      </c>
+      <c r="F9" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G9" s="31" t="n">
+        <v>-0.1997</v>
+      </c>
+      <c r="H9" s="31" t="n">
+        <v>-0.1562</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>All bonds (AGG)</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D10" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <v>-0.1843</v>
+      </c>
+      <c r="F10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="31" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="H10" s="31" t="n">
+        <v>-0.1302</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Gold (GLD)</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="C11" s="32" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>-0.4556</v>
+      </c>
+      <c r="F11" s="32" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G11" s="31" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="H11" s="31" t="n">
+        <v>-0.0077</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Rotation CONS</t>
+        </is>
+      </c>
+      <c r="B12" s="33">
+        <f>Statistics!B6</f>
+        <v/>
+      </c>
+      <c r="C12" s="34">
+        <f>Statistics!C6</f>
+        <v/>
+      </c>
+      <c r="D12" s="34">
+        <f>Statistics!D6</f>
+        <v/>
+      </c>
+      <c r="E12" s="33">
+        <f>Statistics!E6</f>
+        <v/>
+      </c>
+      <c r="F12" s="34">
+        <f>Statistics!F6</f>
+        <v/>
+      </c>
+      <c r="G12" s="33">
+        <f>Statistics!G6</f>
+        <v/>
+      </c>
+      <c r="H12" s="33">
+        <f>Statistics!I6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Rotation MOD</t>
+        </is>
+      </c>
+      <c r="B13" s="33">
+        <f>Statistics!B7</f>
+        <v/>
+      </c>
+      <c r="C13" s="34">
+        <f>Statistics!C7</f>
+        <v/>
+      </c>
+      <c r="D13" s="34">
+        <f>Statistics!D7</f>
+        <v/>
+      </c>
+      <c r="E13" s="33">
+        <f>Statistics!E7</f>
+        <v/>
+      </c>
+      <c r="F13" s="34">
+        <f>Statistics!F7</f>
+        <v/>
+      </c>
+      <c r="G13" s="33">
+        <f>Statistics!G7</f>
+        <v/>
+      </c>
+      <c r="H13" s="33">
+        <f>Statistics!I7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Rotation AGG</t>
+        </is>
+      </c>
+      <c r="B14" s="33">
+        <f>Statistics!B8</f>
+        <v/>
+      </c>
+      <c r="C14" s="34">
+        <f>Statistics!C8</f>
+        <v/>
+      </c>
+      <c r="D14" s="34">
+        <f>Statistics!D8</f>
+        <v/>
+      </c>
+      <c r="E14" s="33">
+        <f>Statistics!E8</f>
+        <v/>
+      </c>
+      <c r="F14" s="34">
+        <f>Statistics!F8</f>
+        <v/>
+      </c>
+      <c r="G14" s="33">
+        <f>Statistics!G8</f>
+        <v/>
+      </c>
+      <c r="H14" s="33">
+        <f>Statistics!I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Rotation VAGG</t>
+        </is>
+      </c>
+      <c r="B15" s="33">
+        <f>Statistics!B9</f>
+        <v/>
+      </c>
+      <c r="C15" s="34">
+        <f>Statistics!C9</f>
+        <v/>
+      </c>
+      <c r="D15" s="34">
+        <f>Statistics!D9</f>
+        <v/>
+      </c>
+      <c r="E15" s="33">
+        <f>Statistics!E9</f>
+        <v/>
+      </c>
+      <c r="F15" s="34">
+        <f>Statistics!F9</f>
+        <v/>
+      </c>
+      <c r="G15" s="33">
+        <f>Statistics!G9</f>
+        <v/>
+      </c>
+      <c r="H15" s="33">
+        <f>Statistics!I9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2 · Forward-looking — same contributions, same horizon, to end age</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>Expected return (edit)</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>Balance at end age</t>
+        </is>
+      </c>
+      <c r="E18" s="35" t="inlineStr">
+        <is>
+          <t>vs glide path</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 (SPY)</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="C19" s="36">
+        <f>(1+B19)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="D19" s="29">
+        <f>IF(ABS($C$19-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$19)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$19)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$19)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$19)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$19-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="E19" s="23">
+        <f>D19/$D$29-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Nasdaq 100 (QQQ)</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="C20" s="36">
+        <f>(1+B20)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="D20" s="29">
+        <f>IF(ABS($C$20-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$20)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$20)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$20)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$20)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$20-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="E20" s="23">
+        <f>D20/$D$29-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Dow Jones (DIA)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="C21" s="36">
+        <f>(1+B21)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="D21" s="29">
+        <f>IF(ABS($C$21-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$21)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$21)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$21)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$21)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$21-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="E21" s="23">
+        <f>D21/$D$29-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>60/40 (SPY/AGG)</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="C22" s="36">
+        <f>(1+B22)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="D22" s="29">
+        <f>IF(ABS($C$22-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$22)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$22)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$22)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$22)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$22-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="E22" s="23">
+        <f>D22/$D$29-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>All bonds (AGG)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="C23" s="36">
+        <f>(1+B23)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="D23" s="29">
+        <f>IF(ABS($C$23-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$23)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$23)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$23)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$23)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$23-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="E23" s="23">
+        <f>D23/$D$29-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Gold (GLD)</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="C24" s="36">
+        <f>(1+B24)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="D24" s="29">
+        <f>IF(ABS($C$24-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$24)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$24)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$24)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$24)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$24-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="E24" s="23">
+        <f>D24/$D$29-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Rotation CONS (haircut)</t>
+        </is>
+      </c>
+      <c r="B25" s="24">
+        <f>Settings!$C$13</f>
+        <v/>
+      </c>
+      <c r="C25" s="36">
+        <f>(1+B25)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="D25" s="37">
+        <f>IF(ABS($C$25-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$25)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$25)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$25)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$25)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$25-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="E25" s="23">
+        <f>D25/$D$29-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Rotation MOD (haircut)</t>
+        </is>
+      </c>
+      <c r="B26" s="24">
+        <f>Settings!$C$14</f>
+        <v/>
+      </c>
+      <c r="C26" s="36">
+        <f>(1+B26)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="D26" s="37">
+        <f>IF(ABS($C$26-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$26)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$26)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$26)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$26)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$26-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="E26" s="23">
+        <f>D26/$D$29-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Rotation AGG (haircut)</t>
+        </is>
+      </c>
+      <c r="B27" s="24">
+        <f>Settings!$C$15</f>
+        <v/>
+      </c>
+      <c r="C27" s="36">
+        <f>(1+B27)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="D27" s="37">
+        <f>IF(ABS($C$27-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$27)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$27)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$27)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$27)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$27-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="E27" s="23">
+        <f>D27/$D$29-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Rotation VAGG (haircut)</t>
+        </is>
+      </c>
+      <c r="B28" s="24">
+        <f>Settings!$C$16</f>
+        <v/>
+      </c>
+      <c r="C28" s="36">
+        <f>(1+B28)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="D28" s="37">
+        <f>IF(ABS($C$28-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$28)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$28)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$28)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$28)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$28-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="E28" s="23">
+        <f>D28/$D$29-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="38" t="inlineStr">
+        <is>
+          <t>YOUR GLIDE PATH (exact)</t>
+        </is>
+      </c>
+      <c r="B29" s="24">
+        <f>Statistics!$B$32</f>
+        <v/>
+      </c>
+      <c r="D29" s="39">
+        <f>INDEX(Projection!$E:$E,(Settings!$B$9*12)+4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>Benchmark expected returns default to raw historical CAGR (no haircut) — arguably generous to them; edit the yellow cells to stress. Rotation rows use the Dashboard haircut. Glide row is the exact month-by-month projection.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="001F3864"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2272,7 +3084,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>Age-Aware Wealth Projection</t>
         </is>
@@ -2286,47 +3098,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>Contribution</t>
         </is>
       </c>
-      <c r="E4" s="32" t="inlineStr">
+      <c r="E4" s="41" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="F4" s="32" t="inlineStr">
+      <c r="F4" s="41" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G4" s="32" t="inlineStr">
+      <c r="G4" s="41" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="n">
+      <c r="A5" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="43">
         <f>Dashboard!$C$5+(1-1)/12</f>
         <v/>
       </c>
@@ -2352,10 +3164,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="n">
+      <c r="A6" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="43">
         <f>Dashboard!$C$5+(2-1)/12</f>
         <v/>
       </c>
@@ -2381,10 +3193,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="n">
+      <c r="A7" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="43">
         <f>Dashboard!$C$5+(3-1)/12</f>
         <v/>
       </c>
@@ -2410,10 +3222,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="n">
+      <c r="A8" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="43">
         <f>Dashboard!$C$5+(4-1)/12</f>
         <v/>
       </c>
@@ -2439,10 +3251,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="n">
+      <c r="A9" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="43">
         <f>Dashboard!$C$5+(5-1)/12</f>
         <v/>
       </c>
@@ -2468,10 +3280,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="n">
+      <c r="A10" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="43">
         <f>Dashboard!$C$5+(6-1)/12</f>
         <v/>
       </c>
@@ -2497,10 +3309,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="n">
+      <c r="A11" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="43">
         <f>Dashboard!$C$5+(7-1)/12</f>
         <v/>
       </c>
@@ -2526,10 +3338,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="n">
+      <c r="A12" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="34">
+      <c r="B12" s="43">
         <f>Dashboard!$C$5+(8-1)/12</f>
         <v/>
       </c>
@@ -2555,10 +3367,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="n">
+      <c r="A13" s="42" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="43">
         <f>Dashboard!$C$5+(9-1)/12</f>
         <v/>
       </c>
@@ -2584,10 +3396,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="n">
+      <c r="A14" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="43">
         <f>Dashboard!$C$5+(10-1)/12</f>
         <v/>
       </c>
@@ -2613,10 +3425,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="n">
+      <c r="A15" s="42" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="43">
         <f>Dashboard!$C$5+(11-1)/12</f>
         <v/>
       </c>
@@ -2642,10 +3454,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="n">
+      <c r="A16" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="43">
         <f>Dashboard!$C$5+(12-1)/12</f>
         <v/>
       </c>
@@ -2671,10 +3483,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="n">
+      <c r="A17" s="42" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="43">
         <f>Dashboard!$C$5+(13-1)/12</f>
         <v/>
       </c>
@@ -2700,10 +3512,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="n">
+      <c r="A18" s="42" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="43">
         <f>Dashboard!$C$5+(14-1)/12</f>
         <v/>
       </c>
@@ -2729,10 +3541,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="n">
+      <c r="A19" s="42" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="43">
         <f>Dashboard!$C$5+(15-1)/12</f>
         <v/>
       </c>
@@ -2758,10 +3570,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="n">
+      <c r="A20" s="42" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="34">
+      <c r="B20" s="43">
         <f>Dashboard!$C$5+(16-1)/12</f>
         <v/>
       </c>
@@ -2787,10 +3599,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="n">
+      <c r="A21" s="42" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="43">
         <f>Dashboard!$C$5+(17-1)/12</f>
         <v/>
       </c>
@@ -2816,10 +3628,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="n">
+      <c r="A22" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="34">
+      <c r="B22" s="43">
         <f>Dashboard!$C$5+(18-1)/12</f>
         <v/>
       </c>
@@ -2845,10 +3657,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="33" t="n">
+      <c r="A23" s="42" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="43">
         <f>Dashboard!$C$5+(19-1)/12</f>
         <v/>
       </c>
@@ -2874,10 +3686,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="33" t="n">
+      <c r="A24" s="42" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="34">
+      <c r="B24" s="43">
         <f>Dashboard!$C$5+(20-1)/12</f>
         <v/>
       </c>
@@ -2903,10 +3715,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="33" t="n">
+      <c r="A25" s="42" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="34">
+      <c r="B25" s="43">
         <f>Dashboard!$C$5+(21-1)/12</f>
         <v/>
       </c>
@@ -2932,10 +3744,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="33" t="n">
+      <c r="A26" s="42" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="34">
+      <c r="B26" s="43">
         <f>Dashboard!$C$5+(22-1)/12</f>
         <v/>
       </c>
@@ -2961,10 +3773,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="33" t="n">
+      <c r="A27" s="42" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="34">
+      <c r="B27" s="43">
         <f>Dashboard!$C$5+(23-1)/12</f>
         <v/>
       </c>
@@ -2990,10 +3802,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="33" t="n">
+      <c r="A28" s="42" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="34">
+      <c r="B28" s="43">
         <f>Dashboard!$C$5+(24-1)/12</f>
         <v/>
       </c>
@@ -3019,10 +3831,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="33" t="n">
+      <c r="A29" s="42" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="43">
         <f>Dashboard!$C$5+(25-1)/12</f>
         <v/>
       </c>
@@ -3048,10 +3860,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="33" t="n">
+      <c r="A30" s="42" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="43">
         <f>Dashboard!$C$5+(26-1)/12</f>
         <v/>
       </c>
@@ -3077,10 +3889,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="33" t="n">
+      <c r="A31" s="42" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="43">
         <f>Dashboard!$C$5+(27-1)/12</f>
         <v/>
       </c>
@@ -3106,10 +3918,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="33" t="n">
+      <c r="A32" s="42" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="43">
         <f>Dashboard!$C$5+(28-1)/12</f>
         <v/>
       </c>
@@ -3135,10 +3947,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="33" t="n">
+      <c r="A33" s="42" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="43">
         <f>Dashboard!$C$5+(29-1)/12</f>
         <v/>
       </c>
@@ -3164,10 +3976,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="33" t="n">
+      <c r="A34" s="42" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="43">
         <f>Dashboard!$C$5+(30-1)/12</f>
         <v/>
       </c>
@@ -3193,10 +4005,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="33" t="n">
+      <c r="A35" s="42" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="34">
+      <c r="B35" s="43">
         <f>Dashboard!$C$5+(31-1)/12</f>
         <v/>
       </c>
@@ -3222,10 +4034,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="33" t="n">
+      <c r="A36" s="42" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="34">
+      <c r="B36" s="43">
         <f>Dashboard!$C$5+(32-1)/12</f>
         <v/>
       </c>
@@ -3251,10 +4063,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="33" t="n">
+      <c r="A37" s="42" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="34">
+      <c r="B37" s="43">
         <f>Dashboard!$C$5+(33-1)/12</f>
         <v/>
       </c>
@@ -3280,10 +4092,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="33" t="n">
+      <c r="A38" s="42" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="34">
+      <c r="B38" s="43">
         <f>Dashboard!$C$5+(34-1)/12</f>
         <v/>
       </c>
@@ -3309,10 +4121,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="33" t="n">
+      <c r="A39" s="42" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="34">
+      <c r="B39" s="43">
         <f>Dashboard!$C$5+(35-1)/12</f>
         <v/>
       </c>
@@ -3338,10 +4150,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="33" t="n">
+      <c r="A40" s="42" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="34">
+      <c r="B40" s="43">
         <f>Dashboard!$C$5+(36-1)/12</f>
         <v/>
       </c>
@@ -3367,10 +4179,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="33" t="n">
+      <c r="A41" s="42" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="34">
+      <c r="B41" s="43">
         <f>Dashboard!$C$5+(37-1)/12</f>
         <v/>
       </c>
@@ -3396,10 +4208,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="33" t="n">
+      <c r="A42" s="42" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="34">
+      <c r="B42" s="43">
         <f>Dashboard!$C$5+(38-1)/12</f>
         <v/>
       </c>
@@ -3425,10 +4237,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="33" t="n">
+      <c r="A43" s="42" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="34">
+      <c r="B43" s="43">
         <f>Dashboard!$C$5+(39-1)/12</f>
         <v/>
       </c>
@@ -3454,10 +4266,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="33" t="n">
+      <c r="A44" s="42" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="34">
+      <c r="B44" s="43">
         <f>Dashboard!$C$5+(40-1)/12</f>
         <v/>
       </c>
@@ -3483,10 +4295,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="33" t="n">
+      <c r="A45" s="42" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="34">
+      <c r="B45" s="43">
         <f>Dashboard!$C$5+(41-1)/12</f>
         <v/>
       </c>
@@ -3512,10 +4324,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="33" t="n">
+      <c r="A46" s="42" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="34">
+      <c r="B46" s="43">
         <f>Dashboard!$C$5+(42-1)/12</f>
         <v/>
       </c>
@@ -3541,10 +4353,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="33" t="n">
+      <c r="A47" s="42" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="34">
+      <c r="B47" s="43">
         <f>Dashboard!$C$5+(43-1)/12</f>
         <v/>
       </c>
@@ -3570,10 +4382,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="33" t="n">
+      <c r="A48" s="42" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="34">
+      <c r="B48" s="43">
         <f>Dashboard!$C$5+(44-1)/12</f>
         <v/>
       </c>
@@ -3599,10 +4411,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="33" t="n">
+      <c r="A49" s="42" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="34">
+      <c r="B49" s="43">
         <f>Dashboard!$C$5+(45-1)/12</f>
         <v/>
       </c>
@@ -3628,10 +4440,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="33" t="n">
+      <c r="A50" s="42" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="34">
+      <c r="B50" s="43">
         <f>Dashboard!$C$5+(46-1)/12</f>
         <v/>
       </c>
@@ -3657,10 +4469,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="33" t="n">
+      <c r="A51" s="42" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="34">
+      <c r="B51" s="43">
         <f>Dashboard!$C$5+(47-1)/12</f>
         <v/>
       </c>
@@ -3686,10 +4498,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="33" t="n">
+      <c r="A52" s="42" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="34">
+      <c r="B52" s="43">
         <f>Dashboard!$C$5+(48-1)/12</f>
         <v/>
       </c>
@@ -3715,10 +4527,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="33" t="n">
+      <c r="A53" s="42" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="34">
+      <c r="B53" s="43">
         <f>Dashboard!$C$5+(49-1)/12</f>
         <v/>
       </c>
@@ -3744,10 +4556,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="33" t="n">
+      <c r="A54" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="34">
+      <c r="B54" s="43">
         <f>Dashboard!$C$5+(50-1)/12</f>
         <v/>
       </c>
@@ -3773,10 +4585,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="33" t="n">
+      <c r="A55" s="42" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="34">
+      <c r="B55" s="43">
         <f>Dashboard!$C$5+(51-1)/12</f>
         <v/>
       </c>
@@ -3802,10 +4614,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="33" t="n">
+      <c r="A56" s="42" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="34">
+      <c r="B56" s="43">
         <f>Dashboard!$C$5+(52-1)/12</f>
         <v/>
       </c>
@@ -3831,10 +4643,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="33" t="n">
+      <c r="A57" s="42" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="34">
+      <c r="B57" s="43">
         <f>Dashboard!$C$5+(53-1)/12</f>
         <v/>
       </c>
@@ -3860,10 +4672,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="33" t="n">
+      <c r="A58" s="42" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="34">
+      <c r="B58" s="43">
         <f>Dashboard!$C$5+(54-1)/12</f>
         <v/>
       </c>
@@ -3889,10 +4701,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="33" t="n">
+      <c r="A59" s="42" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="34">
+      <c r="B59" s="43">
         <f>Dashboard!$C$5+(55-1)/12</f>
         <v/>
       </c>
@@ -3918,10 +4730,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="33" t="n">
+      <c r="A60" s="42" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="34">
+      <c r="B60" s="43">
         <f>Dashboard!$C$5+(56-1)/12</f>
         <v/>
       </c>
@@ -3947,10 +4759,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="33" t="n">
+      <c r="A61" s="42" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="34">
+      <c r="B61" s="43">
         <f>Dashboard!$C$5+(57-1)/12</f>
         <v/>
       </c>
@@ -3976,10 +4788,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="33" t="n">
+      <c r="A62" s="42" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="34">
+      <c r="B62" s="43">
         <f>Dashboard!$C$5+(58-1)/12</f>
         <v/>
       </c>
@@ -4005,10 +4817,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="33" t="n">
+      <c r="A63" s="42" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="34">
+      <c r="B63" s="43">
         <f>Dashboard!$C$5+(59-1)/12</f>
         <v/>
       </c>
@@ -4034,10 +4846,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="33" t="n">
+      <c r="A64" s="42" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="34">
+      <c r="B64" s="43">
         <f>Dashboard!$C$5+(60-1)/12</f>
         <v/>
       </c>
@@ -4063,10 +4875,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="33" t="n">
+      <c r="A65" s="42" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="34">
+      <c r="B65" s="43">
         <f>Dashboard!$C$5+(61-1)/12</f>
         <v/>
       </c>
@@ -4092,10 +4904,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="33" t="n">
+      <c r="A66" s="42" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="34">
+      <c r="B66" s="43">
         <f>Dashboard!$C$5+(62-1)/12</f>
         <v/>
       </c>
@@ -4121,10 +4933,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="33" t="n">
+      <c r="A67" s="42" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="34">
+      <c r="B67" s="43">
         <f>Dashboard!$C$5+(63-1)/12</f>
         <v/>
       </c>
@@ -4150,10 +4962,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="33" t="n">
+      <c r="A68" s="42" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="34">
+      <c r="B68" s="43">
         <f>Dashboard!$C$5+(64-1)/12</f>
         <v/>
       </c>
@@ -4179,10 +4991,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="33" t="n">
+      <c r="A69" s="42" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="34">
+      <c r="B69" s="43">
         <f>Dashboard!$C$5+(65-1)/12</f>
         <v/>
       </c>
@@ -4208,10 +5020,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="33" t="n">
+      <c r="A70" s="42" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="34">
+      <c r="B70" s="43">
         <f>Dashboard!$C$5+(66-1)/12</f>
         <v/>
       </c>
@@ -4237,10 +5049,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="33" t="n">
+      <c r="A71" s="42" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="34">
+      <c r="B71" s="43">
         <f>Dashboard!$C$5+(67-1)/12</f>
         <v/>
       </c>
@@ -4266,10 +5078,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="33" t="n">
+      <c r="A72" s="42" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="34">
+      <c r="B72" s="43">
         <f>Dashboard!$C$5+(68-1)/12</f>
         <v/>
       </c>
@@ -4295,10 +5107,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="33" t="n">
+      <c r="A73" s="42" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="34">
+      <c r="B73" s="43">
         <f>Dashboard!$C$5+(69-1)/12</f>
         <v/>
       </c>
@@ -4324,10 +5136,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="33" t="n">
+      <c r="A74" s="42" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="34">
+      <c r="B74" s="43">
         <f>Dashboard!$C$5+(70-1)/12</f>
         <v/>
       </c>
@@ -4353,10 +5165,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="33" t="n">
+      <c r="A75" s="42" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="34">
+      <c r="B75" s="43">
         <f>Dashboard!$C$5+(71-1)/12</f>
         <v/>
       </c>
@@ -4382,10 +5194,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="33" t="n">
+      <c r="A76" s="42" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="34">
+      <c r="B76" s="43">
         <f>Dashboard!$C$5+(72-1)/12</f>
         <v/>
       </c>
@@ -4411,10 +5223,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="33" t="n">
+      <c r="A77" s="42" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="34">
+      <c r="B77" s="43">
         <f>Dashboard!$C$5+(73-1)/12</f>
         <v/>
       </c>
@@ -4440,10 +5252,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="33" t="n">
+      <c r="A78" s="42" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="34">
+      <c r="B78" s="43">
         <f>Dashboard!$C$5+(74-1)/12</f>
         <v/>
       </c>
@@ -4469,10 +5281,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="33" t="n">
+      <c r="A79" s="42" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="34">
+      <c r="B79" s="43">
         <f>Dashboard!$C$5+(75-1)/12</f>
         <v/>
       </c>
@@ -4498,10 +5310,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="33" t="n">
+      <c r="A80" s="42" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="34">
+      <c r="B80" s="43">
         <f>Dashboard!$C$5+(76-1)/12</f>
         <v/>
       </c>
@@ -4527,10 +5339,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="33" t="n">
+      <c r="A81" s="42" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="34">
+      <c r="B81" s="43">
         <f>Dashboard!$C$5+(77-1)/12</f>
         <v/>
       </c>
@@ -4556,10 +5368,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="33" t="n">
+      <c r="A82" s="42" t="n">
         <v>78</v>
       </c>
-      <c r="B82" s="34">
+      <c r="B82" s="43">
         <f>Dashboard!$C$5+(78-1)/12</f>
         <v/>
       </c>
@@ -4585,10 +5397,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="33" t="n">
+      <c r="A83" s="42" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="34">
+      <c r="B83" s="43">
         <f>Dashboard!$C$5+(79-1)/12</f>
         <v/>
       </c>
@@ -4614,10 +5426,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="33" t="n">
+      <c r="A84" s="42" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="34">
+      <c r="B84" s="43">
         <f>Dashboard!$C$5+(80-1)/12</f>
         <v/>
       </c>
@@ -4643,10 +5455,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="33" t="n">
+      <c r="A85" s="42" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="34">
+      <c r="B85" s="43">
         <f>Dashboard!$C$5+(81-1)/12</f>
         <v/>
       </c>
@@ -4672,10 +5484,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="33" t="n">
+      <c r="A86" s="42" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="34">
+      <c r="B86" s="43">
         <f>Dashboard!$C$5+(82-1)/12</f>
         <v/>
       </c>
@@ -4701,10 +5513,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="33" t="n">
+      <c r="A87" s="42" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="34">
+      <c r="B87" s="43">
         <f>Dashboard!$C$5+(83-1)/12</f>
         <v/>
       </c>
@@ -4730,10 +5542,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="33" t="n">
+      <c r="A88" s="42" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="34">
+      <c r="B88" s="43">
         <f>Dashboard!$C$5+(84-1)/12</f>
         <v/>
       </c>
@@ -4759,10 +5571,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="33" t="n">
+      <c r="A89" s="42" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="34">
+      <c r="B89" s="43">
         <f>Dashboard!$C$5+(85-1)/12</f>
         <v/>
       </c>
@@ -4788,10 +5600,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="33" t="n">
+      <c r="A90" s="42" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="34">
+      <c r="B90" s="43">
         <f>Dashboard!$C$5+(86-1)/12</f>
         <v/>
       </c>
@@ -4817,10 +5629,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="33" t="n">
+      <c r="A91" s="42" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="34">
+      <c r="B91" s="43">
         <f>Dashboard!$C$5+(87-1)/12</f>
         <v/>
       </c>
@@ -4846,10 +5658,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="33" t="n">
+      <c r="A92" s="42" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="34">
+      <c r="B92" s="43">
         <f>Dashboard!$C$5+(88-1)/12</f>
         <v/>
       </c>
@@ -4875,10 +5687,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="33" t="n">
+      <c r="A93" s="42" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="34">
+      <c r="B93" s="43">
         <f>Dashboard!$C$5+(89-1)/12</f>
         <v/>
       </c>
@@ -4904,10 +5716,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="33" t="n">
+      <c r="A94" s="42" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="34">
+      <c r="B94" s="43">
         <f>Dashboard!$C$5+(90-1)/12</f>
         <v/>
       </c>
@@ -4933,10 +5745,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="33" t="n">
+      <c r="A95" s="42" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="34">
+      <c r="B95" s="43">
         <f>Dashboard!$C$5+(91-1)/12</f>
         <v/>
       </c>
@@ -4962,10 +5774,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="33" t="n">
+      <c r="A96" s="42" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="34">
+      <c r="B96" s="43">
         <f>Dashboard!$C$5+(92-1)/12</f>
         <v/>
       </c>
@@ -4991,10 +5803,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="33" t="n">
+      <c r="A97" s="42" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="34">
+      <c r="B97" s="43">
         <f>Dashboard!$C$5+(93-1)/12</f>
         <v/>
       </c>
@@ -5020,10 +5832,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="33" t="n">
+      <c r="A98" s="42" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="34">
+      <c r="B98" s="43">
         <f>Dashboard!$C$5+(94-1)/12</f>
         <v/>
       </c>
@@ -5049,10 +5861,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="33" t="n">
+      <c r="A99" s="42" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="34">
+      <c r="B99" s="43">
         <f>Dashboard!$C$5+(95-1)/12</f>
         <v/>
       </c>
@@ -5078,10 +5890,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="33" t="n">
+      <c r="A100" s="42" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="34">
+      <c r="B100" s="43">
         <f>Dashboard!$C$5+(96-1)/12</f>
         <v/>
       </c>
@@ -5107,10 +5919,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="33" t="n">
+      <c r="A101" s="42" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="34">
+      <c r="B101" s="43">
         <f>Dashboard!$C$5+(97-1)/12</f>
         <v/>
       </c>
@@ -5136,10 +5948,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="33" t="n">
+      <c r="A102" s="42" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="34">
+      <c r="B102" s="43">
         <f>Dashboard!$C$5+(98-1)/12</f>
         <v/>
       </c>
@@ -5165,10 +5977,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="33" t="n">
+      <c r="A103" s="42" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="34">
+      <c r="B103" s="43">
         <f>Dashboard!$C$5+(99-1)/12</f>
         <v/>
       </c>
@@ -5194,10 +6006,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="33" t="n">
+      <c r="A104" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="34">
+      <c r="B104" s="43">
         <f>Dashboard!$C$5+(100-1)/12</f>
         <v/>
       </c>
@@ -5223,10 +6035,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="33" t="n">
+      <c r="A105" s="42" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="34">
+      <c r="B105" s="43">
         <f>Dashboard!$C$5+(101-1)/12</f>
         <v/>
       </c>
@@ -5252,10 +6064,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="33" t="n">
+      <c r="A106" s="42" t="n">
         <v>102</v>
       </c>
-      <c r="B106" s="34">
+      <c r="B106" s="43">
         <f>Dashboard!$C$5+(102-1)/12</f>
         <v/>
       </c>
@@ -5281,10 +6093,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="33" t="n">
+      <c r="A107" s="42" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="34">
+      <c r="B107" s="43">
         <f>Dashboard!$C$5+(103-1)/12</f>
         <v/>
       </c>
@@ -5310,10 +6122,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="33" t="n">
+      <c r="A108" s="42" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="34">
+      <c r="B108" s="43">
         <f>Dashboard!$C$5+(104-1)/12</f>
         <v/>
       </c>
@@ -5339,10 +6151,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="33" t="n">
+      <c r="A109" s="42" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="34">
+      <c r="B109" s="43">
         <f>Dashboard!$C$5+(105-1)/12</f>
         <v/>
       </c>
@@ -5368,10 +6180,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="33" t="n">
+      <c r="A110" s="42" t="n">
         <v>106</v>
       </c>
-      <c r="B110" s="34">
+      <c r="B110" s="43">
         <f>Dashboard!$C$5+(106-1)/12</f>
         <v/>
       </c>
@@ -5397,10 +6209,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="33" t="n">
+      <c r="A111" s="42" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="34">
+      <c r="B111" s="43">
         <f>Dashboard!$C$5+(107-1)/12</f>
         <v/>
       </c>
@@ -5426,10 +6238,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="33" t="n">
+      <c r="A112" s="42" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="34">
+      <c r="B112" s="43">
         <f>Dashboard!$C$5+(108-1)/12</f>
         <v/>
       </c>
@@ -5455,10 +6267,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="33" t="n">
+      <c r="A113" s="42" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="34">
+      <c r="B113" s="43">
         <f>Dashboard!$C$5+(109-1)/12</f>
         <v/>
       </c>
@@ -5484,10 +6296,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="33" t="n">
+      <c r="A114" s="42" t="n">
         <v>110</v>
       </c>
-      <c r="B114" s="34">
+      <c r="B114" s="43">
         <f>Dashboard!$C$5+(110-1)/12</f>
         <v/>
       </c>
@@ -5513,10 +6325,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="33" t="n">
+      <c r="A115" s="42" t="n">
         <v>111</v>
       </c>
-      <c r="B115" s="34">
+      <c r="B115" s="43">
         <f>Dashboard!$C$5+(111-1)/12</f>
         <v/>
       </c>
@@ -5542,10 +6354,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="33" t="n">
+      <c r="A116" s="42" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="34">
+      <c r="B116" s="43">
         <f>Dashboard!$C$5+(112-1)/12</f>
         <v/>
       </c>
@@ -5571,10 +6383,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="33" t="n">
+      <c r="A117" s="42" t="n">
         <v>113</v>
       </c>
-      <c r="B117" s="34">
+      <c r="B117" s="43">
         <f>Dashboard!$C$5+(113-1)/12</f>
         <v/>
       </c>
@@ -5600,10 +6412,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="33" t="n">
+      <c r="A118" s="42" t="n">
         <v>114</v>
       </c>
-      <c r="B118" s="34">
+      <c r="B118" s="43">
         <f>Dashboard!$C$5+(114-1)/12</f>
         <v/>
       </c>
@@ -5629,10 +6441,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="33" t="n">
+      <c r="A119" s="42" t="n">
         <v>115</v>
       </c>
-      <c r="B119" s="34">
+      <c r="B119" s="43">
         <f>Dashboard!$C$5+(115-1)/12</f>
         <v/>
       </c>
@@ -5658,10 +6470,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="33" t="n">
+      <c r="A120" s="42" t="n">
         <v>116</v>
       </c>
-      <c r="B120" s="34">
+      <c r="B120" s="43">
         <f>Dashboard!$C$5+(116-1)/12</f>
         <v/>
       </c>
@@ -5687,10 +6499,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="33" t="n">
+      <c r="A121" s="42" t="n">
         <v>117</v>
       </c>
-      <c r="B121" s="34">
+      <c r="B121" s="43">
         <f>Dashboard!$C$5+(117-1)/12</f>
         <v/>
       </c>
@@ -5716,10 +6528,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="33" t="n">
+      <c r="A122" s="42" t="n">
         <v>118</v>
       </c>
-      <c r="B122" s="34">
+      <c r="B122" s="43">
         <f>Dashboard!$C$5+(118-1)/12</f>
         <v/>
       </c>
@@ -5745,10 +6557,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="33" t="n">
+      <c r="A123" s="42" t="n">
         <v>119</v>
       </c>
-      <c r="B123" s="34">
+      <c r="B123" s="43">
         <f>Dashboard!$C$5+(119-1)/12</f>
         <v/>
       </c>
@@ -5774,10 +6586,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="33" t="n">
+      <c r="A124" s="42" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="34">
+      <c r="B124" s="43">
         <f>Dashboard!$C$5+(120-1)/12</f>
         <v/>
       </c>
@@ -5803,10 +6615,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="33" t="n">
+      <c r="A125" s="42" t="n">
         <v>121</v>
       </c>
-      <c r="B125" s="34">
+      <c r="B125" s="43">
         <f>Dashboard!$C$5+(121-1)/12</f>
         <v/>
       </c>
@@ -5832,10 +6644,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="33" t="n">
+      <c r="A126" s="42" t="n">
         <v>122</v>
       </c>
-      <c r="B126" s="34">
+      <c r="B126" s="43">
         <f>Dashboard!$C$5+(122-1)/12</f>
         <v/>
       </c>
@@ -5861,10 +6673,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="33" t="n">
+      <c r="A127" s="42" t="n">
         <v>123</v>
       </c>
-      <c r="B127" s="34">
+      <c r="B127" s="43">
         <f>Dashboard!$C$5+(123-1)/12</f>
         <v/>
       </c>
@@ -5890,10 +6702,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="33" t="n">
+      <c r="A128" s="42" t="n">
         <v>124</v>
       </c>
-      <c r="B128" s="34">
+      <c r="B128" s="43">
         <f>Dashboard!$C$5+(124-1)/12</f>
         <v/>
       </c>
@@ -5919,10 +6731,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="33" t="n">
+      <c r="A129" s="42" t="n">
         <v>125</v>
       </c>
-      <c r="B129" s="34">
+      <c r="B129" s="43">
         <f>Dashboard!$C$5+(125-1)/12</f>
         <v/>
       </c>
@@ -5948,10 +6760,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="33" t="n">
+      <c r="A130" s="42" t="n">
         <v>126</v>
       </c>
-      <c r="B130" s="34">
+      <c r="B130" s="43">
         <f>Dashboard!$C$5+(126-1)/12</f>
         <v/>
       </c>
@@ -5977,10 +6789,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="33" t="n">
+      <c r="A131" s="42" t="n">
         <v>127</v>
       </c>
-      <c r="B131" s="34">
+      <c r="B131" s="43">
         <f>Dashboard!$C$5+(127-1)/12</f>
         <v/>
       </c>
@@ -6006,10 +6818,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="33" t="n">
+      <c r="A132" s="42" t="n">
         <v>128</v>
       </c>
-      <c r="B132" s="34">
+      <c r="B132" s="43">
         <f>Dashboard!$C$5+(128-1)/12</f>
         <v/>
       </c>
@@ -6035,10 +6847,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="33" t="n">
+      <c r="A133" s="42" t="n">
         <v>129</v>
       </c>
-      <c r="B133" s="34">
+      <c r="B133" s="43">
         <f>Dashboard!$C$5+(129-1)/12</f>
         <v/>
       </c>
@@ -6064,10 +6876,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="33" t="n">
+      <c r="A134" s="42" t="n">
         <v>130</v>
       </c>
-      <c r="B134" s="34">
+      <c r="B134" s="43">
         <f>Dashboard!$C$5+(130-1)/12</f>
         <v/>
       </c>
@@ -6093,10 +6905,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="33" t="n">
+      <c r="A135" s="42" t="n">
         <v>131</v>
       </c>
-      <c r="B135" s="34">
+      <c r="B135" s="43">
         <f>Dashboard!$C$5+(131-1)/12</f>
         <v/>
       </c>
@@ -6122,10 +6934,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="33" t="n">
+      <c r="A136" s="42" t="n">
         <v>132</v>
       </c>
-      <c r="B136" s="34">
+      <c r="B136" s="43">
         <f>Dashboard!$C$5+(132-1)/12</f>
         <v/>
       </c>
@@ -6151,10 +6963,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="33" t="n">
+      <c r="A137" s="42" t="n">
         <v>133</v>
       </c>
-      <c r="B137" s="34">
+      <c r="B137" s="43">
         <f>Dashboard!$C$5+(133-1)/12</f>
         <v/>
       </c>
@@ -6180,10 +6992,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="33" t="n">
+      <c r="A138" s="42" t="n">
         <v>134</v>
       </c>
-      <c r="B138" s="34">
+      <c r="B138" s="43">
         <f>Dashboard!$C$5+(134-1)/12</f>
         <v/>
       </c>
@@ -6209,10 +7021,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="33" t="n">
+      <c r="A139" s="42" t="n">
         <v>135</v>
       </c>
-      <c r="B139" s="34">
+      <c r="B139" s="43">
         <f>Dashboard!$C$5+(135-1)/12</f>
         <v/>
       </c>
@@ -6238,10 +7050,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="33" t="n">
+      <c r="A140" s="42" t="n">
         <v>136</v>
       </c>
-      <c r="B140" s="34">
+      <c r="B140" s="43">
         <f>Dashboard!$C$5+(136-1)/12</f>
         <v/>
       </c>
@@ -6267,10 +7079,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="33" t="n">
+      <c r="A141" s="42" t="n">
         <v>137</v>
       </c>
-      <c r="B141" s="34">
+      <c r="B141" s="43">
         <f>Dashboard!$C$5+(137-1)/12</f>
         <v/>
       </c>
@@ -6296,10 +7108,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="33" t="n">
+      <c r="A142" s="42" t="n">
         <v>138</v>
       </c>
-      <c r="B142" s="34">
+      <c r="B142" s="43">
         <f>Dashboard!$C$5+(138-1)/12</f>
         <v/>
       </c>
@@ -6325,10 +7137,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="33" t="n">
+      <c r="A143" s="42" t="n">
         <v>139</v>
       </c>
-      <c r="B143" s="34">
+      <c r="B143" s="43">
         <f>Dashboard!$C$5+(139-1)/12</f>
         <v/>
       </c>
@@ -6354,10 +7166,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="33" t="n">
+      <c r="A144" s="42" t="n">
         <v>140</v>
       </c>
-      <c r="B144" s="34">
+      <c r="B144" s="43">
         <f>Dashboard!$C$5+(140-1)/12</f>
         <v/>
       </c>
@@ -6383,10 +7195,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="33" t="n">
+      <c r="A145" s="42" t="n">
         <v>141</v>
       </c>
-      <c r="B145" s="34">
+      <c r="B145" s="43">
         <f>Dashboard!$C$5+(141-1)/12</f>
         <v/>
       </c>
@@ -6412,10 +7224,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="33" t="n">
+      <c r="A146" s="42" t="n">
         <v>142</v>
       </c>
-      <c r="B146" s="34">
+      <c r="B146" s="43">
         <f>Dashboard!$C$5+(142-1)/12</f>
         <v/>
       </c>
@@ -6441,10 +7253,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="33" t="n">
+      <c r="A147" s="42" t="n">
         <v>143</v>
       </c>
-      <c r="B147" s="34">
+      <c r="B147" s="43">
         <f>Dashboard!$C$5+(143-1)/12</f>
         <v/>
       </c>
@@ -6470,10 +7282,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="33" t="n">
+      <c r="A148" s="42" t="n">
         <v>144</v>
       </c>
-      <c r="B148" s="34">
+      <c r="B148" s="43">
         <f>Dashboard!$C$5+(144-1)/12</f>
         <v/>
       </c>
@@ -6499,10 +7311,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="33" t="n">
+      <c r="A149" s="42" t="n">
         <v>145</v>
       </c>
-      <c r="B149" s="34">
+      <c r="B149" s="43">
         <f>Dashboard!$C$5+(145-1)/12</f>
         <v/>
       </c>
@@ -6528,10 +7340,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="33" t="n">
+      <c r="A150" s="42" t="n">
         <v>146</v>
       </c>
-      <c r="B150" s="34">
+      <c r="B150" s="43">
         <f>Dashboard!$C$5+(146-1)/12</f>
         <v/>
       </c>
@@ -6557,10 +7369,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="33" t="n">
+      <c r="A151" s="42" t="n">
         <v>147</v>
       </c>
-      <c r="B151" s="34">
+      <c r="B151" s="43">
         <f>Dashboard!$C$5+(147-1)/12</f>
         <v/>
       </c>
@@ -6586,10 +7398,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="33" t="n">
+      <c r="A152" s="42" t="n">
         <v>148</v>
       </c>
-      <c r="B152" s="34">
+      <c r="B152" s="43">
         <f>Dashboard!$C$5+(148-1)/12</f>
         <v/>
       </c>
@@ -6615,10 +7427,10 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="33" t="n">
+      <c r="A153" s="42" t="n">
         <v>149</v>
       </c>
-      <c r="B153" s="34">
+      <c r="B153" s="43">
         <f>Dashboard!$C$5+(149-1)/12</f>
         <v/>
       </c>
@@ -6644,10 +7456,10 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="33" t="n">
+      <c r="A154" s="42" t="n">
         <v>150</v>
       </c>
-      <c r="B154" s="34">
+      <c r="B154" s="43">
         <f>Dashboard!$C$5+(150-1)/12</f>
         <v/>
       </c>
@@ -6673,10 +7485,10 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="33" t="n">
+      <c r="A155" s="42" t="n">
         <v>151</v>
       </c>
-      <c r="B155" s="34">
+      <c r="B155" s="43">
         <f>Dashboard!$C$5+(151-1)/12</f>
         <v/>
       </c>
@@ -6702,10 +7514,10 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="33" t="n">
+      <c r="A156" s="42" t="n">
         <v>152</v>
       </c>
-      <c r="B156" s="34">
+      <c r="B156" s="43">
         <f>Dashboard!$C$5+(152-1)/12</f>
         <v/>
       </c>
@@ -6731,10 +7543,10 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="33" t="n">
+      <c r="A157" s="42" t="n">
         <v>153</v>
       </c>
-      <c r="B157" s="34">
+      <c r="B157" s="43">
         <f>Dashboard!$C$5+(153-1)/12</f>
         <v/>
       </c>
@@ -6760,10 +7572,10 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="33" t="n">
+      <c r="A158" s="42" t="n">
         <v>154</v>
       </c>
-      <c r="B158" s="34">
+      <c r="B158" s="43">
         <f>Dashboard!$C$5+(154-1)/12</f>
         <v/>
       </c>
@@ -6789,10 +7601,10 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="33" t="n">
+      <c r="A159" s="42" t="n">
         <v>155</v>
       </c>
-      <c r="B159" s="34">
+      <c r="B159" s="43">
         <f>Dashboard!$C$5+(155-1)/12</f>
         <v/>
       </c>
@@ -6818,10 +7630,10 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="33" t="n">
+      <c r="A160" s="42" t="n">
         <v>156</v>
       </c>
-      <c r="B160" s="34">
+      <c r="B160" s="43">
         <f>Dashboard!$C$5+(156-1)/12</f>
         <v/>
       </c>
@@ -6847,10 +7659,10 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="33" t="n">
+      <c r="A161" s="42" t="n">
         <v>157</v>
       </c>
-      <c r="B161" s="34">
+      <c r="B161" s="43">
         <f>Dashboard!$C$5+(157-1)/12</f>
         <v/>
       </c>
@@ -6876,10 +7688,10 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="33" t="n">
+      <c r="A162" s="42" t="n">
         <v>158</v>
       </c>
-      <c r="B162" s="34">
+      <c r="B162" s="43">
         <f>Dashboard!$C$5+(158-1)/12</f>
         <v/>
       </c>
@@ -6905,10 +7717,10 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="33" t="n">
+      <c r="A163" s="42" t="n">
         <v>159</v>
       </c>
-      <c r="B163" s="34">
+      <c r="B163" s="43">
         <f>Dashboard!$C$5+(159-1)/12</f>
         <v/>
       </c>
@@ -6934,10 +7746,10 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="33" t="n">
+      <c r="A164" s="42" t="n">
         <v>160</v>
       </c>
-      <c r="B164" s="34">
+      <c r="B164" s="43">
         <f>Dashboard!$C$5+(160-1)/12</f>
         <v/>
       </c>
@@ -6963,10 +7775,10 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="33" t="n">
+      <c r="A165" s="42" t="n">
         <v>161</v>
       </c>
-      <c r="B165" s="34">
+      <c r="B165" s="43">
         <f>Dashboard!$C$5+(161-1)/12</f>
         <v/>
       </c>
@@ -6992,10 +7804,10 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="33" t="n">
+      <c r="A166" s="42" t="n">
         <v>162</v>
       </c>
-      <c r="B166" s="34">
+      <c r="B166" s="43">
         <f>Dashboard!$C$5+(162-1)/12</f>
         <v/>
       </c>
@@ -7021,10 +7833,10 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="33" t="n">
+      <c r="A167" s="42" t="n">
         <v>163</v>
       </c>
-      <c r="B167" s="34">
+      <c r="B167" s="43">
         <f>Dashboard!$C$5+(163-1)/12</f>
         <v/>
       </c>
@@ -7050,10 +7862,10 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="33" t="n">
+      <c r="A168" s="42" t="n">
         <v>164</v>
       </c>
-      <c r="B168" s="34">
+      <c r="B168" s="43">
         <f>Dashboard!$C$5+(164-1)/12</f>
         <v/>
       </c>
@@ -7079,10 +7891,10 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="33" t="n">
+      <c r="A169" s="42" t="n">
         <v>165</v>
       </c>
-      <c r="B169" s="34">
+      <c r="B169" s="43">
         <f>Dashboard!$C$5+(165-1)/12</f>
         <v/>
       </c>
@@ -7108,10 +7920,10 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="33" t="n">
+      <c r="A170" s="42" t="n">
         <v>166</v>
       </c>
-      <c r="B170" s="34">
+      <c r="B170" s="43">
         <f>Dashboard!$C$5+(166-1)/12</f>
         <v/>
       </c>
@@ -7137,10 +7949,10 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="33" t="n">
+      <c r="A171" s="42" t="n">
         <v>167</v>
       </c>
-      <c r="B171" s="34">
+      <c r="B171" s="43">
         <f>Dashboard!$C$5+(167-1)/12</f>
         <v/>
       </c>
@@ -7166,10 +7978,10 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="33" t="n">
+      <c r="A172" s="42" t="n">
         <v>168</v>
       </c>
-      <c r="B172" s="34">
+      <c r="B172" s="43">
         <f>Dashboard!$C$5+(168-1)/12</f>
         <v/>
       </c>
@@ -7195,10 +8007,10 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="33" t="n">
+      <c r="A173" s="42" t="n">
         <v>169</v>
       </c>
-      <c r="B173" s="34">
+      <c r="B173" s="43">
         <f>Dashboard!$C$5+(169-1)/12</f>
         <v/>
       </c>
@@ -7224,10 +8036,10 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="33" t="n">
+      <c r="A174" s="42" t="n">
         <v>170</v>
       </c>
-      <c r="B174" s="34">
+      <c r="B174" s="43">
         <f>Dashboard!$C$5+(170-1)/12</f>
         <v/>
       </c>
@@ -7253,10 +8065,10 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="33" t="n">
+      <c r="A175" s="42" t="n">
         <v>171</v>
       </c>
-      <c r="B175" s="34">
+      <c r="B175" s="43">
         <f>Dashboard!$C$5+(171-1)/12</f>
         <v/>
       </c>
@@ -7282,10 +8094,10 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="33" t="n">
+      <c r="A176" s="42" t="n">
         <v>172</v>
       </c>
-      <c r="B176" s="34">
+      <c r="B176" s="43">
         <f>Dashboard!$C$5+(172-1)/12</f>
         <v/>
       </c>
@@ -7311,10 +8123,10 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="33" t="n">
+      <c r="A177" s="42" t="n">
         <v>173</v>
       </c>
-      <c r="B177" s="34">
+      <c r="B177" s="43">
         <f>Dashboard!$C$5+(173-1)/12</f>
         <v/>
       </c>
@@ -7340,10 +8152,10 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="33" t="n">
+      <c r="A178" s="42" t="n">
         <v>174</v>
       </c>
-      <c r="B178" s="34">
+      <c r="B178" s="43">
         <f>Dashboard!$C$5+(174-1)/12</f>
         <v/>
       </c>
@@ -7369,10 +8181,10 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="33" t="n">
+      <c r="A179" s="42" t="n">
         <v>175</v>
       </c>
-      <c r="B179" s="34">
+      <c r="B179" s="43">
         <f>Dashboard!$C$5+(175-1)/12</f>
         <v/>
       </c>
@@ -7398,10 +8210,10 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="33" t="n">
+      <c r="A180" s="42" t="n">
         <v>176</v>
       </c>
-      <c r="B180" s="34">
+      <c r="B180" s="43">
         <f>Dashboard!$C$5+(176-1)/12</f>
         <v/>
       </c>
@@ -7427,10 +8239,10 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="33" t="n">
+      <c r="A181" s="42" t="n">
         <v>177</v>
       </c>
-      <c r="B181" s="34">
+      <c r="B181" s="43">
         <f>Dashboard!$C$5+(177-1)/12</f>
         <v/>
       </c>
@@ -7456,10 +8268,10 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="33" t="n">
+      <c r="A182" s="42" t="n">
         <v>178</v>
       </c>
-      <c r="B182" s="34">
+      <c r="B182" s="43">
         <f>Dashboard!$C$5+(178-1)/12</f>
         <v/>
       </c>
@@ -7485,10 +8297,10 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="33" t="n">
+      <c r="A183" s="42" t="n">
         <v>179</v>
       </c>
-      <c r="B183" s="34">
+      <c r="B183" s="43">
         <f>Dashboard!$C$5+(179-1)/12</f>
         <v/>
       </c>
@@ -7514,10 +8326,10 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="33" t="n">
+      <c r="A184" s="42" t="n">
         <v>180</v>
       </c>
-      <c r="B184" s="34">
+      <c r="B184" s="43">
         <f>Dashboard!$C$5+(180-1)/12</f>
         <v/>
       </c>
@@ -7543,10 +8355,10 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="33" t="n">
+      <c r="A185" s="42" t="n">
         <v>181</v>
       </c>
-      <c r="B185" s="34">
+      <c r="B185" s="43">
         <f>Dashboard!$C$5+(181-1)/12</f>
         <v/>
       </c>
@@ -7572,10 +8384,10 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="33" t="n">
+      <c r="A186" s="42" t="n">
         <v>182</v>
       </c>
-      <c r="B186" s="34">
+      <c r="B186" s="43">
         <f>Dashboard!$C$5+(182-1)/12</f>
         <v/>
       </c>
@@ -7601,10 +8413,10 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="33" t="n">
+      <c r="A187" s="42" t="n">
         <v>183</v>
       </c>
-      <c r="B187" s="34">
+      <c r="B187" s="43">
         <f>Dashboard!$C$5+(183-1)/12</f>
         <v/>
       </c>
@@ -7630,10 +8442,10 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="33" t="n">
+      <c r="A188" s="42" t="n">
         <v>184</v>
       </c>
-      <c r="B188" s="34">
+      <c r="B188" s="43">
         <f>Dashboard!$C$5+(184-1)/12</f>
         <v/>
       </c>
@@ -7659,10 +8471,10 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="33" t="n">
+      <c r="A189" s="42" t="n">
         <v>185</v>
       </c>
-      <c r="B189" s="34">
+      <c r="B189" s="43">
         <f>Dashboard!$C$5+(185-1)/12</f>
         <v/>
       </c>
@@ -7688,10 +8500,10 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="33" t="n">
+      <c r="A190" s="42" t="n">
         <v>186</v>
       </c>
-      <c r="B190" s="34">
+      <c r="B190" s="43">
         <f>Dashboard!$C$5+(186-1)/12</f>
         <v/>
       </c>
@@ -7717,10 +8529,10 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="33" t="n">
+      <c r="A191" s="42" t="n">
         <v>187</v>
       </c>
-      <c r="B191" s="34">
+      <c r="B191" s="43">
         <f>Dashboard!$C$5+(187-1)/12</f>
         <v/>
       </c>
@@ -7746,10 +8558,10 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="33" t="n">
+      <c r="A192" s="42" t="n">
         <v>188</v>
       </c>
-      <c r="B192" s="34">
+      <c r="B192" s="43">
         <f>Dashboard!$C$5+(188-1)/12</f>
         <v/>
       </c>
@@ -7775,10 +8587,10 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="33" t="n">
+      <c r="A193" s="42" t="n">
         <v>189</v>
       </c>
-      <c r="B193" s="34">
+      <c r="B193" s="43">
         <f>Dashboard!$C$5+(189-1)/12</f>
         <v/>
       </c>
@@ -7804,10 +8616,10 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="33" t="n">
+      <c r="A194" s="42" t="n">
         <v>190</v>
       </c>
-      <c r="B194" s="34">
+      <c r="B194" s="43">
         <f>Dashboard!$C$5+(190-1)/12</f>
         <v/>
       </c>
@@ -7833,10 +8645,10 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="33" t="n">
+      <c r="A195" s="42" t="n">
         <v>191</v>
       </c>
-      <c r="B195" s="34">
+      <c r="B195" s="43">
         <f>Dashboard!$C$5+(191-1)/12</f>
         <v/>
       </c>
@@ -7862,10 +8674,10 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="33" t="n">
+      <c r="A196" s="42" t="n">
         <v>192</v>
       </c>
-      <c r="B196" s="34">
+      <c r="B196" s="43">
         <f>Dashboard!$C$5+(192-1)/12</f>
         <v/>
       </c>
@@ -7891,10 +8703,10 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="33" t="n">
+      <c r="A197" s="42" t="n">
         <v>193</v>
       </c>
-      <c r="B197" s="34">
+      <c r="B197" s="43">
         <f>Dashboard!$C$5+(193-1)/12</f>
         <v/>
       </c>
@@ -7920,10 +8732,10 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="33" t="n">
+      <c r="A198" s="42" t="n">
         <v>194</v>
       </c>
-      <c r="B198" s="34">
+      <c r="B198" s="43">
         <f>Dashboard!$C$5+(194-1)/12</f>
         <v/>
       </c>
@@ -7949,10 +8761,10 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="33" t="n">
+      <c r="A199" s="42" t="n">
         <v>195</v>
       </c>
-      <c r="B199" s="34">
+      <c r="B199" s="43">
         <f>Dashboard!$C$5+(195-1)/12</f>
         <v/>
       </c>
@@ -7978,10 +8790,10 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="33" t="n">
+      <c r="A200" s="42" t="n">
         <v>196</v>
       </c>
-      <c r="B200" s="34">
+      <c r="B200" s="43">
         <f>Dashboard!$C$5+(196-1)/12</f>
         <v/>
       </c>
@@ -8007,10 +8819,10 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="33" t="n">
+      <c r="A201" s="42" t="n">
         <v>197</v>
       </c>
-      <c r="B201" s="34">
+      <c r="B201" s="43">
         <f>Dashboard!$C$5+(197-1)/12</f>
         <v/>
       </c>
@@ -8036,10 +8848,10 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="33" t="n">
+      <c r="A202" s="42" t="n">
         <v>198</v>
       </c>
-      <c r="B202" s="34">
+      <c r="B202" s="43">
         <f>Dashboard!$C$5+(198-1)/12</f>
         <v/>
       </c>
@@ -8065,10 +8877,10 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="33" t="n">
+      <c r="A203" s="42" t="n">
         <v>199</v>
       </c>
-      <c r="B203" s="34">
+      <c r="B203" s="43">
         <f>Dashboard!$C$5+(199-1)/12</f>
         <v/>
       </c>
@@ -8094,10 +8906,10 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="33" t="n">
+      <c r="A204" s="42" t="n">
         <v>200</v>
       </c>
-      <c r="B204" s="34">
+      <c r="B204" s="43">
         <f>Dashboard!$C$5+(200-1)/12</f>
         <v/>
       </c>
@@ -8123,10 +8935,10 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="33" t="n">
+      <c r="A205" s="42" t="n">
         <v>201</v>
       </c>
-      <c r="B205" s="34">
+      <c r="B205" s="43">
         <f>Dashboard!$C$5+(201-1)/12</f>
         <v/>
       </c>
@@ -8152,10 +8964,10 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="33" t="n">
+      <c r="A206" s="42" t="n">
         <v>202</v>
       </c>
-      <c r="B206" s="34">
+      <c r="B206" s="43">
         <f>Dashboard!$C$5+(202-1)/12</f>
         <v/>
       </c>
@@ -8181,10 +8993,10 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="33" t="n">
+      <c r="A207" s="42" t="n">
         <v>203</v>
       </c>
-      <c r="B207" s="34">
+      <c r="B207" s="43">
         <f>Dashboard!$C$5+(203-1)/12</f>
         <v/>
       </c>
@@ -8210,10 +9022,10 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="33" t="n">
+      <c r="A208" s="42" t="n">
         <v>204</v>
       </c>
-      <c r="B208" s="34">
+      <c r="B208" s="43">
         <f>Dashboard!$C$5+(204-1)/12</f>
         <v/>
       </c>
@@ -8239,10 +9051,10 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="33" t="n">
+      <c r="A209" s="42" t="n">
         <v>205</v>
       </c>
-      <c r="B209" s="34">
+      <c r="B209" s="43">
         <f>Dashboard!$C$5+(205-1)/12</f>
         <v/>
       </c>
@@ -8268,10 +9080,10 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="33" t="n">
+      <c r="A210" s="42" t="n">
         <v>206</v>
       </c>
-      <c r="B210" s="34">
+      <c r="B210" s="43">
         <f>Dashboard!$C$5+(206-1)/12</f>
         <v/>
       </c>
@@ -8297,10 +9109,10 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="33" t="n">
+      <c r="A211" s="42" t="n">
         <v>207</v>
       </c>
-      <c r="B211" s="34">
+      <c r="B211" s="43">
         <f>Dashboard!$C$5+(207-1)/12</f>
         <v/>
       </c>
@@ -8326,10 +9138,10 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="33" t="n">
+      <c r="A212" s="42" t="n">
         <v>208</v>
       </c>
-      <c r="B212" s="34">
+      <c r="B212" s="43">
         <f>Dashboard!$C$5+(208-1)/12</f>
         <v/>
       </c>
@@ -8355,10 +9167,10 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="33" t="n">
+      <c r="A213" s="42" t="n">
         <v>209</v>
       </c>
-      <c r="B213" s="34">
+      <c r="B213" s="43">
         <f>Dashboard!$C$5+(209-1)/12</f>
         <v/>
       </c>
@@ -8384,10 +9196,10 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="33" t="n">
+      <c r="A214" s="42" t="n">
         <v>210</v>
       </c>
-      <c r="B214" s="34">
+      <c r="B214" s="43">
         <f>Dashboard!$C$5+(210-1)/12</f>
         <v/>
       </c>
@@ -8413,10 +9225,10 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="33" t="n">
+      <c r="A215" s="42" t="n">
         <v>211</v>
       </c>
-      <c r="B215" s="34">
+      <c r="B215" s="43">
         <f>Dashboard!$C$5+(211-1)/12</f>
         <v/>
       </c>
@@ -8442,10 +9254,10 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="33" t="n">
+      <c r="A216" s="42" t="n">
         <v>212</v>
       </c>
-      <c r="B216" s="34">
+      <c r="B216" s="43">
         <f>Dashboard!$C$5+(212-1)/12</f>
         <v/>
       </c>
@@ -8471,10 +9283,10 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="33" t="n">
+      <c r="A217" s="42" t="n">
         <v>213</v>
       </c>
-      <c r="B217" s="34">
+      <c r="B217" s="43">
         <f>Dashboard!$C$5+(213-1)/12</f>
         <v/>
       </c>
@@ -8500,10 +9312,10 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="33" t="n">
+      <c r="A218" s="42" t="n">
         <v>214</v>
       </c>
-      <c r="B218" s="34">
+      <c r="B218" s="43">
         <f>Dashboard!$C$5+(214-1)/12</f>
         <v/>
       </c>
@@ -8529,10 +9341,10 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="33" t="n">
+      <c r="A219" s="42" t="n">
         <v>215</v>
       </c>
-      <c r="B219" s="34">
+      <c r="B219" s="43">
         <f>Dashboard!$C$5+(215-1)/12</f>
         <v/>
       </c>
@@ -8558,10 +9370,10 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="33" t="n">
+      <c r="A220" s="42" t="n">
         <v>216</v>
       </c>
-      <c r="B220" s="34">
+      <c r="B220" s="43">
         <f>Dashboard!$C$5+(216-1)/12</f>
         <v/>
       </c>
@@ -8587,10 +9399,10 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="33" t="n">
+      <c r="A221" s="42" t="n">
         <v>217</v>
       </c>
-      <c r="B221" s="34">
+      <c r="B221" s="43">
         <f>Dashboard!$C$5+(217-1)/12</f>
         <v/>
       </c>
@@ -8616,10 +9428,10 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="33" t="n">
+      <c r="A222" s="42" t="n">
         <v>218</v>
       </c>
-      <c r="B222" s="34">
+      <c r="B222" s="43">
         <f>Dashboard!$C$5+(218-1)/12</f>
         <v/>
       </c>
@@ -8645,10 +9457,10 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="33" t="n">
+      <c r="A223" s="42" t="n">
         <v>219</v>
       </c>
-      <c r="B223" s="34">
+      <c r="B223" s="43">
         <f>Dashboard!$C$5+(219-1)/12</f>
         <v/>
       </c>
@@ -8674,10 +9486,10 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="33" t="n">
+      <c r="A224" s="42" t="n">
         <v>220</v>
       </c>
-      <c r="B224" s="34">
+      <c r="B224" s="43">
         <f>Dashboard!$C$5+(220-1)/12</f>
         <v/>
       </c>
@@ -8703,10 +9515,10 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="33" t="n">
+      <c r="A225" s="42" t="n">
         <v>221</v>
       </c>
-      <c r="B225" s="34">
+      <c r="B225" s="43">
         <f>Dashboard!$C$5+(221-1)/12</f>
         <v/>
       </c>
@@ -8732,10 +9544,10 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="33" t="n">
+      <c r="A226" s="42" t="n">
         <v>222</v>
       </c>
-      <c r="B226" s="34">
+      <c r="B226" s="43">
         <f>Dashboard!$C$5+(222-1)/12</f>
         <v/>
       </c>
@@ -8761,10 +9573,10 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="33" t="n">
+      <c r="A227" s="42" t="n">
         <v>223</v>
       </c>
-      <c r="B227" s="34">
+      <c r="B227" s="43">
         <f>Dashboard!$C$5+(223-1)/12</f>
         <v/>
       </c>
@@ -8790,10 +9602,10 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="33" t="n">
+      <c r="A228" s="42" t="n">
         <v>224</v>
       </c>
-      <c r="B228" s="34">
+      <c r="B228" s="43">
         <f>Dashboard!$C$5+(224-1)/12</f>
         <v/>
       </c>
@@ -8819,10 +9631,10 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="33" t="n">
+      <c r="A229" s="42" t="n">
         <v>225</v>
       </c>
-      <c r="B229" s="34">
+      <c r="B229" s="43">
         <f>Dashboard!$C$5+(225-1)/12</f>
         <v/>
       </c>
@@ -8848,10 +9660,10 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="33" t="n">
+      <c r="A230" s="42" t="n">
         <v>226</v>
       </c>
-      <c r="B230" s="34">
+      <c r="B230" s="43">
         <f>Dashboard!$C$5+(226-1)/12</f>
         <v/>
       </c>
@@ -8877,10 +9689,10 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="33" t="n">
+      <c r="A231" s="42" t="n">
         <v>227</v>
       </c>
-      <c r="B231" s="34">
+      <c r="B231" s="43">
         <f>Dashboard!$C$5+(227-1)/12</f>
         <v/>
       </c>
@@ -8906,10 +9718,10 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="33" t="n">
+      <c r="A232" s="42" t="n">
         <v>228</v>
       </c>
-      <c r="B232" s="34">
+      <c r="B232" s="43">
         <f>Dashboard!$C$5+(228-1)/12</f>
         <v/>
       </c>
@@ -8935,10 +9747,10 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="33" t="n">
+      <c r="A233" s="42" t="n">
         <v>229</v>
       </c>
-      <c r="B233" s="34">
+      <c r="B233" s="43">
         <f>Dashboard!$C$5+(229-1)/12</f>
         <v/>
       </c>
@@ -8964,10 +9776,10 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="33" t="n">
+      <c r="A234" s="42" t="n">
         <v>230</v>
       </c>
-      <c r="B234" s="34">
+      <c r="B234" s="43">
         <f>Dashboard!$C$5+(230-1)/12</f>
         <v/>
       </c>
@@ -8993,10 +9805,10 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="33" t="n">
+      <c r="A235" s="42" t="n">
         <v>231</v>
       </c>
-      <c r="B235" s="34">
+      <c r="B235" s="43">
         <f>Dashboard!$C$5+(231-1)/12</f>
         <v/>
       </c>
@@ -9022,10 +9834,10 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="33" t="n">
+      <c r="A236" s="42" t="n">
         <v>232</v>
       </c>
-      <c r="B236" s="34">
+      <c r="B236" s="43">
         <f>Dashboard!$C$5+(232-1)/12</f>
         <v/>
       </c>
@@ -9051,10 +9863,10 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="33" t="n">
+      <c r="A237" s="42" t="n">
         <v>233</v>
       </c>
-      <c r="B237" s="34">
+      <c r="B237" s="43">
         <f>Dashboard!$C$5+(233-1)/12</f>
         <v/>
       </c>
@@ -9080,10 +9892,10 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="33" t="n">
+      <c r="A238" s="42" t="n">
         <v>234</v>
       </c>
-      <c r="B238" s="34">
+      <c r="B238" s="43">
         <f>Dashboard!$C$5+(234-1)/12</f>
         <v/>
       </c>
@@ -9109,10 +9921,10 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="33" t="n">
+      <c r="A239" s="42" t="n">
         <v>235</v>
       </c>
-      <c r="B239" s="34">
+      <c r="B239" s="43">
         <f>Dashboard!$C$5+(235-1)/12</f>
         <v/>
       </c>
@@ -9138,10 +9950,10 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="33" t="n">
+      <c r="A240" s="42" t="n">
         <v>236</v>
       </c>
-      <c r="B240" s="34">
+      <c r="B240" s="43">
         <f>Dashboard!$C$5+(236-1)/12</f>
         <v/>
       </c>
@@ -9167,10 +9979,10 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="33" t="n">
+      <c r="A241" s="42" t="n">
         <v>237</v>
       </c>
-      <c r="B241" s="34">
+      <c r="B241" s="43">
         <f>Dashboard!$C$5+(237-1)/12</f>
         <v/>
       </c>
@@ -9196,10 +10008,10 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="33" t="n">
+      <c r="A242" s="42" t="n">
         <v>238</v>
       </c>
-      <c r="B242" s="34">
+      <c r="B242" s="43">
         <f>Dashboard!$C$5+(238-1)/12</f>
         <v/>
       </c>
@@ -9225,10 +10037,10 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="33" t="n">
+      <c r="A243" s="42" t="n">
         <v>239</v>
       </c>
-      <c r="B243" s="34">
+      <c r="B243" s="43">
         <f>Dashboard!$C$5+(239-1)/12</f>
         <v/>
       </c>
@@ -9254,10 +10066,10 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="33" t="n">
+      <c r="A244" s="42" t="n">
         <v>240</v>
       </c>
-      <c r="B244" s="34">
+      <c r="B244" s="43">
         <f>Dashboard!$C$5+(240-1)/12</f>
         <v/>
       </c>
@@ -9283,10 +10095,10 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="33" t="n">
+      <c r="A245" s="42" t="n">
         <v>241</v>
       </c>
-      <c r="B245" s="34">
+      <c r="B245" s="43">
         <f>Dashboard!$C$5+(241-1)/12</f>
         <v/>
       </c>
@@ -9312,10 +10124,10 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="33" t="n">
+      <c r="A246" s="42" t="n">
         <v>242</v>
       </c>
-      <c r="B246" s="34">
+      <c r="B246" s="43">
         <f>Dashboard!$C$5+(242-1)/12</f>
         <v/>
       </c>
@@ -9341,10 +10153,10 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="33" t="n">
+      <c r="A247" s="42" t="n">
         <v>243</v>
       </c>
-      <c r="B247" s="34">
+      <c r="B247" s="43">
         <f>Dashboard!$C$5+(243-1)/12</f>
         <v/>
       </c>
@@ -9370,10 +10182,10 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="33" t="n">
+      <c r="A248" s="42" t="n">
         <v>244</v>
       </c>
-      <c r="B248" s="34">
+      <c r="B248" s="43">
         <f>Dashboard!$C$5+(244-1)/12</f>
         <v/>
       </c>
@@ -9399,10 +10211,10 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="33" t="n">
+      <c r="A249" s="42" t="n">
         <v>245</v>
       </c>
-      <c r="B249" s="34">
+      <c r="B249" s="43">
         <f>Dashboard!$C$5+(245-1)/12</f>
         <v/>
       </c>
@@ -9428,10 +10240,10 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="33" t="n">
+      <c r="A250" s="42" t="n">
         <v>246</v>
       </c>
-      <c r="B250" s="34">
+      <c r="B250" s="43">
         <f>Dashboard!$C$5+(246-1)/12</f>
         <v/>
       </c>
@@ -9457,10 +10269,10 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="33" t="n">
+      <c r="A251" s="42" t="n">
         <v>247</v>
       </c>
-      <c r="B251" s="34">
+      <c r="B251" s="43">
         <f>Dashboard!$C$5+(247-1)/12</f>
         <v/>
       </c>
@@ -9486,10 +10298,10 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="33" t="n">
+      <c r="A252" s="42" t="n">
         <v>248</v>
       </c>
-      <c r="B252" s="34">
+      <c r="B252" s="43">
         <f>Dashboard!$C$5+(248-1)/12</f>
         <v/>
       </c>
@@ -9515,10 +10327,10 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="33" t="n">
+      <c r="A253" s="42" t="n">
         <v>249</v>
       </c>
-      <c r="B253" s="34">
+      <c r="B253" s="43">
         <f>Dashboard!$C$5+(249-1)/12</f>
         <v/>
       </c>
@@ -9544,10 +10356,10 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="33" t="n">
+      <c r="A254" s="42" t="n">
         <v>250</v>
       </c>
-      <c r="B254" s="34">
+      <c r="B254" s="43">
         <f>Dashboard!$C$5+(250-1)/12</f>
         <v/>
       </c>
@@ -9573,10 +10385,10 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="33" t="n">
+      <c r="A255" s="42" t="n">
         <v>251</v>
       </c>
-      <c r="B255" s="34">
+      <c r="B255" s="43">
         <f>Dashboard!$C$5+(251-1)/12</f>
         <v/>
       </c>
@@ -9602,10 +10414,10 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="33" t="n">
+      <c r="A256" s="42" t="n">
         <v>252</v>
       </c>
-      <c r="B256" s="34">
+      <c r="B256" s="43">
         <f>Dashboard!$C$5+(252-1)/12</f>
         <v/>
       </c>
@@ -9631,10 +10443,10 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="33" t="n">
+      <c r="A257" s="42" t="n">
         <v>253</v>
       </c>
-      <c r="B257" s="34">
+      <c r="B257" s="43">
         <f>Dashboard!$C$5+(253-1)/12</f>
         <v/>
       </c>
@@ -9660,10 +10472,10 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="33" t="n">
+      <c r="A258" s="42" t="n">
         <v>254</v>
       </c>
-      <c r="B258" s="34">
+      <c r="B258" s="43">
         <f>Dashboard!$C$5+(254-1)/12</f>
         <v/>
       </c>
@@ -9689,10 +10501,10 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="33" t="n">
+      <c r="A259" s="42" t="n">
         <v>255</v>
       </c>
-      <c r="B259" s="34">
+      <c r="B259" s="43">
         <f>Dashboard!$C$5+(255-1)/12</f>
         <v/>
       </c>
@@ -9718,10 +10530,10 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="33" t="n">
+      <c r="A260" s="42" t="n">
         <v>256</v>
       </c>
-      <c r="B260" s="34">
+      <c r="B260" s="43">
         <f>Dashboard!$C$5+(256-1)/12</f>
         <v/>
       </c>
@@ -9747,10 +10559,10 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="33" t="n">
+      <c r="A261" s="42" t="n">
         <v>257</v>
       </c>
-      <c r="B261" s="34">
+      <c r="B261" s="43">
         <f>Dashboard!$C$5+(257-1)/12</f>
         <v/>
       </c>
@@ -9776,10 +10588,10 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="33" t="n">
+      <c r="A262" s="42" t="n">
         <v>258</v>
       </c>
-      <c r="B262" s="34">
+      <c r="B262" s="43">
         <f>Dashboard!$C$5+(258-1)/12</f>
         <v/>
       </c>
@@ -9805,10 +10617,10 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="33" t="n">
+      <c r="A263" s="42" t="n">
         <v>259</v>
       </c>
-      <c r="B263" s="34">
+      <c r="B263" s="43">
         <f>Dashboard!$C$5+(259-1)/12</f>
         <v/>
       </c>
@@ -9834,10 +10646,10 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="33" t="n">
+      <c r="A264" s="42" t="n">
         <v>260</v>
       </c>
-      <c r="B264" s="34">
+      <c r="B264" s="43">
         <f>Dashboard!$C$5+(260-1)/12</f>
         <v/>
       </c>
@@ -9863,10 +10675,10 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="33" t="n">
+      <c r="A265" s="42" t="n">
         <v>261</v>
       </c>
-      <c r="B265" s="34">
+      <c r="B265" s="43">
         <f>Dashboard!$C$5+(261-1)/12</f>
         <v/>
       </c>
@@ -9892,10 +10704,10 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="33" t="n">
+      <c r="A266" s="42" t="n">
         <v>262</v>
       </c>
-      <c r="B266" s="34">
+      <c r="B266" s="43">
         <f>Dashboard!$C$5+(262-1)/12</f>
         <v/>
       </c>
@@ -9921,10 +10733,10 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="33" t="n">
+      <c r="A267" s="42" t="n">
         <v>263</v>
       </c>
-      <c r="B267" s="34">
+      <c r="B267" s="43">
         <f>Dashboard!$C$5+(263-1)/12</f>
         <v/>
       </c>
@@ -9950,10 +10762,10 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="33" t="n">
+      <c r="A268" s="42" t="n">
         <v>264</v>
       </c>
-      <c r="B268" s="34">
+      <c r="B268" s="43">
         <f>Dashboard!$C$5+(264-1)/12</f>
         <v/>
       </c>
@@ -9979,10 +10791,10 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="33" t="n">
+      <c r="A269" s="42" t="n">
         <v>265</v>
       </c>
-      <c r="B269" s="34">
+      <c r="B269" s="43">
         <f>Dashboard!$C$5+(265-1)/12</f>
         <v/>
       </c>
@@ -10008,10 +10820,10 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="33" t="n">
+      <c r="A270" s="42" t="n">
         <v>266</v>
       </c>
-      <c r="B270" s="34">
+      <c r="B270" s="43">
         <f>Dashboard!$C$5+(266-1)/12</f>
         <v/>
       </c>
@@ -10037,10 +10849,10 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="33" t="n">
+      <c r="A271" s="42" t="n">
         <v>267</v>
       </c>
-      <c r="B271" s="34">
+      <c r="B271" s="43">
         <f>Dashboard!$C$5+(267-1)/12</f>
         <v/>
       </c>
@@ -10066,10 +10878,10 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="33" t="n">
+      <c r="A272" s="42" t="n">
         <v>268</v>
       </c>
-      <c r="B272" s="34">
+      <c r="B272" s="43">
         <f>Dashboard!$C$5+(268-1)/12</f>
         <v/>
       </c>
@@ -10095,10 +10907,10 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="33" t="n">
+      <c r="A273" s="42" t="n">
         <v>269</v>
       </c>
-      <c r="B273" s="34">
+      <c r="B273" s="43">
         <f>Dashboard!$C$5+(269-1)/12</f>
         <v/>
       </c>
@@ -10124,10 +10936,10 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="33" t="n">
+      <c r="A274" s="42" t="n">
         <v>270</v>
       </c>
-      <c r="B274" s="34">
+      <c r="B274" s="43">
         <f>Dashboard!$C$5+(270-1)/12</f>
         <v/>
       </c>
@@ -10153,10 +10965,10 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="33" t="n">
+      <c r="A275" s="42" t="n">
         <v>271</v>
       </c>
-      <c r="B275" s="34">
+      <c r="B275" s="43">
         <f>Dashboard!$C$5+(271-1)/12</f>
         <v/>
       </c>
@@ -10182,10 +10994,10 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="33" t="n">
+      <c r="A276" s="42" t="n">
         <v>272</v>
       </c>
-      <c r="B276" s="34">
+      <c r="B276" s="43">
         <f>Dashboard!$C$5+(272-1)/12</f>
         <v/>
       </c>
@@ -10211,10 +11023,10 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="33" t="n">
+      <c r="A277" s="42" t="n">
         <v>273</v>
       </c>
-      <c r="B277" s="34">
+      <c r="B277" s="43">
         <f>Dashboard!$C$5+(273-1)/12</f>
         <v/>
       </c>
@@ -10240,10 +11052,10 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="33" t="n">
+      <c r="A278" s="42" t="n">
         <v>274</v>
       </c>
-      <c r="B278" s="34">
+      <c r="B278" s="43">
         <f>Dashboard!$C$5+(274-1)/12</f>
         <v/>
       </c>
@@ -10269,10 +11081,10 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="33" t="n">
+      <c r="A279" s="42" t="n">
         <v>275</v>
       </c>
-      <c r="B279" s="34">
+      <c r="B279" s="43">
         <f>Dashboard!$C$5+(275-1)/12</f>
         <v/>
       </c>
@@ -10298,10 +11110,10 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="33" t="n">
+      <c r="A280" s="42" t="n">
         <v>276</v>
       </c>
-      <c r="B280" s="34">
+      <c r="B280" s="43">
         <f>Dashboard!$C$5+(276-1)/12</f>
         <v/>
       </c>
@@ -10327,10 +11139,10 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="33" t="n">
+      <c r="A281" s="42" t="n">
         <v>277</v>
       </c>
-      <c r="B281" s="34">
+      <c r="B281" s="43">
         <f>Dashboard!$C$5+(277-1)/12</f>
         <v/>
       </c>
@@ -10356,10 +11168,10 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="33" t="n">
+      <c r="A282" s="42" t="n">
         <v>278</v>
       </c>
-      <c r="B282" s="34">
+      <c r="B282" s="43">
         <f>Dashboard!$C$5+(278-1)/12</f>
         <v/>
       </c>
@@ -10385,10 +11197,10 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="33" t="n">
+      <c r="A283" s="42" t="n">
         <v>279</v>
       </c>
-      <c r="B283" s="34">
+      <c r="B283" s="43">
         <f>Dashboard!$C$5+(279-1)/12</f>
         <v/>
       </c>
@@ -10414,10 +11226,10 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="33" t="n">
+      <c r="A284" s="42" t="n">
         <v>280</v>
       </c>
-      <c r="B284" s="34">
+      <c r="B284" s="43">
         <f>Dashboard!$C$5+(280-1)/12</f>
         <v/>
       </c>
@@ -10443,10 +11255,10 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="33" t="n">
+      <c r="A285" s="42" t="n">
         <v>281</v>
       </c>
-      <c r="B285" s="34">
+      <c r="B285" s="43">
         <f>Dashboard!$C$5+(281-1)/12</f>
         <v/>
       </c>
@@ -10472,10 +11284,10 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="33" t="n">
+      <c r="A286" s="42" t="n">
         <v>282</v>
       </c>
-      <c r="B286" s="34">
+      <c r="B286" s="43">
         <f>Dashboard!$C$5+(282-1)/12</f>
         <v/>
       </c>
@@ -10501,10 +11313,10 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="33" t="n">
+      <c r="A287" s="42" t="n">
         <v>283</v>
       </c>
-      <c r="B287" s="34">
+      <c r="B287" s="43">
         <f>Dashboard!$C$5+(283-1)/12</f>
         <v/>
       </c>
@@ -10530,10 +11342,10 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="33" t="n">
+      <c r="A288" s="42" t="n">
         <v>284</v>
       </c>
-      <c r="B288" s="34">
+      <c r="B288" s="43">
         <f>Dashboard!$C$5+(284-1)/12</f>
         <v/>
       </c>
@@ -10559,10 +11371,10 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="33" t="n">
+      <c r="A289" s="42" t="n">
         <v>285</v>
       </c>
-      <c r="B289" s="34">
+      <c r="B289" s="43">
         <f>Dashboard!$C$5+(285-1)/12</f>
         <v/>
       </c>
@@ -10588,10 +11400,10 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="33" t="n">
+      <c r="A290" s="42" t="n">
         <v>286</v>
       </c>
-      <c r="B290" s="34">
+      <c r="B290" s="43">
         <f>Dashboard!$C$5+(286-1)/12</f>
         <v/>
       </c>
@@ -10617,10 +11429,10 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="33" t="n">
+      <c r="A291" s="42" t="n">
         <v>287</v>
       </c>
-      <c r="B291" s="34">
+      <c r="B291" s="43">
         <f>Dashboard!$C$5+(287-1)/12</f>
         <v/>
       </c>
@@ -10646,10 +11458,10 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="33" t="n">
+      <c r="A292" s="42" t="n">
         <v>288</v>
       </c>
-      <c r="B292" s="34">
+      <c r="B292" s="43">
         <f>Dashboard!$C$5+(288-1)/12</f>
         <v/>
       </c>
@@ -10675,10 +11487,10 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="33" t="n">
+      <c r="A293" s="42" t="n">
         <v>289</v>
       </c>
-      <c r="B293" s="34">
+      <c r="B293" s="43">
         <f>Dashboard!$C$5+(289-1)/12</f>
         <v/>
       </c>
@@ -10704,10 +11516,10 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="33" t="n">
+      <c r="A294" s="42" t="n">
         <v>290</v>
       </c>
-      <c r="B294" s="34">
+      <c r="B294" s="43">
         <f>Dashboard!$C$5+(290-1)/12</f>
         <v/>
       </c>
@@ -10733,10 +11545,10 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="33" t="n">
+      <c r="A295" s="42" t="n">
         <v>291</v>
       </c>
-      <c r="B295" s="34">
+      <c r="B295" s="43">
         <f>Dashboard!$C$5+(291-1)/12</f>
         <v/>
       </c>
@@ -10762,10 +11574,10 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="33" t="n">
+      <c r="A296" s="42" t="n">
         <v>292</v>
       </c>
-      <c r="B296" s="34">
+      <c r="B296" s="43">
         <f>Dashboard!$C$5+(292-1)/12</f>
         <v/>
       </c>
@@ -10791,10 +11603,10 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="33" t="n">
+      <c r="A297" s="42" t="n">
         <v>293</v>
       </c>
-      <c r="B297" s="34">
+      <c r="B297" s="43">
         <f>Dashboard!$C$5+(293-1)/12</f>
         <v/>
       </c>
@@ -10820,10 +11632,10 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="33" t="n">
+      <c r="A298" s="42" t="n">
         <v>294</v>
       </c>
-      <c r="B298" s="34">
+      <c r="B298" s="43">
         <f>Dashboard!$C$5+(294-1)/12</f>
         <v/>
       </c>
@@ -10849,10 +11661,10 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="33" t="n">
+      <c r="A299" s="42" t="n">
         <v>295</v>
       </c>
-      <c r="B299" s="34">
+      <c r="B299" s="43">
         <f>Dashboard!$C$5+(295-1)/12</f>
         <v/>
       </c>
@@ -10878,10 +11690,10 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="33" t="n">
+      <c r="A300" s="42" t="n">
         <v>296</v>
       </c>
-      <c r="B300" s="34">
+      <c r="B300" s="43">
         <f>Dashboard!$C$5+(296-1)/12</f>
         <v/>
       </c>
@@ -10907,10 +11719,10 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="33" t="n">
+      <c r="A301" s="42" t="n">
         <v>297</v>
       </c>
-      <c r="B301" s="34">
+      <c r="B301" s="43">
         <f>Dashboard!$C$5+(297-1)/12</f>
         <v/>
       </c>
@@ -10936,10 +11748,10 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="33" t="n">
+      <c r="A302" s="42" t="n">
         <v>298</v>
       </c>
-      <c r="B302" s="34">
+      <c r="B302" s="43">
         <f>Dashboard!$C$5+(298-1)/12</f>
         <v/>
       </c>
@@ -10965,10 +11777,10 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="33" t="n">
+      <c r="A303" s="42" t="n">
         <v>299</v>
       </c>
-      <c r="B303" s="34">
+      <c r="B303" s="43">
         <f>Dashboard!$C$5+(299-1)/12</f>
         <v/>
       </c>
@@ -10994,10 +11806,10 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="33" t="n">
+      <c r="A304" s="42" t="n">
         <v>300</v>
       </c>
-      <c r="B304" s="34">
+      <c r="B304" s="43">
         <f>Dashboard!$C$5+(300-1)/12</f>
         <v/>
       </c>
@@ -11023,10 +11835,10 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="33" t="n">
+      <c r="A305" s="42" t="n">
         <v>301</v>
       </c>
-      <c r="B305" s="34">
+      <c r="B305" s="43">
         <f>Dashboard!$C$5+(301-1)/12</f>
         <v/>
       </c>
@@ -11052,10 +11864,10 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="33" t="n">
+      <c r="A306" s="42" t="n">
         <v>302</v>
       </c>
-      <c r="B306" s="34">
+      <c r="B306" s="43">
         <f>Dashboard!$C$5+(302-1)/12</f>
         <v/>
       </c>
@@ -11081,10 +11893,10 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="33" t="n">
+      <c r="A307" s="42" t="n">
         <v>303</v>
       </c>
-      <c r="B307" s="34">
+      <c r="B307" s="43">
         <f>Dashboard!$C$5+(303-1)/12</f>
         <v/>
       </c>
@@ -11110,10 +11922,10 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="33" t="n">
+      <c r="A308" s="42" t="n">
         <v>304</v>
       </c>
-      <c r="B308" s="34">
+      <c r="B308" s="43">
         <f>Dashboard!$C$5+(304-1)/12</f>
         <v/>
       </c>
@@ -11139,10 +11951,10 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="33" t="n">
+      <c r="A309" s="42" t="n">
         <v>305</v>
       </c>
-      <c r="B309" s="34">
+      <c r="B309" s="43">
         <f>Dashboard!$C$5+(305-1)/12</f>
         <v/>
       </c>
@@ -11168,10 +11980,10 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="33" t="n">
+      <c r="A310" s="42" t="n">
         <v>306</v>
       </c>
-      <c r="B310" s="34">
+      <c r="B310" s="43">
         <f>Dashboard!$C$5+(306-1)/12</f>
         <v/>
       </c>
@@ -11197,10 +12009,10 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="33" t="n">
+      <c r="A311" s="42" t="n">
         <v>307</v>
       </c>
-      <c r="B311" s="34">
+      <c r="B311" s="43">
         <f>Dashboard!$C$5+(307-1)/12</f>
         <v/>
       </c>
@@ -11226,10 +12038,10 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="33" t="n">
+      <c r="A312" s="42" t="n">
         <v>308</v>
       </c>
-      <c r="B312" s="34">
+      <c r="B312" s="43">
         <f>Dashboard!$C$5+(308-1)/12</f>
         <v/>
       </c>
@@ -11255,10 +12067,10 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="33" t="n">
+      <c r="A313" s="42" t="n">
         <v>309</v>
       </c>
-      <c r="B313" s="34">
+      <c r="B313" s="43">
         <f>Dashboard!$C$5+(309-1)/12</f>
         <v/>
       </c>
@@ -11284,10 +12096,10 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="33" t="n">
+      <c r="A314" s="42" t="n">
         <v>310</v>
       </c>
-      <c r="B314" s="34">
+      <c r="B314" s="43">
         <f>Dashboard!$C$5+(310-1)/12</f>
         <v/>
       </c>
@@ -11313,10 +12125,10 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="33" t="n">
+      <c r="A315" s="42" t="n">
         <v>311</v>
       </c>
-      <c r="B315" s="34">
+      <c r="B315" s="43">
         <f>Dashboard!$C$5+(311-1)/12</f>
         <v/>
       </c>
@@ -11342,10 +12154,10 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="33" t="n">
+      <c r="A316" s="42" t="n">
         <v>312</v>
       </c>
-      <c r="B316" s="34">
+      <c r="B316" s="43">
         <f>Dashboard!$C$5+(312-1)/12</f>
         <v/>
       </c>
@@ -11371,10 +12183,10 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="33" t="n">
+      <c r="A317" s="42" t="n">
         <v>313</v>
       </c>
-      <c r="B317" s="34">
+      <c r="B317" s="43">
         <f>Dashboard!$C$5+(313-1)/12</f>
         <v/>
       </c>
@@ -11400,10 +12212,10 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="33" t="n">
+      <c r="A318" s="42" t="n">
         <v>314</v>
       </c>
-      <c r="B318" s="34">
+      <c r="B318" s="43">
         <f>Dashboard!$C$5+(314-1)/12</f>
         <v/>
       </c>
@@ -11429,10 +12241,10 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="33" t="n">
+      <c r="A319" s="42" t="n">
         <v>315</v>
       </c>
-      <c r="B319" s="34">
+      <c r="B319" s="43">
         <f>Dashboard!$C$5+(315-1)/12</f>
         <v/>
       </c>
@@ -11458,10 +12270,10 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="33" t="n">
+      <c r="A320" s="42" t="n">
         <v>316</v>
       </c>
-      <c r="B320" s="34">
+      <c r="B320" s="43">
         <f>Dashboard!$C$5+(316-1)/12</f>
         <v/>
       </c>
@@ -11487,10 +12299,10 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="33" t="n">
+      <c r="A321" s="42" t="n">
         <v>317</v>
       </c>
-      <c r="B321" s="34">
+      <c r="B321" s="43">
         <f>Dashboard!$C$5+(317-1)/12</f>
         <v/>
       </c>
@@ -11516,10 +12328,10 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="33" t="n">
+      <c r="A322" s="42" t="n">
         <v>318</v>
       </c>
-      <c r="B322" s="34">
+      <c r="B322" s="43">
         <f>Dashboard!$C$5+(318-1)/12</f>
         <v/>
       </c>
@@ -11545,10 +12357,10 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="33" t="n">
+      <c r="A323" s="42" t="n">
         <v>319</v>
       </c>
-      <c r="B323" s="34">
+      <c r="B323" s="43">
         <f>Dashboard!$C$5+(319-1)/12</f>
         <v/>
       </c>
@@ -11574,10 +12386,10 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="33" t="n">
+      <c r="A324" s="42" t="n">
         <v>320</v>
       </c>
-      <c r="B324" s="34">
+      <c r="B324" s="43">
         <f>Dashboard!$C$5+(320-1)/12</f>
         <v/>
       </c>
@@ -11603,10 +12415,10 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="33" t="n">
+      <c r="A325" s="42" t="n">
         <v>321</v>
       </c>
-      <c r="B325" s="34">
+      <c r="B325" s="43">
         <f>Dashboard!$C$5+(321-1)/12</f>
         <v/>
       </c>
@@ -11632,10 +12444,10 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="33" t="n">
+      <c r="A326" s="42" t="n">
         <v>322</v>
       </c>
-      <c r="B326" s="34">
+      <c r="B326" s="43">
         <f>Dashboard!$C$5+(322-1)/12</f>
         <v/>
       </c>
@@ -11661,10 +12473,10 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="33" t="n">
+      <c r="A327" s="42" t="n">
         <v>323</v>
       </c>
-      <c r="B327" s="34">
+      <c r="B327" s="43">
         <f>Dashboard!$C$5+(323-1)/12</f>
         <v/>
       </c>
@@ -11690,10 +12502,10 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="33" t="n">
+      <c r="A328" s="42" t="n">
         <v>324</v>
       </c>
-      <c r="B328" s="34">
+      <c r="B328" s="43">
         <f>Dashboard!$C$5+(324-1)/12</f>
         <v/>
       </c>
@@ -11719,10 +12531,10 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="33" t="n">
+      <c r="A329" s="42" t="n">
         <v>325</v>
       </c>
-      <c r="B329" s="34">
+      <c r="B329" s="43">
         <f>Dashboard!$C$5+(325-1)/12</f>
         <v/>
       </c>
@@ -11748,10 +12560,10 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="33" t="n">
+      <c r="A330" s="42" t="n">
         <v>326</v>
       </c>
-      <c r="B330" s="34">
+      <c r="B330" s="43">
         <f>Dashboard!$C$5+(326-1)/12</f>
         <v/>
       </c>
@@ -11777,10 +12589,10 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="33" t="n">
+      <c r="A331" s="42" t="n">
         <v>327</v>
       </c>
-      <c r="B331" s="34">
+      <c r="B331" s="43">
         <f>Dashboard!$C$5+(327-1)/12</f>
         <v/>
       </c>
@@ -11806,10 +12618,10 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="33" t="n">
+      <c r="A332" s="42" t="n">
         <v>328</v>
       </c>
-      <c r="B332" s="34">
+      <c r="B332" s="43">
         <f>Dashboard!$C$5+(328-1)/12</f>
         <v/>
       </c>
@@ -11835,10 +12647,10 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="33" t="n">
+      <c r="A333" s="42" t="n">
         <v>329</v>
       </c>
-      <c r="B333" s="34">
+      <c r="B333" s="43">
         <f>Dashboard!$C$5+(329-1)/12</f>
         <v/>
       </c>
@@ -11864,10 +12676,10 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="33" t="n">
+      <c r="A334" s="42" t="n">
         <v>330</v>
       </c>
-      <c r="B334" s="34">
+      <c r="B334" s="43">
         <f>Dashboard!$C$5+(330-1)/12</f>
         <v/>
       </c>
@@ -11893,10 +12705,10 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="33" t="n">
+      <c r="A335" s="42" t="n">
         <v>331</v>
       </c>
-      <c r="B335" s="34">
+      <c r="B335" s="43">
         <f>Dashboard!$C$5+(331-1)/12</f>
         <v/>
       </c>
@@ -11922,10 +12734,10 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="33" t="n">
+      <c r="A336" s="42" t="n">
         <v>332</v>
       </c>
-      <c r="B336" s="34">
+      <c r="B336" s="43">
         <f>Dashboard!$C$5+(332-1)/12</f>
         <v/>
       </c>
@@ -11951,10 +12763,10 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="33" t="n">
+      <c r="A337" s="42" t="n">
         <v>333</v>
       </c>
-      <c r="B337" s="34">
+      <c r="B337" s="43">
         <f>Dashboard!$C$5+(333-1)/12</f>
         <v/>
       </c>
@@ -11980,10 +12792,10 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="33" t="n">
+      <c r="A338" s="42" t="n">
         <v>334</v>
       </c>
-      <c r="B338" s="34">
+      <c r="B338" s="43">
         <f>Dashboard!$C$5+(334-1)/12</f>
         <v/>
       </c>
@@ -12009,10 +12821,10 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="33" t="n">
+      <c r="A339" s="42" t="n">
         <v>335</v>
       </c>
-      <c r="B339" s="34">
+      <c r="B339" s="43">
         <f>Dashboard!$C$5+(335-1)/12</f>
         <v/>
       </c>
@@ -12038,10 +12850,10 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="33" t="n">
+      <c r="A340" s="42" t="n">
         <v>336</v>
       </c>
-      <c r="B340" s="34">
+      <c r="B340" s="43">
         <f>Dashboard!$C$5+(336-1)/12</f>
         <v/>
       </c>
@@ -12067,10 +12879,10 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="33" t="n">
+      <c r="A341" s="42" t="n">
         <v>337</v>
       </c>
-      <c r="B341" s="34">
+      <c r="B341" s="43">
         <f>Dashboard!$C$5+(337-1)/12</f>
         <v/>
       </c>
@@ -12096,10 +12908,10 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="33" t="n">
+      <c r="A342" s="42" t="n">
         <v>338</v>
       </c>
-      <c r="B342" s="34">
+      <c r="B342" s="43">
         <f>Dashboard!$C$5+(338-1)/12</f>
         <v/>
       </c>
@@ -12125,10 +12937,10 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="33" t="n">
+      <c r="A343" s="42" t="n">
         <v>339</v>
       </c>
-      <c r="B343" s="34">
+      <c r="B343" s="43">
         <f>Dashboard!$C$5+(339-1)/12</f>
         <v/>
       </c>
@@ -12154,10 +12966,10 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="33" t="n">
+      <c r="A344" s="42" t="n">
         <v>340</v>
       </c>
-      <c r="B344" s="34">
+      <c r="B344" s="43">
         <f>Dashboard!$C$5+(340-1)/12</f>
         <v/>
       </c>
@@ -12183,10 +12995,10 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="33" t="n">
+      <c r="A345" s="42" t="n">
         <v>341</v>
       </c>
-      <c r="B345" s="34">
+      <c r="B345" s="43">
         <f>Dashboard!$C$5+(341-1)/12</f>
         <v/>
       </c>
@@ -12212,10 +13024,10 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="33" t="n">
+      <c r="A346" s="42" t="n">
         <v>342</v>
       </c>
-      <c r="B346" s="34">
+      <c r="B346" s="43">
         <f>Dashboard!$C$5+(342-1)/12</f>
         <v/>
       </c>
@@ -12241,10 +13053,10 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="33" t="n">
+      <c r="A347" s="42" t="n">
         <v>343</v>
       </c>
-      <c r="B347" s="34">
+      <c r="B347" s="43">
         <f>Dashboard!$C$5+(343-1)/12</f>
         <v/>
       </c>
@@ -12270,10 +13082,10 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="33" t="n">
+      <c r="A348" s="42" t="n">
         <v>344</v>
       </c>
-      <c r="B348" s="34">
+      <c r="B348" s="43">
         <f>Dashboard!$C$5+(344-1)/12</f>
         <v/>
       </c>
@@ -12299,10 +13111,10 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="33" t="n">
+      <c r="A349" s="42" t="n">
         <v>345</v>
       </c>
-      <c r="B349" s="34">
+      <c r="B349" s="43">
         <f>Dashboard!$C$5+(345-1)/12</f>
         <v/>
       </c>
@@ -12328,10 +13140,10 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="33" t="n">
+      <c r="A350" s="42" t="n">
         <v>346</v>
       </c>
-      <c r="B350" s="34">
+      <c r="B350" s="43">
         <f>Dashboard!$C$5+(346-1)/12</f>
         <v/>
       </c>
@@ -12357,10 +13169,10 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="33" t="n">
+      <c r="A351" s="42" t="n">
         <v>347</v>
       </c>
-      <c r="B351" s="34">
+      <c r="B351" s="43">
         <f>Dashboard!$C$5+(347-1)/12</f>
         <v/>
       </c>
@@ -12386,10 +13198,10 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="33" t="n">
+      <c r="A352" s="42" t="n">
         <v>348</v>
       </c>
-      <c r="B352" s="34">
+      <c r="B352" s="43">
         <f>Dashboard!$C$5+(348-1)/12</f>
         <v/>
       </c>
@@ -12415,10 +13227,10 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="33" t="n">
+      <c r="A353" s="42" t="n">
         <v>349</v>
       </c>
-      <c r="B353" s="34">
+      <c r="B353" s="43">
         <f>Dashboard!$C$5+(349-1)/12</f>
         <v/>
       </c>
@@ -12444,10 +13256,10 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="33" t="n">
+      <c r="A354" s="42" t="n">
         <v>350</v>
       </c>
-      <c r="B354" s="34">
+      <c r="B354" s="43">
         <f>Dashboard!$C$5+(350-1)/12</f>
         <v/>
       </c>
@@ -12473,10 +13285,10 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="33" t="n">
+      <c r="A355" s="42" t="n">
         <v>351</v>
       </c>
-      <c r="B355" s="34">
+      <c r="B355" s="43">
         <f>Dashboard!$C$5+(351-1)/12</f>
         <v/>
       </c>
@@ -12502,10 +13314,10 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="33" t="n">
+      <c r="A356" s="42" t="n">
         <v>352</v>
       </c>
-      <c r="B356" s="34">
+      <c r="B356" s="43">
         <f>Dashboard!$C$5+(352-1)/12</f>
         <v/>
       </c>
@@ -12531,10 +13343,10 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="33" t="n">
+      <c r="A357" s="42" t="n">
         <v>353</v>
       </c>
-      <c r="B357" s="34">
+      <c r="B357" s="43">
         <f>Dashboard!$C$5+(353-1)/12</f>
         <v/>
       </c>
@@ -12560,10 +13372,10 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="33" t="n">
+      <c r="A358" s="42" t="n">
         <v>354</v>
       </c>
-      <c r="B358" s="34">
+      <c r="B358" s="43">
         <f>Dashboard!$C$5+(354-1)/12</f>
         <v/>
       </c>
@@ -12589,10 +13401,10 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="33" t="n">
+      <c r="A359" s="42" t="n">
         <v>355</v>
       </c>
-      <c r="B359" s="34">
+      <c r="B359" s="43">
         <f>Dashboard!$C$5+(355-1)/12</f>
         <v/>
       </c>
@@ -12618,10 +13430,10 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="33" t="n">
+      <c r="A360" s="42" t="n">
         <v>356</v>
       </c>
-      <c r="B360" s="34">
+      <c r="B360" s="43">
         <f>Dashboard!$C$5+(356-1)/12</f>
         <v/>
       </c>
@@ -12647,10 +13459,10 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="33" t="n">
+      <c r="A361" s="42" t="n">
         <v>357</v>
       </c>
-      <c r="B361" s="34">
+      <c r="B361" s="43">
         <f>Dashboard!$C$5+(357-1)/12</f>
         <v/>
       </c>
@@ -12676,10 +13488,10 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="33" t="n">
+      <c r="A362" s="42" t="n">
         <v>358</v>
       </c>
-      <c r="B362" s="34">
+      <c r="B362" s="43">
         <f>Dashboard!$C$5+(358-1)/12</f>
         <v/>
       </c>
@@ -12705,10 +13517,10 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="33" t="n">
+      <c r="A363" s="42" t="n">
         <v>359</v>
       </c>
-      <c r="B363" s="34">
+      <c r="B363" s="43">
         <f>Dashboard!$C$5+(359-1)/12</f>
         <v/>
       </c>
@@ -12734,10 +13546,10 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="33" t="n">
+      <c r="A364" s="42" t="n">
         <v>360</v>
       </c>
-      <c r="B364" s="34">
+      <c r="B364" s="43">
         <f>Dashboard!$C$5+(360-1)/12</f>
         <v/>
       </c>
@@ -12763,10 +13575,10 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="33" t="n">
+      <c r="A365" s="42" t="n">
         <v>361</v>
       </c>
-      <c r="B365" s="34">
+      <c r="B365" s="43">
         <f>Dashboard!$C$5+(361-1)/12</f>
         <v/>
       </c>
@@ -12792,10 +13604,10 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="33" t="n">
+      <c r="A366" s="42" t="n">
         <v>362</v>
       </c>
-      <c r="B366" s="34">
+      <c r="B366" s="43">
         <f>Dashboard!$C$5+(362-1)/12</f>
         <v/>
       </c>
@@ -12821,10 +13633,10 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="33" t="n">
+      <c r="A367" s="42" t="n">
         <v>363</v>
       </c>
-      <c r="B367" s="34">
+      <c r="B367" s="43">
         <f>Dashboard!$C$5+(363-1)/12</f>
         <v/>
       </c>
@@ -12850,10 +13662,10 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="33" t="n">
+      <c r="A368" s="42" t="n">
         <v>364</v>
       </c>
-      <c r="B368" s="34">
+      <c r="B368" s="43">
         <f>Dashboard!$C$5+(364-1)/12</f>
         <v/>
       </c>
@@ -12879,10 +13691,10 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="33" t="n">
+      <c r="A369" s="42" t="n">
         <v>365</v>
       </c>
-      <c r="B369" s="34">
+      <c r="B369" s="43">
         <f>Dashboard!$C$5+(365-1)/12</f>
         <v/>
       </c>
@@ -12908,10 +13720,10 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="33" t="n">
+      <c r="A370" s="42" t="n">
         <v>366</v>
       </c>
-      <c r="B370" s="34">
+      <c r="B370" s="43">
         <f>Dashboard!$C$5+(366-1)/12</f>
         <v/>
       </c>
@@ -12937,10 +13749,10 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="33" t="n">
+      <c r="A371" s="42" t="n">
         <v>367</v>
       </c>
-      <c r="B371" s="34">
+      <c r="B371" s="43">
         <f>Dashboard!$C$5+(367-1)/12</f>
         <v/>
       </c>
@@ -12966,10 +13778,10 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="33" t="n">
+      <c r="A372" s="42" t="n">
         <v>368</v>
       </c>
-      <c r="B372" s="34">
+      <c r="B372" s="43">
         <f>Dashboard!$C$5+(368-1)/12</f>
         <v/>
       </c>
@@ -12995,10 +13807,10 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="33" t="n">
+      <c r="A373" s="42" t="n">
         <v>369</v>
       </c>
-      <c r="B373" s="34">
+      <c r="B373" s="43">
         <f>Dashboard!$C$5+(369-1)/12</f>
         <v/>
       </c>
@@ -13024,10 +13836,10 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="33" t="n">
+      <c r="A374" s="42" t="n">
         <v>370</v>
       </c>
-      <c r="B374" s="34">
+      <c r="B374" s="43">
         <f>Dashboard!$C$5+(370-1)/12</f>
         <v/>
       </c>
@@ -13053,10 +13865,10 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="33" t="n">
+      <c r="A375" s="42" t="n">
         <v>371</v>
       </c>
-      <c r="B375" s="34">
+      <c r="B375" s="43">
         <f>Dashboard!$C$5+(371-1)/12</f>
         <v/>
       </c>
@@ -13082,10 +13894,10 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="33" t="n">
+      <c r="A376" s="42" t="n">
         <v>372</v>
       </c>
-      <c r="B376" s="34">
+      <c r="B376" s="43">
         <f>Dashboard!$C$5+(372-1)/12</f>
         <v/>
       </c>
@@ -13111,10 +13923,10 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="33" t="n">
+      <c r="A377" s="42" t="n">
         <v>373</v>
       </c>
-      <c r="B377" s="34">
+      <c r="B377" s="43">
         <f>Dashboard!$C$5+(373-1)/12</f>
         <v/>
       </c>
@@ -13140,10 +13952,10 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="33" t="n">
+      <c r="A378" s="42" t="n">
         <v>374</v>
       </c>
-      <c r="B378" s="34">
+      <c r="B378" s="43">
         <f>Dashboard!$C$5+(374-1)/12</f>
         <v/>
       </c>
@@ -13169,10 +13981,10 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="33" t="n">
+      <c r="A379" s="42" t="n">
         <v>375</v>
       </c>
-      <c r="B379" s="34">
+      <c r="B379" s="43">
         <f>Dashboard!$C$5+(375-1)/12</f>
         <v/>
       </c>
@@ -13198,10 +14010,10 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="33" t="n">
+      <c r="A380" s="42" t="n">
         <v>376</v>
       </c>
-      <c r="B380" s="34">
+      <c r="B380" s="43">
         <f>Dashboard!$C$5+(376-1)/12</f>
         <v/>
       </c>
@@ -13227,10 +14039,10 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="33" t="n">
+      <c r="A381" s="42" t="n">
         <v>377</v>
       </c>
-      <c r="B381" s="34">
+      <c r="B381" s="43">
         <f>Dashboard!$C$5+(377-1)/12</f>
         <v/>
       </c>
@@ -13256,10 +14068,10 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="33" t="n">
+      <c r="A382" s="42" t="n">
         <v>378</v>
       </c>
-      <c r="B382" s="34">
+      <c r="B382" s="43">
         <f>Dashboard!$C$5+(378-1)/12</f>
         <v/>
       </c>
@@ -13285,10 +14097,10 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="33" t="n">
+      <c r="A383" s="42" t="n">
         <v>379</v>
       </c>
-      <c r="B383" s="34">
+      <c r="B383" s="43">
         <f>Dashboard!$C$5+(379-1)/12</f>
         <v/>
       </c>
@@ -13314,10 +14126,10 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="33" t="n">
+      <c r="A384" s="42" t="n">
         <v>380</v>
       </c>
-      <c r="B384" s="34">
+      <c r="B384" s="43">
         <f>Dashboard!$C$5+(380-1)/12</f>
         <v/>
       </c>
@@ -13343,10 +14155,10 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="33" t="n">
+      <c r="A385" s="42" t="n">
         <v>381</v>
       </c>
-      <c r="B385" s="34">
+      <c r="B385" s="43">
         <f>Dashboard!$C$5+(381-1)/12</f>
         <v/>
       </c>
@@ -13372,10 +14184,10 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="33" t="n">
+      <c r="A386" s="42" t="n">
         <v>382</v>
       </c>
-      <c r="B386" s="34">
+      <c r="B386" s="43">
         <f>Dashboard!$C$5+(382-1)/12</f>
         <v/>
       </c>
@@ -13401,10 +14213,10 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="33" t="n">
+      <c r="A387" s="42" t="n">
         <v>383</v>
       </c>
-      <c r="B387" s="34">
+      <c r="B387" s="43">
         <f>Dashboard!$C$5+(383-1)/12</f>
         <v/>
       </c>
@@ -13430,10 +14242,10 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="33" t="n">
+      <c r="A388" s="42" t="n">
         <v>384</v>
       </c>
-      <c r="B388" s="34">
+      <c r="B388" s="43">
         <f>Dashboard!$C$5+(384-1)/12</f>
         <v/>
       </c>
@@ -13459,10 +14271,10 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="33" t="n">
+      <c r="A389" s="42" t="n">
         <v>385</v>
       </c>
-      <c r="B389" s="34">
+      <c r="B389" s="43">
         <f>Dashboard!$C$5+(385-1)/12</f>
         <v/>
       </c>
@@ -13488,10 +14300,10 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="33" t="n">
+      <c r="A390" s="42" t="n">
         <v>386</v>
       </c>
-      <c r="B390" s="34">
+      <c r="B390" s="43">
         <f>Dashboard!$C$5+(386-1)/12</f>
         <v/>
       </c>
@@ -13517,10 +14329,10 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="33" t="n">
+      <c r="A391" s="42" t="n">
         <v>387</v>
       </c>
-      <c r="B391" s="34">
+      <c r="B391" s="43">
         <f>Dashboard!$C$5+(387-1)/12</f>
         <v/>
       </c>
@@ -13546,10 +14358,10 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="33" t="n">
+      <c r="A392" s="42" t="n">
         <v>388</v>
       </c>
-      <c r="B392" s="34">
+      <c r="B392" s="43">
         <f>Dashboard!$C$5+(388-1)/12</f>
         <v/>
       </c>
@@ -13575,10 +14387,10 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="33" t="n">
+      <c r="A393" s="42" t="n">
         <v>389</v>
       </c>
-      <c r="B393" s="34">
+      <c r="B393" s="43">
         <f>Dashboard!$C$5+(389-1)/12</f>
         <v/>
       </c>
@@ -13604,10 +14416,10 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="33" t="n">
+      <c r="A394" s="42" t="n">
         <v>390</v>
       </c>
-      <c r="B394" s="34">
+      <c r="B394" s="43">
         <f>Dashboard!$C$5+(390-1)/12</f>
         <v/>
       </c>
@@ -13633,10 +14445,10 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="33" t="n">
+      <c r="A395" s="42" t="n">
         <v>391</v>
       </c>
-      <c r="B395" s="34">
+      <c r="B395" s="43">
         <f>Dashboard!$C$5+(391-1)/12</f>
         <v/>
       </c>
@@ -13662,10 +14474,10 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="33" t="n">
+      <c r="A396" s="42" t="n">
         <v>392</v>
       </c>
-      <c r="B396" s="34">
+      <c r="B396" s="43">
         <f>Dashboard!$C$5+(392-1)/12</f>
         <v/>
       </c>
@@ -13691,10 +14503,10 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="33" t="n">
+      <c r="A397" s="42" t="n">
         <v>393</v>
       </c>
-      <c r="B397" s="34">
+      <c r="B397" s="43">
         <f>Dashboard!$C$5+(393-1)/12</f>
         <v/>
       </c>
@@ -13720,10 +14532,10 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="33" t="n">
+      <c r="A398" s="42" t="n">
         <v>394</v>
       </c>
-      <c r="B398" s="34">
+      <c r="B398" s="43">
         <f>Dashboard!$C$5+(394-1)/12</f>
         <v/>
       </c>
@@ -13749,10 +14561,10 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="33" t="n">
+      <c r="A399" s="42" t="n">
         <v>395</v>
       </c>
-      <c r="B399" s="34">
+      <c r="B399" s="43">
         <f>Dashboard!$C$5+(395-1)/12</f>
         <v/>
       </c>
@@ -13778,10 +14590,10 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="33" t="n">
+      <c r="A400" s="42" t="n">
         <v>396</v>
       </c>
-      <c r="B400" s="34">
+      <c r="B400" s="43">
         <f>Dashboard!$C$5+(396-1)/12</f>
         <v/>
       </c>
@@ -13807,10 +14619,10 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="33" t="n">
+      <c r="A401" s="42" t="n">
         <v>397</v>
       </c>
-      <c r="B401" s="34">
+      <c r="B401" s="43">
         <f>Dashboard!$C$5+(397-1)/12</f>
         <v/>
       </c>
@@ -13836,10 +14648,10 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="33" t="n">
+      <c r="A402" s="42" t="n">
         <v>398</v>
       </c>
-      <c r="B402" s="34">
+      <c r="B402" s="43">
         <f>Dashboard!$C$5+(398-1)/12</f>
         <v/>
       </c>
@@ -13865,10 +14677,10 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="33" t="n">
+      <c r="A403" s="42" t="n">
         <v>399</v>
       </c>
-      <c r="B403" s="34">
+      <c r="B403" s="43">
         <f>Dashboard!$C$5+(399-1)/12</f>
         <v/>
       </c>
@@ -13894,10 +14706,10 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="33" t="n">
+      <c r="A404" s="42" t="n">
         <v>400</v>
       </c>
-      <c r="B404" s="34">
+      <c r="B404" s="43">
         <f>Dashboard!$C$5+(400-1)/12</f>
         <v/>
       </c>
@@ -13923,10 +14735,10 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="33" t="n">
+      <c r="A405" s="42" t="n">
         <v>401</v>
       </c>
-      <c r="B405" s="34">
+      <c r="B405" s="43">
         <f>Dashboard!$C$5+(401-1)/12</f>
         <v/>
       </c>
@@ -13952,10 +14764,10 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="33" t="n">
+      <c r="A406" s="42" t="n">
         <v>402</v>
       </c>
-      <c r="B406" s="34">
+      <c r="B406" s="43">
         <f>Dashboard!$C$5+(402-1)/12</f>
         <v/>
       </c>
@@ -13981,10 +14793,10 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="33" t="n">
+      <c r="A407" s="42" t="n">
         <v>403</v>
       </c>
-      <c r="B407" s="34">
+      <c r="B407" s="43">
         <f>Dashboard!$C$5+(403-1)/12</f>
         <v/>
       </c>
@@ -14010,10 +14822,10 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="33" t="n">
+      <c r="A408" s="42" t="n">
         <v>404</v>
       </c>
-      <c r="B408" s="34">
+      <c r="B408" s="43">
         <f>Dashboard!$C$5+(404-1)/12</f>
         <v/>
       </c>
@@ -14039,10 +14851,10 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="33" t="n">
+      <c r="A409" s="42" t="n">
         <v>405</v>
       </c>
-      <c r="B409" s="34">
+      <c r="B409" s="43">
         <f>Dashboard!$C$5+(405-1)/12</f>
         <v/>
       </c>
@@ -14068,10 +14880,10 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="33" t="n">
+      <c r="A410" s="42" t="n">
         <v>406</v>
       </c>
-      <c r="B410" s="34">
+      <c r="B410" s="43">
         <f>Dashboard!$C$5+(406-1)/12</f>
         <v/>
       </c>
@@ -14097,10 +14909,10 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="33" t="n">
+      <c r="A411" s="42" t="n">
         <v>407</v>
       </c>
-      <c r="B411" s="34">
+      <c r="B411" s="43">
         <f>Dashboard!$C$5+(407-1)/12</f>
         <v/>
       </c>
@@ -14126,10 +14938,10 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="33" t="n">
+      <c r="A412" s="42" t="n">
         <v>408</v>
       </c>
-      <c r="B412" s="34">
+      <c r="B412" s="43">
         <f>Dashboard!$C$5+(408-1)/12</f>
         <v/>
       </c>
@@ -14155,10 +14967,10 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="33" t="n">
+      <c r="A413" s="42" t="n">
         <v>409</v>
       </c>
-      <c r="B413" s="34">
+      <c r="B413" s="43">
         <f>Dashboard!$C$5+(409-1)/12</f>
         <v/>
       </c>
@@ -14184,10 +14996,10 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="33" t="n">
+      <c r="A414" s="42" t="n">
         <v>410</v>
       </c>
-      <c r="B414" s="34">
+      <c r="B414" s="43">
         <f>Dashboard!$C$5+(410-1)/12</f>
         <v/>
       </c>
@@ -14213,10 +15025,10 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="33" t="n">
+      <c r="A415" s="42" t="n">
         <v>411</v>
       </c>
-      <c r="B415" s="34">
+      <c r="B415" s="43">
         <f>Dashboard!$C$5+(411-1)/12</f>
         <v/>
       </c>
@@ -14242,10 +15054,10 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="33" t="n">
+      <c r="A416" s="42" t="n">
         <v>412</v>
       </c>
-      <c r="B416" s="34">
+      <c r="B416" s="43">
         <f>Dashboard!$C$5+(412-1)/12</f>
         <v/>
       </c>
@@ -14271,10 +15083,10 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="33" t="n">
+      <c r="A417" s="42" t="n">
         <v>413</v>
       </c>
-      <c r="B417" s="34">
+      <c r="B417" s="43">
         <f>Dashboard!$C$5+(413-1)/12</f>
         <v/>
       </c>
@@ -14300,10 +15112,10 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="33" t="n">
+      <c r="A418" s="42" t="n">
         <v>414</v>
       </c>
-      <c r="B418" s="34">
+      <c r="B418" s="43">
         <f>Dashboard!$C$5+(414-1)/12</f>
         <v/>
       </c>
@@ -14329,10 +15141,10 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="33" t="n">
+      <c r="A419" s="42" t="n">
         <v>415</v>
       </c>
-      <c r="B419" s="34">
+      <c r="B419" s="43">
         <f>Dashboard!$C$5+(415-1)/12</f>
         <v/>
       </c>
@@ -14358,10 +15170,10 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="33" t="n">
+      <c r="A420" s="42" t="n">
         <v>416</v>
       </c>
-      <c r="B420" s="34">
+      <c r="B420" s="43">
         <f>Dashboard!$C$5+(416-1)/12</f>
         <v/>
       </c>
@@ -14387,10 +15199,10 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="33" t="n">
+      <c r="A421" s="42" t="n">
         <v>417</v>
       </c>
-      <c r="B421" s="34">
+      <c r="B421" s="43">
         <f>Dashboard!$C$5+(417-1)/12</f>
         <v/>
       </c>
@@ -14416,10 +15228,10 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="33" t="n">
+      <c r="A422" s="42" t="n">
         <v>418</v>
       </c>
-      <c r="B422" s="34">
+      <c r="B422" s="43">
         <f>Dashboard!$C$5+(418-1)/12</f>
         <v/>
       </c>
@@ -14445,10 +15257,10 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="33" t="n">
+      <c r="A423" s="42" t="n">
         <v>419</v>
       </c>
-      <c r="B423" s="34">
+      <c r="B423" s="43">
         <f>Dashboard!$C$5+(419-1)/12</f>
         <v/>
       </c>
@@ -14474,10 +15286,10 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="33" t="n">
+      <c r="A424" s="42" t="n">
         <v>420</v>
       </c>
-      <c r="B424" s="34">
+      <c r="B424" s="43">
         <f>Dashboard!$C$5+(420-1)/12</f>
         <v/>
       </c>
@@ -14503,10 +15315,10 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="33" t="n">
+      <c r="A425" s="42" t="n">
         <v>421</v>
       </c>
-      <c r="B425" s="34">
+      <c r="B425" s="43">
         <f>Dashboard!$C$5+(421-1)/12</f>
         <v/>
       </c>
@@ -14532,10 +15344,10 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="33" t="n">
+      <c r="A426" s="42" t="n">
         <v>422</v>
       </c>
-      <c r="B426" s="34">
+      <c r="B426" s="43">
         <f>Dashboard!$C$5+(422-1)/12</f>
         <v/>
       </c>
@@ -14561,10 +15373,10 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="33" t="n">
+      <c r="A427" s="42" t="n">
         <v>423</v>
       </c>
-      <c r="B427" s="34">
+      <c r="B427" s="43">
         <f>Dashboard!$C$5+(423-1)/12</f>
         <v/>
       </c>
@@ -14590,10 +15402,10 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="33" t="n">
+      <c r="A428" s="42" t="n">
         <v>424</v>
       </c>
-      <c r="B428" s="34">
+      <c r="B428" s="43">
         <f>Dashboard!$C$5+(424-1)/12</f>
         <v/>
       </c>
@@ -14619,10 +15431,10 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="33" t="n">
+      <c r="A429" s="42" t="n">
         <v>425</v>
       </c>
-      <c r="B429" s="34">
+      <c r="B429" s="43">
         <f>Dashboard!$C$5+(425-1)/12</f>
         <v/>
       </c>
@@ -14648,10 +15460,10 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="33" t="n">
+      <c r="A430" s="42" t="n">
         <v>426</v>
       </c>
-      <c r="B430" s="34">
+      <c r="B430" s="43">
         <f>Dashboard!$C$5+(426-1)/12</f>
         <v/>
       </c>
@@ -14677,10 +15489,10 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="33" t="n">
+      <c r="A431" s="42" t="n">
         <v>427</v>
       </c>
-      <c r="B431" s="34">
+      <c r="B431" s="43">
         <f>Dashboard!$C$5+(427-1)/12</f>
         <v/>
       </c>
@@ -14706,10 +15518,10 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="33" t="n">
+      <c r="A432" s="42" t="n">
         <v>428</v>
       </c>
-      <c r="B432" s="34">
+      <c r="B432" s="43">
         <f>Dashboard!$C$5+(428-1)/12</f>
         <v/>
       </c>
@@ -14735,10 +15547,10 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="33" t="n">
+      <c r="A433" s="42" t="n">
         <v>429</v>
       </c>
-      <c r="B433" s="34">
+      <c r="B433" s="43">
         <f>Dashboard!$C$5+(429-1)/12</f>
         <v/>
       </c>
@@ -14764,10 +15576,10 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="33" t="n">
+      <c r="A434" s="42" t="n">
         <v>430</v>
       </c>
-      <c r="B434" s="34">
+      <c r="B434" s="43">
         <f>Dashboard!$C$5+(430-1)/12</f>
         <v/>
       </c>
@@ -14793,10 +15605,10 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="33" t="n">
+      <c r="A435" s="42" t="n">
         <v>431</v>
       </c>
-      <c r="B435" s="34">
+      <c r="B435" s="43">
         <f>Dashboard!$C$5+(431-1)/12</f>
         <v/>
       </c>
@@ -14822,10 +15634,10 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="33" t="n">
+      <c r="A436" s="42" t="n">
         <v>432</v>
       </c>
-      <c r="B436" s="34">
+      <c r="B436" s="43">
         <f>Dashboard!$C$5+(432-1)/12</f>
         <v/>
       </c>
@@ -14851,10 +15663,10 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="33" t="n">
+      <c r="A437" s="42" t="n">
         <v>433</v>
       </c>
-      <c r="B437" s="34">
+      <c r="B437" s="43">
         <f>Dashboard!$C$5+(433-1)/12</f>
         <v/>
       </c>
@@ -14880,10 +15692,10 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="33" t="n">
+      <c r="A438" s="42" t="n">
         <v>434</v>
       </c>
-      <c r="B438" s="34">
+      <c r="B438" s="43">
         <f>Dashboard!$C$5+(434-1)/12</f>
         <v/>
       </c>
@@ -14909,10 +15721,10 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="33" t="n">
+      <c r="A439" s="42" t="n">
         <v>435</v>
       </c>
-      <c r="B439" s="34">
+      <c r="B439" s="43">
         <f>Dashboard!$C$5+(435-1)/12</f>
         <v/>
       </c>
@@ -14938,10 +15750,10 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="33" t="n">
+      <c r="A440" s="42" t="n">
         <v>436</v>
       </c>
-      <c r="B440" s="34">
+      <c r="B440" s="43">
         <f>Dashboard!$C$5+(436-1)/12</f>
         <v/>
       </c>
@@ -14967,10 +15779,10 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="33" t="n">
+      <c r="A441" s="42" t="n">
         <v>437</v>
       </c>
-      <c r="B441" s="34">
+      <c r="B441" s="43">
         <f>Dashboard!$C$5+(437-1)/12</f>
         <v/>
       </c>
@@ -14996,10 +15808,10 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="33" t="n">
+      <c r="A442" s="42" t="n">
         <v>438</v>
       </c>
-      <c r="B442" s="34">
+      <c r="B442" s="43">
         <f>Dashboard!$C$5+(438-1)/12</f>
         <v/>
       </c>
@@ -15025,10 +15837,10 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="33" t="n">
+      <c r="A443" s="42" t="n">
         <v>439</v>
       </c>
-      <c r="B443" s="34">
+      <c r="B443" s="43">
         <f>Dashboard!$C$5+(439-1)/12</f>
         <v/>
       </c>
@@ -15054,10 +15866,10 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="33" t="n">
+      <c r="A444" s="42" t="n">
         <v>440</v>
       </c>
-      <c r="B444" s="34">
+      <c r="B444" s="43">
         <f>Dashboard!$C$5+(440-1)/12</f>
         <v/>
       </c>
@@ -15083,10 +15895,10 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="33" t="n">
+      <c r="A445" s="42" t="n">
         <v>441</v>
       </c>
-      <c r="B445" s="34">
+      <c r="B445" s="43">
         <f>Dashboard!$C$5+(441-1)/12</f>
         <v/>
       </c>
@@ -15112,10 +15924,10 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="33" t="n">
+      <c r="A446" s="42" t="n">
         <v>442</v>
       </c>
-      <c r="B446" s="34">
+      <c r="B446" s="43">
         <f>Dashboard!$C$5+(442-1)/12</f>
         <v/>
       </c>
@@ -15141,10 +15953,10 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="33" t="n">
+      <c r="A447" s="42" t="n">
         <v>443</v>
       </c>
-      <c r="B447" s="34">
+      <c r="B447" s="43">
         <f>Dashboard!$C$5+(443-1)/12</f>
         <v/>
       </c>
@@ -15170,10 +15982,10 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="33" t="n">
+      <c r="A448" s="42" t="n">
         <v>444</v>
       </c>
-      <c r="B448" s="34">
+      <c r="B448" s="43">
         <f>Dashboard!$C$5+(444-1)/12</f>
         <v/>
       </c>
@@ -15199,10 +16011,10 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="33" t="n">
+      <c r="A449" s="42" t="n">
         <v>445</v>
       </c>
-      <c r="B449" s="34">
+      <c r="B449" s="43">
         <f>Dashboard!$C$5+(445-1)/12</f>
         <v/>
       </c>
@@ -15228,10 +16040,10 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="33" t="n">
+      <c r="A450" s="42" t="n">
         <v>446</v>
       </c>
-      <c r="B450" s="34">
+      <c r="B450" s="43">
         <f>Dashboard!$C$5+(446-1)/12</f>
         <v/>
       </c>
@@ -15257,10 +16069,10 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="33" t="n">
+      <c r="A451" s="42" t="n">
         <v>447</v>
       </c>
-      <c r="B451" s="34">
+      <c r="B451" s="43">
         <f>Dashboard!$C$5+(447-1)/12</f>
         <v/>
       </c>
@@ -15286,10 +16098,10 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="33" t="n">
+      <c r="A452" s="42" t="n">
         <v>448</v>
       </c>
-      <c r="B452" s="34">
+      <c r="B452" s="43">
         <f>Dashboard!$C$5+(448-1)/12</f>
         <v/>
       </c>
@@ -15315,10 +16127,10 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="33" t="n">
+      <c r="A453" s="42" t="n">
         <v>449</v>
       </c>
-      <c r="B453" s="34">
+      <c r="B453" s="43">
         <f>Dashboard!$C$5+(449-1)/12</f>
         <v/>
       </c>
@@ -15344,10 +16156,10 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="33" t="n">
+      <c r="A454" s="42" t="n">
         <v>450</v>
       </c>
-      <c r="B454" s="34">
+      <c r="B454" s="43">
         <f>Dashboard!$C$5+(450-1)/12</f>
         <v/>
       </c>
@@ -15373,10 +16185,10 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="33" t="n">
+      <c r="A455" s="42" t="n">
         <v>451</v>
       </c>
-      <c r="B455" s="34">
+      <c r="B455" s="43">
         <f>Dashboard!$C$5+(451-1)/12</f>
         <v/>
       </c>
@@ -15402,10 +16214,10 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="33" t="n">
+      <c r="A456" s="42" t="n">
         <v>452</v>
       </c>
-      <c r="B456" s="34">
+      <c r="B456" s="43">
         <f>Dashboard!$C$5+(452-1)/12</f>
         <v/>
       </c>
@@ -15431,10 +16243,10 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="33" t="n">
+      <c r="A457" s="42" t="n">
         <v>453</v>
       </c>
-      <c r="B457" s="34">
+      <c r="B457" s="43">
         <f>Dashboard!$C$5+(453-1)/12</f>
         <v/>
       </c>
@@ -15460,10 +16272,10 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="33" t="n">
+      <c r="A458" s="42" t="n">
         <v>454</v>
       </c>
-      <c r="B458" s="34">
+      <c r="B458" s="43">
         <f>Dashboard!$C$5+(454-1)/12</f>
         <v/>
       </c>
@@ -15489,10 +16301,10 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="33" t="n">
+      <c r="A459" s="42" t="n">
         <v>455</v>
       </c>
-      <c r="B459" s="34">
+      <c r="B459" s="43">
         <f>Dashboard!$C$5+(455-1)/12</f>
         <v/>
       </c>
@@ -15518,10 +16330,10 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="33" t="n">
+      <c r="A460" s="42" t="n">
         <v>456</v>
       </c>
-      <c r="B460" s="34">
+      <c r="B460" s="43">
         <f>Dashboard!$C$5+(456-1)/12</f>
         <v/>
       </c>
@@ -15547,10 +16359,10 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="33" t="n">
+      <c r="A461" s="42" t="n">
         <v>457</v>
       </c>
-      <c r="B461" s="34">
+      <c r="B461" s="43">
         <f>Dashboard!$C$5+(457-1)/12</f>
         <v/>
       </c>
@@ -15576,10 +16388,10 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="33" t="n">
+      <c r="A462" s="42" t="n">
         <v>458</v>
       </c>
-      <c r="B462" s="34">
+      <c r="B462" s="43">
         <f>Dashboard!$C$5+(458-1)/12</f>
         <v/>
       </c>
@@ -15605,10 +16417,10 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="33" t="n">
+      <c r="A463" s="42" t="n">
         <v>459</v>
       </c>
-      <c r="B463" s="34">
+      <c r="B463" s="43">
         <f>Dashboard!$C$5+(459-1)/12</f>
         <v/>
       </c>
@@ -15634,10 +16446,10 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="33" t="n">
+      <c r="A464" s="42" t="n">
         <v>460</v>
       </c>
-      <c r="B464" s="34">
+      <c r="B464" s="43">
         <f>Dashboard!$C$5+(460-1)/12</f>
         <v/>
       </c>
@@ -15663,10 +16475,10 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="33" t="n">
+      <c r="A465" s="42" t="n">
         <v>461</v>
       </c>
-      <c r="B465" s="34">
+      <c r="B465" s="43">
         <f>Dashboard!$C$5+(461-1)/12</f>
         <v/>
       </c>
@@ -15692,10 +16504,10 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="33" t="n">
+      <c r="A466" s="42" t="n">
         <v>462</v>
       </c>
-      <c r="B466" s="34">
+      <c r="B466" s="43">
         <f>Dashboard!$C$5+(462-1)/12</f>
         <v/>
       </c>
@@ -15721,10 +16533,10 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="33" t="n">
+      <c r="A467" s="42" t="n">
         <v>463</v>
       </c>
-      <c r="B467" s="34">
+      <c r="B467" s="43">
         <f>Dashboard!$C$5+(463-1)/12</f>
         <v/>
       </c>
@@ -15750,10 +16562,10 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="33" t="n">
+      <c r="A468" s="42" t="n">
         <v>464</v>
       </c>
-      <c r="B468" s="34">
+      <c r="B468" s="43">
         <f>Dashboard!$C$5+(464-1)/12</f>
         <v/>
       </c>
@@ -15779,10 +16591,10 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="33" t="n">
+      <c r="A469" s="42" t="n">
         <v>465</v>
       </c>
-      <c r="B469" s="34">
+      <c r="B469" s="43">
         <f>Dashboard!$C$5+(465-1)/12</f>
         <v/>
       </c>
@@ -15808,10 +16620,10 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="33" t="n">
+      <c r="A470" s="42" t="n">
         <v>466</v>
       </c>
-      <c r="B470" s="34">
+      <c r="B470" s="43">
         <f>Dashboard!$C$5+(466-1)/12</f>
         <v/>
       </c>
@@ -15837,10 +16649,10 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="33" t="n">
+      <c r="A471" s="42" t="n">
         <v>467</v>
       </c>
-      <c r="B471" s="34">
+      <c r="B471" s="43">
         <f>Dashboard!$C$5+(467-1)/12</f>
         <v/>
       </c>
@@ -15866,10 +16678,10 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="33" t="n">
+      <c r="A472" s="42" t="n">
         <v>468</v>
       </c>
-      <c r="B472" s="34">
+      <c r="B472" s="43">
         <f>Dashboard!$C$5+(468-1)/12</f>
         <v/>
       </c>
@@ -15895,10 +16707,10 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="33" t="n">
+      <c r="A473" s="42" t="n">
         <v>469</v>
       </c>
-      <c r="B473" s="34">
+      <c r="B473" s="43">
         <f>Dashboard!$C$5+(469-1)/12</f>
         <v/>
       </c>
@@ -15924,10 +16736,10 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="33" t="n">
+      <c r="A474" s="42" t="n">
         <v>470</v>
       </c>
-      <c r="B474" s="34">
+      <c r="B474" s="43">
         <f>Dashboard!$C$5+(470-1)/12</f>
         <v/>
       </c>
@@ -15953,10 +16765,10 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="33" t="n">
+      <c r="A475" s="42" t="n">
         <v>471</v>
       </c>
-      <c r="B475" s="34">
+      <c r="B475" s="43">
         <f>Dashboard!$C$5+(471-1)/12</f>
         <v/>
       </c>
@@ -15982,10 +16794,10 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="33" t="n">
+      <c r="A476" s="42" t="n">
         <v>472</v>
       </c>
-      <c r="B476" s="34">
+      <c r="B476" s="43">
         <f>Dashboard!$C$5+(472-1)/12</f>
         <v/>
       </c>
@@ -16011,10 +16823,10 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="33" t="n">
+      <c r="A477" s="42" t="n">
         <v>473</v>
       </c>
-      <c r="B477" s="34">
+      <c r="B477" s="43">
         <f>Dashboard!$C$5+(473-1)/12</f>
         <v/>
       </c>
@@ -16040,10 +16852,10 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="33" t="n">
+      <c r="A478" s="42" t="n">
         <v>474</v>
       </c>
-      <c r="B478" s="34">
+      <c r="B478" s="43">
         <f>Dashboard!$C$5+(474-1)/12</f>
         <v/>
       </c>
@@ -16069,10 +16881,10 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="33" t="n">
+      <c r="A479" s="42" t="n">
         <v>475</v>
       </c>
-      <c r="B479" s="34">
+      <c r="B479" s="43">
         <f>Dashboard!$C$5+(475-1)/12</f>
         <v/>
       </c>
@@ -16098,10 +16910,10 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="33" t="n">
+      <c r="A480" s="42" t="n">
         <v>476</v>
       </c>
-      <c r="B480" s="34">
+      <c r="B480" s="43">
         <f>Dashboard!$C$5+(476-1)/12</f>
         <v/>
       </c>
@@ -16127,10 +16939,10 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="33" t="n">
+      <c r="A481" s="42" t="n">
         <v>477</v>
       </c>
-      <c r="B481" s="34">
+      <c r="B481" s="43">
         <f>Dashboard!$C$5+(477-1)/12</f>
         <v/>
       </c>
@@ -16156,10 +16968,10 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="33" t="n">
+      <c r="A482" s="42" t="n">
         <v>478</v>
       </c>
-      <c r="B482" s="34">
+      <c r="B482" s="43">
         <f>Dashboard!$C$5+(478-1)/12</f>
         <v/>
       </c>
@@ -16185,10 +16997,10 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="33" t="n">
+      <c r="A483" s="42" t="n">
         <v>479</v>
       </c>
-      <c r="B483" s="34">
+      <c r="B483" s="43">
         <f>Dashboard!$C$5+(479-1)/12</f>
         <v/>
       </c>
@@ -16214,10 +17026,10 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="33" t="n">
+      <c r="A484" s="42" t="n">
         <v>480</v>
       </c>
-      <c r="B484" s="34">
+      <c r="B484" s="43">
         <f>Dashboard!$C$5+(480-1)/12</f>
         <v/>
       </c>
@@ -16247,7 +17059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00FFC000"/>
@@ -16268,7 +17080,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>Advanced Settings</t>
         </is>
@@ -16294,22 +17106,22 @@
       <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>Reflation</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>Stagflation</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>Deflation</t>
         </is>
@@ -16337,7 +17149,7 @@
         <f>SUM(B6:E6)</f>
         <v/>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="45">
         <f>IF(ABS(F6-1)&gt;0.005,"← must sum to 100%","")</f>
         <v/>
       </c>
@@ -16358,7 +17170,7 @@
           <t>Horizon (years, from Dashboard ages)</t>
         </is>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="46">
         <f>Dashboard!$C$6-Dashboard!$C$5</f>
         <v/>
       </c>
@@ -16389,183 +17201,183 @@
       <c r="H11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>Mean monthly</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="D12" s="38" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>Monthly sd</t>
         </is>
       </c>
-      <c r="E12" s="38" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>Annual sd</t>
         </is>
       </c>
-      <c r="F12" s="38" t="inlineStr">
+      <c r="F12" s="35" t="inlineStr">
         <is>
           <t>S.E. (avg, horizon)</t>
         </is>
       </c>
-      <c r="G12" s="38" t="inlineStr">
+      <c r="G12" s="35" t="inlineStr">
         <is>
           <t>Low monthly</t>
         </is>
       </c>
-      <c r="H12" s="38" t="inlineStr">
+      <c r="H12" s="35" t="inlineStr">
         <is>
           <t>High monthly</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>CONS</t>
         </is>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="36">
         <f>(SUMPRODUCT($B$6:$E$6,Data!$B$6:$E$6)-$B$8/10000/12)*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="48">
         <f>(1+B13)^12-1</f>
         <v/>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="36">
         <f>SUMPRODUCT($B$6:$E$6,Data!$B$13:$E$13)</f>
         <v/>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="48">
         <f>D13*SQRT(12)</f>
         <v/>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="48">
         <f>E13/SQRT(MAX(1,$B$9))</f>
         <v/>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="36">
         <f>(1+C13-F13)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="H13" s="40">
+      <c r="H13" s="36">
         <f>(1+C13+F13)^(1/12)-1</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="B14" s="40">
+      <c r="B14" s="36">
         <f>(SUMPRODUCT($B$6:$E$6,Data!$B$7:$E$7)-$B$8/10000/12)*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="48">
         <f>(1+B14)^12-1</f>
         <v/>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="36">
         <f>SUMPRODUCT($B$6:$E$6,Data!$B$14:$E$14)</f>
         <v/>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="48">
         <f>D14*SQRT(12)</f>
         <v/>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="48">
         <f>E14/SQRT(MAX(1,$B$9))</f>
         <v/>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="36">
         <f>(1+C14-F14)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="H14" s="40">
+      <c r="H14" s="36">
         <f>(1+C14+F14)^(1/12)-1</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>AGG</t>
         </is>
       </c>
-      <c r="B15" s="40">
+      <c r="B15" s="36">
         <f>(SUMPRODUCT($B$6:$E$6,Data!$B$8:$E$8)-$B$8/10000/12)*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="48">
         <f>(1+B15)^12-1</f>
         <v/>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="36">
         <f>SUMPRODUCT($B$6:$E$6,Data!$B$15:$E$15)</f>
         <v/>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="48">
         <f>D15*SQRT(12)</f>
         <v/>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="48">
         <f>E15/SQRT(MAX(1,$B$9))</f>
         <v/>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="36">
         <f>(1+C15-F15)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="H15" s="40">
+      <c r="H15" s="36">
         <f>(1+C15+F15)^(1/12)-1</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>VAGG</t>
         </is>
       </c>
-      <c r="B16" s="40">
+      <c r="B16" s="36">
         <f>(SUMPRODUCT($B$6:$E$6,Data!$B$9:$E$9)-$B$8/10000/12)*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="48">
         <f>(1+B16)^12-1</f>
         <v/>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="36">
         <f>SUMPRODUCT($B$6:$E$6,Data!$B$16:$E$16)</f>
         <v/>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="48">
         <f>D16*SQRT(12)</f>
         <v/>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="48">
         <f>E16/SQRT(MAX(1,$B$9))</f>
         <v/>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="36">
         <f>(1+C16-F16)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="H16" s="40">
+      <c r="H16" s="36">
         <f>(1+C16+F16)^(1/12)-1</f>
         <v/>
       </c>
@@ -16585,7 +17397,7 @@
           <t>Year 1</t>
         </is>
       </c>
-      <c r="B19" s="42">
+      <c r="B19" s="49">
         <f>Dashboard!$C$8</f>
         <v/>
       </c>
@@ -16993,7 +17805,7 @@
           <t>Implied contribution growth, monthly (yr1 → horizon)</t>
         </is>
       </c>
-      <c r="B60" s="43">
+      <c r="B60" s="50">
         <f>(INDEX($B$19:$B$58,MIN(40,MAX(1,$B$9)))/Dashboard!$C$8)^(1/MAX(1,(MIN(40,$B$9)-1)*12))-1</f>
         <v/>
       </c>
@@ -17003,7 +17815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -17021,7 +17833,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="51" t="inlineStr">
         <is>
           <t>Model Data — per-regime return statistics (v2 rotation backtest, Jun 2007–Aug 2026)</t>
         </is>
@@ -17046,100 +17858,100 @@
       <c r="E4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>Reflation</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>Stagflation</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>Deflation</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>CONS</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="52" t="n">
         <v>0.00731</v>
       </c>
-      <c r="C6" s="45" t="n">
+      <c r="C6" s="52" t="n">
         <v>0.00769</v>
       </c>
-      <c r="D6" s="45" t="n">
+      <c r="D6" s="52" t="n">
         <v>-0.00047</v>
       </c>
-      <c r="E6" s="45" t="n">
+      <c r="E6" s="52" t="n">
         <v>0.007820000000000001</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="52" t="n">
         <v>0.01397</v>
       </c>
-      <c r="C7" s="45" t="n">
+      <c r="C7" s="52" t="n">
         <v>0.01033</v>
       </c>
-      <c r="D7" s="45" t="n">
+      <c r="D7" s="52" t="n">
         <v>-0.0011</v>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="52" t="n">
         <v>0.01283</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>AGG</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="52" t="n">
         <v>0.03406</v>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C8" s="52" t="n">
         <v>0.01138</v>
       </c>
-      <c r="D8" s="45" t="n">
+      <c r="D8" s="52" t="n">
         <v>-0.00554</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="52" t="n">
         <v>0.01183</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>VAGG</t>
         </is>
       </c>
-      <c r="B9" s="45" t="n">
+      <c r="B9" s="52" t="n">
         <v>0.05004</v>
       </c>
-      <c r="C9" s="45" t="n">
+      <c r="C9" s="52" t="n">
         <v>0.01556</v>
       </c>
-      <c r="D9" s="45" t="n">
+      <c r="D9" s="52" t="n">
         <v>-0.00698</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="52" t="n">
         <v>0.01445</v>
       </c>
     </row>
@@ -17155,100 +17967,100 @@
       <c r="E11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="44" t="inlineStr">
         <is>
           <t>Reflation</t>
         </is>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="D12" s="44" t="inlineStr">
         <is>
           <t>Stagflation</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E12" s="44" t="inlineStr">
         <is>
           <t>Deflation</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>CONS</t>
         </is>
       </c>
-      <c r="B13" s="45" t="n">
+      <c r="B13" s="52" t="n">
         <v>0.01765</v>
       </c>
-      <c r="C13" s="45" t="n">
+      <c r="C13" s="52" t="n">
         <v>0.0223</v>
       </c>
-      <c r="D13" s="45" t="n">
+      <c r="D13" s="52" t="n">
         <v>0.01283</v>
       </c>
-      <c r="E13" s="45" t="n">
+      <c r="E13" s="52" t="n">
         <v>0.0278</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="B14" s="45" t="n">
+      <c r="B14" s="52" t="n">
         <v>0.03064</v>
       </c>
-      <c r="C14" s="45" t="n">
+      <c r="C14" s="52" t="n">
         <v>0.03189</v>
       </c>
-      <c r="D14" s="45" t="n">
+      <c r="D14" s="52" t="n">
         <v>0.01504</v>
       </c>
-      <c r="E14" s="45" t="n">
+      <c r="E14" s="52" t="n">
         <v>0.03919</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>AGG</t>
         </is>
       </c>
-      <c r="B15" s="45" t="n">
+      <c r="B15" s="52" t="n">
         <v>0.09061</v>
       </c>
-      <c r="C15" s="45" t="n">
+      <c r="C15" s="52" t="n">
         <v>0.04874</v>
       </c>
-      <c r="D15" s="45" t="n">
+      <c r="D15" s="52" t="n">
         <v>0.02913</v>
       </c>
-      <c r="E15" s="45" t="n">
+      <c r="E15" s="52" t="n">
         <v>0.0717</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>VAGG</t>
         </is>
       </c>
-      <c r="B16" s="45" t="n">
+      <c r="B16" s="52" t="n">
         <v>0.13741</v>
       </c>
-      <c r="C16" s="45" t="n">
+      <c r="C16" s="52" t="n">
         <v>0.06776</v>
       </c>
-      <c r="D16" s="45" t="n">
+      <c r="D16" s="52" t="n">
         <v>0.03462</v>
       </c>
-      <c r="E16" s="45" t="n">
+      <c r="E16" s="52" t="n">
         <v>0.1052</v>
       </c>
     </row>
@@ -17264,22 +18076,22 @@
       <c r="E18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="44" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="44" t="inlineStr">
         <is>
           <t>Reflation</t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D19" s="44" t="inlineStr">
         <is>
           <t>Stagflation</t>
         </is>
       </c>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="E19" s="44" t="inlineStr">
         <is>
           <t>Deflation</t>
         </is>
@@ -17291,16 +18103,16 @@
           <t>Share of months</t>
         </is>
       </c>
-      <c r="B20" s="46" t="n">
+      <c r="B20" s="53" t="n">
         <v>0.323</v>
       </c>
-      <c r="C20" s="46" t="n">
+      <c r="C20" s="53" t="n">
         <v>0.466</v>
       </c>
-      <c r="D20" s="46" t="n">
+      <c r="D20" s="53" t="n">
         <v>0.082</v>
       </c>
-      <c r="E20" s="46" t="n">
+      <c r="E20" s="53" t="n">
         <v>0.129</v>
       </c>
     </row>
@@ -17310,16 +18122,16 @@
           <t>Avg duration (months)</t>
         </is>
       </c>
-      <c r="B21" s="47" t="n">
+      <c r="B21" s="54" t="n">
         <v>3.3</v>
       </c>
-      <c r="C21" s="47" t="n">
+      <c r="C21" s="54" t="n">
         <v>5.4</v>
       </c>
-      <c r="D21" s="47" t="n">
+      <c r="D21" s="54" t="n">
         <v>2.7</v>
       </c>
-      <c r="E21" s="47" t="n">
+      <c r="E21" s="54" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -17329,7 +18141,7 @@
           <t>Risk-free rate (annual)</t>
         </is>
       </c>
-      <c r="B23" s="46" t="n">
+      <c r="B23" s="53" t="n">
         <v>0.019</v>
       </c>
     </row>
@@ -17338,133 +18150,147 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>Methodology &amp; Assumptions</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="48" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>Glide path</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t>The Dashboard assigns a risk tier to each 5-year age block (age 25→65 = 8 decision points). The projection applies each block's tier return, switching automatically at block boundaries. Defaults de-risk with age: VAGG→AGG→MOD→CONS.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>Framework</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>Four macro regimes (growth x inflation) classified monthly ex-ante (SPY &amp; DBC vs 10-month SMAs, locked). Each tier = fixed allocation per regime (matrix v2). Per-tier expected returns blend per-regime statistics by the Settings regime mix, minus switch-cost drag.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Contributions</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="55" t="inlineStr">
         <is>
           <t>Year-by-year monthly schedule on Settings (defaults: $500 yr1, $800 by yr3, +12%/yr to yr15 as income scales to ~$500k, +8%/yr after), capped on the Dashboard. Projection applies the exact schedule.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>Uncertainty</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="49" t="inlineStr">
+      <c r="A13" s="55" t="inlineStr">
         <is>
           <t>Low/High paths and Statistics percentiles band the uncertainty of the AVERAGE growth rate (+/- s.e. = annual sd / sqrt(horizon years)). They are not drawdown bounds: backtested max drawdowns are CONS -13%, MOD -15%, AGG -37%, VAGG -51%, and a VAGG-heavy early glide will experience them.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>Return haircut</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="49" t="inlineStr">
+      <c r="A16" s="55" t="inlineStr">
         <is>
           <t>Long-horizon compounding of raw backtest returns is not credible (edges decay; regimes shift; capacity and execution erode results). The Dashboard haircut (default 25%) scales all tier returns down before projecting. Set 0% to see raw-backtest numbers; treat those as an upper bound, not a plan.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>Evidence quality</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="49" t="inlineStr">
+      <c r="A19" s="55" t="inlineStr">
         <is>
           <t>Backtest Jun 2007-Aug 2026; leveraged instruments simulated pre-2010; playbooks partly second-generation designs. The append-only monthly paper ledger is the binding forward test. Statistics percentiles additionally approximate contributions as smooth growth (cap ignored).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="48" t="inlineStr">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="55" t="inlineStr">
+        <is>
+          <t>Benchmark historical stats computed on the identical window/method as the tiers (source: Yahoo adjusted closes). Forward balances use the same start, contribution schedule approximation, and horizon; benchmarks default to raw historical CAGR while rotation rows are haircut - edit either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
         <is>
           <t>Colors</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="49" t="inlineStr">
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="55" t="inlineStr">
         <is>
           <t>Yellow = inputs. Blue = editable assumptions. Green = derived/links. Navy bars = sections. Grey columns on the glide table are helpers used by Statistics.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="48" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t>Disclaimer</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="49" t="inlineStr">
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="55" t="inlineStr">
         <is>
           <t>Personal research tooling; not investment advice. Past and simulated performance do not guarantee future results.</t>
         </is>

--- a/GrowthProjection.xlsx
+++ b/GrowthProjection.xlsx
@@ -211,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -285,6 +285,11 @@
     <xf numFmtId="2" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -709,7 +714,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Comparison'!$D$19:$D$29</f>
+              <f>'Comparison'!$E$19:$E$29</f>
             </numRef>
           </val>
         </ser>
@@ -2770,7 +2775,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2 · Forward-looking — same contributions, same horizon, to end age</t>
+          <t>2 · Forward-looking — same contributions, same horizon, SAME haircut on every row</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr"/>
@@ -2778,32 +2783,48 @@
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
+      <c r="G17" s="35" t="inlineStr">
+        <is>
+          <t>Benchmark haircut:</t>
+        </is>
+      </c>
+      <c r="H17" s="36">
+        <f>Dashboard!$C$10</f>
+        <v/>
+      </c>
+      <c r="I17" s="37" t="inlineStr">
+        <is>
+          <t>(links to Dashboard; overwrite to differ)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>Expected return (edit)</t>
-        </is>
-      </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
+        <is>
+          <t>Raw hist. CAGR</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>Net expected (after haircut)</t>
+        </is>
+      </c>
+      <c r="D18" s="38" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D18" s="35" t="inlineStr">
+      <c r="E18" s="38" t="inlineStr">
         <is>
           <t>Balance at end age</t>
         </is>
       </c>
-      <c r="E18" s="35" t="inlineStr">
+      <c r="F18" s="38" t="inlineStr">
         <is>
           <t>vs glide path</t>
         </is>
@@ -2818,16 +2839,20 @@
       <c r="B19" s="8" t="n">
         <v>0.1083</v>
       </c>
-      <c r="C19" s="36">
-        <f>(1+B19)^(1/12)-1</f>
-        <v/>
-      </c>
-      <c r="D19" s="29">
-        <f>IF(ABS($C$19-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$19)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$19)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$19)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$19)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$19-Settings!$B$60))</f>
-        <v/>
-      </c>
-      <c r="E19" s="23">
-        <f>D19/$D$29-1</f>
+      <c r="C19" s="23">
+        <f>B19*(1-$H$17)</f>
+        <v/>
+      </c>
+      <c r="D19" s="39">
+        <f>(1+C19)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="E19" s="29">
+        <f>IF(ABS($D$19-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$D$19)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$D$19)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$D$19)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$D$19)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($D$19-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="F19" s="23">
+        <f>E19/$E$29-1</f>
         <v/>
       </c>
     </row>
@@ -2840,16 +2865,20 @@
       <c r="B20" s="8" t="n">
         <v>0.1626</v>
       </c>
-      <c r="C20" s="36">
-        <f>(1+B20)^(1/12)-1</f>
-        <v/>
-      </c>
-      <c r="D20" s="29">
-        <f>IF(ABS($C$20-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$20)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$20)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$20)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$20)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$20-Settings!$B$60))</f>
-        <v/>
-      </c>
-      <c r="E20" s="23">
-        <f>D20/$D$29-1</f>
+      <c r="C20" s="23">
+        <f>B20*(1-$H$17)</f>
+        <v/>
+      </c>
+      <c r="D20" s="39">
+        <f>(1+C20)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="E20" s="29">
+        <f>IF(ABS($D$20-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$D$20)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$D$20)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$D$20)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$D$20)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($D$20-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="F20" s="23">
+        <f>E20/$E$29-1</f>
         <v/>
       </c>
     </row>
@@ -2862,16 +2891,20 @@
       <c r="B21" s="8" t="n">
         <v>0.0978</v>
       </c>
-      <c r="C21" s="36">
-        <f>(1+B21)^(1/12)-1</f>
-        <v/>
-      </c>
-      <c r="D21" s="29">
-        <f>IF(ABS($C$21-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$21)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$21)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$21)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$21)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$21-Settings!$B$60))</f>
-        <v/>
-      </c>
-      <c r="E21" s="23">
-        <f>D21/$D$29-1</f>
+      <c r="C21" s="23">
+        <f>B21*(1-$H$17)</f>
+        <v/>
+      </c>
+      <c r="D21" s="39">
+        <f>(1+C21)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="E21" s="29">
+        <f>IF(ABS($D$21-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$D$21)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$D$21)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$D$21)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$D$21)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($D$21-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="F21" s="23">
+        <f>E21/$E$29-1</f>
         <v/>
       </c>
     </row>
@@ -2884,16 +2917,20 @@
       <c r="B22" s="8" t="n">
         <v>0.08169999999999999</v>
       </c>
-      <c r="C22" s="36">
-        <f>(1+B22)^(1/12)-1</f>
-        <v/>
-      </c>
-      <c r="D22" s="29">
-        <f>IF(ABS($C$22-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$22)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$22)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$22)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$22)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$22-Settings!$B$60))</f>
-        <v/>
-      </c>
-      <c r="E22" s="23">
-        <f>D22/$D$29-1</f>
+      <c r="C22" s="23">
+        <f>B22*(1-$H$17)</f>
+        <v/>
+      </c>
+      <c r="D22" s="39">
+        <f>(1+C22)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="E22" s="29">
+        <f>IF(ABS($D$22-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$D$22)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$D$22)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$D$22)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$D$22)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($D$22-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="F22" s="23">
+        <f>E22/$E$29-1</f>
         <v/>
       </c>
     </row>
@@ -2906,16 +2943,20 @@
       <c r="B23" s="8" t="n">
         <v>0.0298</v>
       </c>
-      <c r="C23" s="36">
-        <f>(1+B23)^(1/12)-1</f>
-        <v/>
-      </c>
-      <c r="D23" s="29">
-        <f>IF(ABS($C$23-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$23)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$23)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$23)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$23)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$23-Settings!$B$60))</f>
-        <v/>
-      </c>
-      <c r="E23" s="23">
-        <f>D23/$D$29-1</f>
+      <c r="C23" s="23">
+        <f>B23*(1-$H$17)</f>
+        <v/>
+      </c>
+      <c r="D23" s="39">
+        <f>(1+C23)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="E23" s="29">
+        <f>IF(ABS($D$23-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$D$23)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$D$23)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$D$23)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$D$23)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($D$23-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="F23" s="23">
+        <f>E23/$E$29-1</f>
         <v/>
       </c>
     </row>
@@ -2928,113 +2969,133 @@
       <c r="B24" s="8" t="n">
         <v>0.0998</v>
       </c>
-      <c r="C24" s="36">
-        <f>(1+B24)^(1/12)-1</f>
-        <v/>
-      </c>
-      <c r="D24" s="29">
-        <f>IF(ABS($C$24-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$24)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$24)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$24)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$24)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$24-Settings!$B$60))</f>
-        <v/>
-      </c>
-      <c r="E24" s="23">
-        <f>D24/$D$29-1</f>
+      <c r="C24" s="23">
+        <f>B24*(1-$H$17)</f>
+        <v/>
+      </c>
+      <c r="D24" s="39">
+        <f>(1+C24)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="E24" s="29">
+        <f>IF(ABS($D$24-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$D$24)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$D$24)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$D$24)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$D$24)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($D$24-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="F24" s="23">
+        <f>E24/$E$29-1</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>Rotation CONS (haircut)</t>
+          <t>Rotation CONS</t>
         </is>
       </c>
       <c r="B25" s="24">
+        <f>Statistics!$B$6</f>
+        <v/>
+      </c>
+      <c r="C25" s="24">
         <f>Settings!$C$13</f>
         <v/>
       </c>
-      <c r="C25" s="36">
-        <f>(1+B25)^(1/12)-1</f>
-        <v/>
-      </c>
-      <c r="D25" s="37">
-        <f>IF(ABS($C$25-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$25)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$25)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$25)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$25)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$25-Settings!$B$60))</f>
-        <v/>
-      </c>
-      <c r="E25" s="23">
-        <f>D25/$D$29-1</f>
+      <c r="D25" s="39">
+        <f>(1+C25)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="E25" s="40">
+        <f>IF(ABS($D$25-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$D$25)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$D$25)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$D$25)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$D$25)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($D$25-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="F25" s="23">
+        <f>E25/$E$29-1</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>Rotation MOD (haircut)</t>
+          <t>Rotation MOD</t>
         </is>
       </c>
       <c r="B26" s="24">
+        <f>Statistics!$B$7</f>
+        <v/>
+      </c>
+      <c r="C26" s="24">
         <f>Settings!$C$14</f>
         <v/>
       </c>
-      <c r="C26" s="36">
-        <f>(1+B26)^(1/12)-1</f>
-        <v/>
-      </c>
-      <c r="D26" s="37">
-        <f>IF(ABS($C$26-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$26)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$26)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$26)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$26)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$26-Settings!$B$60))</f>
-        <v/>
-      </c>
-      <c r="E26" s="23">
-        <f>D26/$D$29-1</f>
+      <c r="D26" s="39">
+        <f>(1+C26)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="E26" s="40">
+        <f>IF(ABS($D$26-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$D$26)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$D$26)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$D$26)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$D$26)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($D$26-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="F26" s="23">
+        <f>E26/$E$29-1</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>Rotation AGG (haircut)</t>
+          <t>Rotation AGG</t>
         </is>
       </c>
       <c r="B27" s="24">
+        <f>Statistics!$B$8</f>
+        <v/>
+      </c>
+      <c r="C27" s="24">
         <f>Settings!$C$15</f>
         <v/>
       </c>
-      <c r="C27" s="36">
-        <f>(1+B27)^(1/12)-1</f>
-        <v/>
-      </c>
-      <c r="D27" s="37">
-        <f>IF(ABS($C$27-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$27)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$27)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$27)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$27)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$27-Settings!$B$60))</f>
-        <v/>
-      </c>
-      <c r="E27" s="23">
-        <f>D27/$D$29-1</f>
+      <c r="D27" s="39">
+        <f>(1+C27)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="E27" s="40">
+        <f>IF(ABS($D$27-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$D$27)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$D$27)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$D$27)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$D$27)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($D$27-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="F27" s="23">
+        <f>E27/$E$29-1</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>Rotation VAGG (haircut)</t>
+          <t>Rotation VAGG</t>
         </is>
       </c>
       <c r="B28" s="24">
+        <f>Statistics!$B$9</f>
+        <v/>
+      </c>
+      <c r="C28" s="24">
         <f>Settings!$C$16</f>
         <v/>
       </c>
-      <c r="C28" s="36">
-        <f>(1+B28)^(1/12)-1</f>
-        <v/>
-      </c>
-      <c r="D28" s="37">
-        <f>IF(ABS($C$28-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$C$28)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$C$28)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$C$28)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$C$28)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($C$28-Settings!$B$60))</f>
-        <v/>
-      </c>
-      <c r="E28" s="23">
-        <f>D28/$D$29-1</f>
+      <c r="D28" s="39">
+        <f>(1+C28)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="E28" s="40">
+        <f>IF(ABS($D$28-Settings!$B$60)&lt;0.000001,Dashboard!$C$7*(1+$D$28)^(Settings!$B$9*12)+Dashboard!$C$8*(Settings!$B$9*12)*(1+$D$28)^((Settings!$B$9*12)-1),Dashboard!$C$7*(1+$D$28)^(Settings!$B$9*12)+Dashboard!$C$8*(((1+$D$28)^(Settings!$B$9*12))-((1+Settings!$B$60)^(Settings!$B$9*12)))/($D$28-Settings!$B$60))</f>
+        <v/>
+      </c>
+      <c r="F28" s="23">
+        <f>E28/$E$29-1</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="inlineStr">
+      <c r="A29" s="41" t="inlineStr">
         <is>
           <t>YOUR GLIDE PATH (exact)</t>
         </is>
@@ -3043,7 +3104,7 @@
         <f>Statistics!$B$32</f>
         <v/>
       </c>
-      <c r="D29" s="39">
+      <c r="E29" s="42">
         <f>INDEX(Projection!$E:$E,(Settings!$B$9*12)+4)</f>
         <v/>
       </c>
@@ -3051,7 +3112,7 @@
     <row r="31">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>Benchmark expected returns default to raw historical CAGR (no haircut) — arguably generous to them; edit the yellow cells to stress. Rotation rows use the Dashboard haircut. Glide row is the exact month-by-month projection.</t>
+          <t>One haircut, every row: benchmarks and rotation tiers are discounted identically (benchmark haircut links to the Dashboard input; overwrite it only to make a deliberate argument). Rotation net = the Settings engine rate, so this table matches the Projection. Glide row is the exact month-by-month path.</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3145,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>Age-Aware Wealth Projection</t>
         </is>
@@ -3098,47 +3159,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="41" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>Contribution</t>
         </is>
       </c>
-      <c r="E4" s="41" t="inlineStr">
+      <c r="E4" s="44" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="F4" s="41" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G4" s="41" t="inlineStr">
+      <c r="G4" s="44" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="n">
+      <c r="A5" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="43">
+      <c r="B5" s="46">
         <f>Dashboard!$C$5+(1-1)/12</f>
         <v/>
       </c>
@@ -3164,10 +3225,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="42" t="n">
+      <c r="A6" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="43">
+      <c r="B6" s="46">
         <f>Dashboard!$C$5+(2-1)/12</f>
         <v/>
       </c>
@@ -3193,10 +3254,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="42" t="n">
+      <c r="A7" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="43">
+      <c r="B7" s="46">
         <f>Dashboard!$C$5+(3-1)/12</f>
         <v/>
       </c>
@@ -3222,10 +3283,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="n">
+      <c r="A8" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="43">
+      <c r="B8" s="46">
         <f>Dashboard!$C$5+(4-1)/12</f>
         <v/>
       </c>
@@ -3251,10 +3312,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="42" t="n">
+      <c r="A9" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="43">
+      <c r="B9" s="46">
         <f>Dashboard!$C$5+(5-1)/12</f>
         <v/>
       </c>
@@ -3280,10 +3341,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="42" t="n">
+      <c r="A10" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="46">
         <f>Dashboard!$C$5+(6-1)/12</f>
         <v/>
       </c>
@@ -3309,10 +3370,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="42" t="n">
+      <c r="A11" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="43">
+      <c r="B11" s="46">
         <f>Dashboard!$C$5+(7-1)/12</f>
         <v/>
       </c>
@@ -3338,10 +3399,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="42" t="n">
+      <c r="A12" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="43">
+      <c r="B12" s="46">
         <f>Dashboard!$C$5+(8-1)/12</f>
         <v/>
       </c>
@@ -3367,10 +3428,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="42" t="n">
+      <c r="A13" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="43">
+      <c r="B13" s="46">
         <f>Dashboard!$C$5+(9-1)/12</f>
         <v/>
       </c>
@@ -3396,10 +3457,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="42" t="n">
+      <c r="A14" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="43">
+      <c r="B14" s="46">
         <f>Dashboard!$C$5+(10-1)/12</f>
         <v/>
       </c>
@@ -3425,10 +3486,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="42" t="n">
+      <c r="A15" s="45" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="43">
+      <c r="B15" s="46">
         <f>Dashboard!$C$5+(11-1)/12</f>
         <v/>
       </c>
@@ -3454,10 +3515,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="42" t="n">
+      <c r="A16" s="45" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="46">
         <f>Dashboard!$C$5+(12-1)/12</f>
         <v/>
       </c>
@@ -3483,10 +3544,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="42" t="n">
+      <c r="A17" s="45" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="46">
         <f>Dashboard!$C$5+(13-1)/12</f>
         <v/>
       </c>
@@ -3512,10 +3573,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="42" t="n">
+      <c r="A18" s="45" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="43">
+      <c r="B18" s="46">
         <f>Dashboard!$C$5+(14-1)/12</f>
         <v/>
       </c>
@@ -3541,10 +3602,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="42" t="n">
+      <c r="A19" s="45" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="43">
+      <c r="B19" s="46">
         <f>Dashboard!$C$5+(15-1)/12</f>
         <v/>
       </c>
@@ -3570,10 +3631,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="42" t="n">
+      <c r="A20" s="45" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="43">
+      <c r="B20" s="46">
         <f>Dashboard!$C$5+(16-1)/12</f>
         <v/>
       </c>
@@ -3599,10 +3660,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="42" t="n">
+      <c r="A21" s="45" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="43">
+      <c r="B21" s="46">
         <f>Dashboard!$C$5+(17-1)/12</f>
         <v/>
       </c>
@@ -3628,10 +3689,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="42" t="n">
+      <c r="A22" s="45" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="43">
+      <c r="B22" s="46">
         <f>Dashboard!$C$5+(18-1)/12</f>
         <v/>
       </c>
@@ -3657,10 +3718,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="42" t="n">
+      <c r="A23" s="45" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="43">
+      <c r="B23" s="46">
         <f>Dashboard!$C$5+(19-1)/12</f>
         <v/>
       </c>
@@ -3686,10 +3747,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="42" t="n">
+      <c r="A24" s="45" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="43">
+      <c r="B24" s="46">
         <f>Dashboard!$C$5+(20-1)/12</f>
         <v/>
       </c>
@@ -3715,10 +3776,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="42" t="n">
+      <c r="A25" s="45" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="43">
+      <c r="B25" s="46">
         <f>Dashboard!$C$5+(21-1)/12</f>
         <v/>
       </c>
@@ -3744,10 +3805,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="42" t="n">
+      <c r="A26" s="45" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="43">
+      <c r="B26" s="46">
         <f>Dashboard!$C$5+(22-1)/12</f>
         <v/>
       </c>
@@ -3773,10 +3834,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="42" t="n">
+      <c r="A27" s="45" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="43">
+      <c r="B27" s="46">
         <f>Dashboard!$C$5+(23-1)/12</f>
         <v/>
       </c>
@@ -3802,10 +3863,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="42" t="n">
+      <c r="A28" s="45" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="43">
+      <c r="B28" s="46">
         <f>Dashboard!$C$5+(24-1)/12</f>
         <v/>
       </c>
@@ -3831,10 +3892,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="42" t="n">
+      <c r="A29" s="45" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="43">
+      <c r="B29" s="46">
         <f>Dashboard!$C$5+(25-1)/12</f>
         <v/>
       </c>
@@ -3860,10 +3921,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="42" t="n">
+      <c r="A30" s="45" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="43">
+      <c r="B30" s="46">
         <f>Dashboard!$C$5+(26-1)/12</f>
         <v/>
       </c>
@@ -3889,10 +3950,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="42" t="n">
+      <c r="A31" s="45" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="43">
+      <c r="B31" s="46">
         <f>Dashboard!$C$5+(27-1)/12</f>
         <v/>
       </c>
@@ -3918,10 +3979,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="42" t="n">
+      <c r="A32" s="45" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="43">
+      <c r="B32" s="46">
         <f>Dashboard!$C$5+(28-1)/12</f>
         <v/>
       </c>
@@ -3947,10 +4008,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="42" t="n">
+      <c r="A33" s="45" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="43">
+      <c r="B33" s="46">
         <f>Dashboard!$C$5+(29-1)/12</f>
         <v/>
       </c>
@@ -3976,10 +4037,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="42" t="n">
+      <c r="A34" s="45" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="43">
+      <c r="B34" s="46">
         <f>Dashboard!$C$5+(30-1)/12</f>
         <v/>
       </c>
@@ -4005,10 +4066,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="42" t="n">
+      <c r="A35" s="45" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="43">
+      <c r="B35" s="46">
         <f>Dashboard!$C$5+(31-1)/12</f>
         <v/>
       </c>
@@ -4034,10 +4095,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="42" t="n">
+      <c r="A36" s="45" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="43">
+      <c r="B36" s="46">
         <f>Dashboard!$C$5+(32-1)/12</f>
         <v/>
       </c>
@@ -4063,10 +4124,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="42" t="n">
+      <c r="A37" s="45" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="43">
+      <c r="B37" s="46">
         <f>Dashboard!$C$5+(33-1)/12</f>
         <v/>
       </c>
@@ -4092,10 +4153,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="42" t="n">
+      <c r="A38" s="45" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="43">
+      <c r="B38" s="46">
         <f>Dashboard!$C$5+(34-1)/12</f>
         <v/>
       </c>
@@ -4121,10 +4182,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="42" t="n">
+      <c r="A39" s="45" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="43">
+      <c r="B39" s="46">
         <f>Dashboard!$C$5+(35-1)/12</f>
         <v/>
       </c>
@@ -4150,10 +4211,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="42" t="n">
+      <c r="A40" s="45" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="43">
+      <c r="B40" s="46">
         <f>Dashboard!$C$5+(36-1)/12</f>
         <v/>
       </c>
@@ -4179,10 +4240,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="42" t="n">
+      <c r="A41" s="45" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="43">
+      <c r="B41" s="46">
         <f>Dashboard!$C$5+(37-1)/12</f>
         <v/>
       </c>
@@ -4208,10 +4269,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="42" t="n">
+      <c r="A42" s="45" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="43">
+      <c r="B42" s="46">
         <f>Dashboard!$C$5+(38-1)/12</f>
         <v/>
       </c>
@@ -4237,10 +4298,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="42" t="n">
+      <c r="A43" s="45" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="43">
+      <c r="B43" s="46">
         <f>Dashboard!$C$5+(39-1)/12</f>
         <v/>
       </c>
@@ -4266,10 +4327,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="42" t="n">
+      <c r="A44" s="45" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="43">
+      <c r="B44" s="46">
         <f>Dashboard!$C$5+(40-1)/12</f>
         <v/>
       </c>
@@ -4295,10 +4356,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="42" t="n">
+      <c r="A45" s="45" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="43">
+      <c r="B45" s="46">
         <f>Dashboard!$C$5+(41-1)/12</f>
         <v/>
       </c>
@@ -4324,10 +4385,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="42" t="n">
+      <c r="A46" s="45" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="43">
+      <c r="B46" s="46">
         <f>Dashboard!$C$5+(42-1)/12</f>
         <v/>
       </c>
@@ -4353,10 +4414,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="42" t="n">
+      <c r="A47" s="45" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="43">
+      <c r="B47" s="46">
         <f>Dashboard!$C$5+(43-1)/12</f>
         <v/>
       </c>
@@ -4382,10 +4443,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="42" t="n">
+      <c r="A48" s="45" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="43">
+      <c r="B48" s="46">
         <f>Dashboard!$C$5+(44-1)/12</f>
         <v/>
       </c>
@@ -4411,10 +4472,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="42" t="n">
+      <c r="A49" s="45" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="43">
+      <c r="B49" s="46">
         <f>Dashboard!$C$5+(45-1)/12</f>
         <v/>
       </c>
@@ -4440,10 +4501,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="42" t="n">
+      <c r="A50" s="45" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="43">
+      <c r="B50" s="46">
         <f>Dashboard!$C$5+(46-1)/12</f>
         <v/>
       </c>
@@ -4469,10 +4530,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="42" t="n">
+      <c r="A51" s="45" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="43">
+      <c r="B51" s="46">
         <f>Dashboard!$C$5+(47-1)/12</f>
         <v/>
       </c>
@@ -4498,10 +4559,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="42" t="n">
+      <c r="A52" s="45" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="43">
+      <c r="B52" s="46">
         <f>Dashboard!$C$5+(48-1)/12</f>
         <v/>
       </c>
@@ -4527,10 +4588,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="42" t="n">
+      <c r="A53" s="45" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="43">
+      <c r="B53" s="46">
         <f>Dashboard!$C$5+(49-1)/12</f>
         <v/>
       </c>
@@ -4556,10 +4617,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="42" t="n">
+      <c r="A54" s="45" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="43">
+      <c r="B54" s="46">
         <f>Dashboard!$C$5+(50-1)/12</f>
         <v/>
       </c>
@@ -4585,10 +4646,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="42" t="n">
+      <c r="A55" s="45" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="43">
+      <c r="B55" s="46">
         <f>Dashboard!$C$5+(51-1)/12</f>
         <v/>
       </c>
@@ -4614,10 +4675,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="42" t="n">
+      <c r="A56" s="45" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="43">
+      <c r="B56" s="46">
         <f>Dashboard!$C$5+(52-1)/12</f>
         <v/>
       </c>
@@ -4643,10 +4704,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="42" t="n">
+      <c r="A57" s="45" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="43">
+      <c r="B57" s="46">
         <f>Dashboard!$C$5+(53-1)/12</f>
         <v/>
       </c>
@@ -4672,10 +4733,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="42" t="n">
+      <c r="A58" s="45" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="43">
+      <c r="B58" s="46">
         <f>Dashboard!$C$5+(54-1)/12</f>
         <v/>
       </c>
@@ -4701,10 +4762,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="42" t="n">
+      <c r="A59" s="45" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="43">
+      <c r="B59" s="46">
         <f>Dashboard!$C$5+(55-1)/12</f>
         <v/>
       </c>
@@ -4730,10 +4791,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="42" t="n">
+      <c r="A60" s="45" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="43">
+      <c r="B60" s="46">
         <f>Dashboard!$C$5+(56-1)/12</f>
         <v/>
       </c>
@@ -4759,10 +4820,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="42" t="n">
+      <c r="A61" s="45" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="43">
+      <c r="B61" s="46">
         <f>Dashboard!$C$5+(57-1)/12</f>
         <v/>
       </c>
@@ -4788,10 +4849,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="42" t="n">
+      <c r="A62" s="45" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="43">
+      <c r="B62" s="46">
         <f>Dashboard!$C$5+(58-1)/12</f>
         <v/>
       </c>
@@ -4817,10 +4878,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="42" t="n">
+      <c r="A63" s="45" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="43">
+      <c r="B63" s="46">
         <f>Dashboard!$C$5+(59-1)/12</f>
         <v/>
       </c>
@@ -4846,10 +4907,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="42" t="n">
+      <c r="A64" s="45" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="43">
+      <c r="B64" s="46">
         <f>Dashboard!$C$5+(60-1)/12</f>
         <v/>
       </c>
@@ -4875,10 +4936,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="42" t="n">
+      <c r="A65" s="45" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="43">
+      <c r="B65" s="46">
         <f>Dashboard!$C$5+(61-1)/12</f>
         <v/>
       </c>
@@ -4904,10 +4965,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="42" t="n">
+      <c r="A66" s="45" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="43">
+      <c r="B66" s="46">
         <f>Dashboard!$C$5+(62-1)/12</f>
         <v/>
       </c>
@@ -4933,10 +4994,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="42" t="n">
+      <c r="A67" s="45" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="43">
+      <c r="B67" s="46">
         <f>Dashboard!$C$5+(63-1)/12</f>
         <v/>
       </c>
@@ -4962,10 +5023,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="42" t="n">
+      <c r="A68" s="45" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="43">
+      <c r="B68" s="46">
         <f>Dashboard!$C$5+(64-1)/12</f>
         <v/>
       </c>
@@ -4991,10 +5052,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="42" t="n">
+      <c r="A69" s="45" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="43">
+      <c r="B69" s="46">
         <f>Dashboard!$C$5+(65-1)/12</f>
         <v/>
       </c>
@@ -5020,10 +5081,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="42" t="n">
+      <c r="A70" s="45" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="43">
+      <c r="B70" s="46">
         <f>Dashboard!$C$5+(66-1)/12</f>
         <v/>
       </c>
@@ -5049,10 +5110,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="42" t="n">
+      <c r="A71" s="45" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="43">
+      <c r="B71" s="46">
         <f>Dashboard!$C$5+(67-1)/12</f>
         <v/>
       </c>
@@ -5078,10 +5139,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="42" t="n">
+      <c r="A72" s="45" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="43">
+      <c r="B72" s="46">
         <f>Dashboard!$C$5+(68-1)/12</f>
         <v/>
       </c>
@@ -5107,10 +5168,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="42" t="n">
+      <c r="A73" s="45" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="43">
+      <c r="B73" s="46">
         <f>Dashboard!$C$5+(69-1)/12</f>
         <v/>
       </c>
@@ -5136,10 +5197,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="42" t="n">
+      <c r="A74" s="45" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="43">
+      <c r="B74" s="46">
         <f>Dashboard!$C$5+(70-1)/12</f>
         <v/>
       </c>
@@ -5165,10 +5226,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="42" t="n">
+      <c r="A75" s="45" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="43">
+      <c r="B75" s="46">
         <f>Dashboard!$C$5+(71-1)/12</f>
         <v/>
       </c>
@@ -5194,10 +5255,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="42" t="n">
+      <c r="A76" s="45" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="43">
+      <c r="B76" s="46">
         <f>Dashboard!$C$5+(72-1)/12</f>
         <v/>
       </c>
@@ -5223,10 +5284,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="42" t="n">
+      <c r="A77" s="45" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="43">
+      <c r="B77" s="46">
         <f>Dashboard!$C$5+(73-1)/12</f>
         <v/>
       </c>
@@ -5252,10 +5313,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="42" t="n">
+      <c r="A78" s="45" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="43">
+      <c r="B78" s="46">
         <f>Dashboard!$C$5+(74-1)/12</f>
         <v/>
       </c>
@@ -5281,10 +5342,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="42" t="n">
+      <c r="A79" s="45" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="43">
+      <c r="B79" s="46">
         <f>Dashboard!$C$5+(75-1)/12</f>
         <v/>
       </c>
@@ -5310,10 +5371,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="42" t="n">
+      <c r="A80" s="45" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="43">
+      <c r="B80" s="46">
         <f>Dashboard!$C$5+(76-1)/12</f>
         <v/>
       </c>
@@ -5339,10 +5400,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="42" t="n">
+      <c r="A81" s="45" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="43">
+      <c r="B81" s="46">
         <f>Dashboard!$C$5+(77-1)/12</f>
         <v/>
       </c>
@@ -5368,10 +5429,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="42" t="n">
+      <c r="A82" s="45" t="n">
         <v>78</v>
       </c>
-      <c r="B82" s="43">
+      <c r="B82" s="46">
         <f>Dashboard!$C$5+(78-1)/12</f>
         <v/>
       </c>
@@ -5397,10 +5458,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="42" t="n">
+      <c r="A83" s="45" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="43">
+      <c r="B83" s="46">
         <f>Dashboard!$C$5+(79-1)/12</f>
         <v/>
       </c>
@@ -5426,10 +5487,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="42" t="n">
+      <c r="A84" s="45" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="43">
+      <c r="B84" s="46">
         <f>Dashboard!$C$5+(80-1)/12</f>
         <v/>
       </c>
@@ -5455,10 +5516,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="42" t="n">
+      <c r="A85" s="45" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="43">
+      <c r="B85" s="46">
         <f>Dashboard!$C$5+(81-1)/12</f>
         <v/>
       </c>
@@ -5484,10 +5545,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="42" t="n">
+      <c r="A86" s="45" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="43">
+      <c r="B86" s="46">
         <f>Dashboard!$C$5+(82-1)/12</f>
         <v/>
       </c>
@@ -5513,10 +5574,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="42" t="n">
+      <c r="A87" s="45" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="43">
+      <c r="B87" s="46">
         <f>Dashboard!$C$5+(83-1)/12</f>
         <v/>
       </c>
@@ -5542,10 +5603,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="42" t="n">
+      <c r="A88" s="45" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="43">
+      <c r="B88" s="46">
         <f>Dashboard!$C$5+(84-1)/12</f>
         <v/>
       </c>
@@ -5571,10 +5632,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="42" t="n">
+      <c r="A89" s="45" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="43">
+      <c r="B89" s="46">
         <f>Dashboard!$C$5+(85-1)/12</f>
         <v/>
       </c>
@@ -5600,10 +5661,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="42" t="n">
+      <c r="A90" s="45" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="43">
+      <c r="B90" s="46">
         <f>Dashboard!$C$5+(86-1)/12</f>
         <v/>
       </c>
@@ -5629,10 +5690,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="42" t="n">
+      <c r="A91" s="45" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="43">
+      <c r="B91" s="46">
         <f>Dashboard!$C$5+(87-1)/12</f>
         <v/>
       </c>
@@ -5658,10 +5719,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="42" t="n">
+      <c r="A92" s="45" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="43">
+      <c r="B92" s="46">
         <f>Dashboard!$C$5+(88-1)/12</f>
         <v/>
       </c>
@@ -5687,10 +5748,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="42" t="n">
+      <c r="A93" s="45" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="43">
+      <c r="B93" s="46">
         <f>Dashboard!$C$5+(89-1)/12</f>
         <v/>
       </c>
@@ -5716,10 +5777,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="42" t="n">
+      <c r="A94" s="45" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="43">
+      <c r="B94" s="46">
         <f>Dashboard!$C$5+(90-1)/12</f>
         <v/>
       </c>
@@ -5745,10 +5806,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="42" t="n">
+      <c r="A95" s="45" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="43">
+      <c r="B95" s="46">
         <f>Dashboard!$C$5+(91-1)/12</f>
         <v/>
       </c>
@@ -5774,10 +5835,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="42" t="n">
+      <c r="A96" s="45" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="43">
+      <c r="B96" s="46">
         <f>Dashboard!$C$5+(92-1)/12</f>
         <v/>
       </c>
@@ -5803,10 +5864,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="42" t="n">
+      <c r="A97" s="45" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="43">
+      <c r="B97" s="46">
         <f>Dashboard!$C$5+(93-1)/12</f>
         <v/>
       </c>
@@ -5832,10 +5893,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="42" t="n">
+      <c r="A98" s="45" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="43">
+      <c r="B98" s="46">
         <f>Dashboard!$C$5+(94-1)/12</f>
         <v/>
       </c>
@@ -5861,10 +5922,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="42" t="n">
+      <c r="A99" s="45" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="43">
+      <c r="B99" s="46">
         <f>Dashboard!$C$5+(95-1)/12</f>
         <v/>
       </c>
@@ -5890,10 +5951,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="42" t="n">
+      <c r="A100" s="45" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="43">
+      <c r="B100" s="46">
         <f>Dashboard!$C$5+(96-1)/12</f>
         <v/>
       </c>
@@ -5919,10 +5980,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="42" t="n">
+      <c r="A101" s="45" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="43">
+      <c r="B101" s="46">
         <f>Dashboard!$C$5+(97-1)/12</f>
         <v/>
       </c>
@@ -5948,10 +6009,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="42" t="n">
+      <c r="A102" s="45" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="43">
+      <c r="B102" s="46">
         <f>Dashboard!$C$5+(98-1)/12</f>
         <v/>
       </c>
@@ -5977,10 +6038,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="42" t="n">
+      <c r="A103" s="45" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="43">
+      <c r="B103" s="46">
         <f>Dashboard!$C$5+(99-1)/12</f>
         <v/>
       </c>
@@ -6006,10 +6067,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="42" t="n">
+      <c r="A104" s="45" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="43">
+      <c r="B104" s="46">
         <f>Dashboard!$C$5+(100-1)/12</f>
         <v/>
       </c>
@@ -6035,10 +6096,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="42" t="n">
+      <c r="A105" s="45" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="43">
+      <c r="B105" s="46">
         <f>Dashboard!$C$5+(101-1)/12</f>
         <v/>
       </c>
@@ -6064,10 +6125,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="42" t="n">
+      <c r="A106" s="45" t="n">
         <v>102</v>
       </c>
-      <c r="B106" s="43">
+      <c r="B106" s="46">
         <f>Dashboard!$C$5+(102-1)/12</f>
         <v/>
       </c>
@@ -6093,10 +6154,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="42" t="n">
+      <c r="A107" s="45" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="43">
+      <c r="B107" s="46">
         <f>Dashboard!$C$5+(103-1)/12</f>
         <v/>
       </c>
@@ -6122,10 +6183,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="42" t="n">
+      <c r="A108" s="45" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="43">
+      <c r="B108" s="46">
         <f>Dashboard!$C$5+(104-1)/12</f>
         <v/>
       </c>
@@ -6151,10 +6212,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="42" t="n">
+      <c r="A109" s="45" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="43">
+      <c r="B109" s="46">
         <f>Dashboard!$C$5+(105-1)/12</f>
         <v/>
       </c>
@@ -6180,10 +6241,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="42" t="n">
+      <c r="A110" s="45" t="n">
         <v>106</v>
       </c>
-      <c r="B110" s="43">
+      <c r="B110" s="46">
         <f>Dashboard!$C$5+(106-1)/12</f>
         <v/>
       </c>
@@ -6209,10 +6270,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="42" t="n">
+      <c r="A111" s="45" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="43">
+      <c r="B111" s="46">
         <f>Dashboard!$C$5+(107-1)/12</f>
         <v/>
       </c>
@@ -6238,10 +6299,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="42" t="n">
+      <c r="A112" s="45" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="43">
+      <c r="B112" s="46">
         <f>Dashboard!$C$5+(108-1)/12</f>
         <v/>
       </c>
@@ -6267,10 +6328,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="42" t="n">
+      <c r="A113" s="45" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="43">
+      <c r="B113" s="46">
         <f>Dashboard!$C$5+(109-1)/12</f>
         <v/>
       </c>
@@ -6296,10 +6357,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="42" t="n">
+      <c r="A114" s="45" t="n">
         <v>110</v>
       </c>
-      <c r="B114" s="43">
+      <c r="B114" s="46">
         <f>Dashboard!$C$5+(110-1)/12</f>
         <v/>
       </c>
@@ -6325,10 +6386,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="42" t="n">
+      <c r="A115" s="45" t="n">
         <v>111</v>
       </c>
-      <c r="B115" s="43">
+      <c r="B115" s="46">
         <f>Dashboard!$C$5+(111-1)/12</f>
         <v/>
       </c>
@@ -6354,10 +6415,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="42" t="n">
+      <c r="A116" s="45" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="43">
+      <c r="B116" s="46">
         <f>Dashboard!$C$5+(112-1)/12</f>
         <v/>
       </c>
@@ -6383,10 +6444,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="42" t="n">
+      <c r="A117" s="45" t="n">
         <v>113</v>
       </c>
-      <c r="B117" s="43">
+      <c r="B117" s="46">
         <f>Dashboard!$C$5+(113-1)/12</f>
         <v/>
       </c>
@@ -6412,10 +6473,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="42" t="n">
+      <c r="A118" s="45" t="n">
         <v>114</v>
       </c>
-      <c r="B118" s="43">
+      <c r="B118" s="46">
         <f>Dashboard!$C$5+(114-1)/12</f>
         <v/>
       </c>
@@ -6441,10 +6502,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="42" t="n">
+      <c r="A119" s="45" t="n">
         <v>115</v>
       </c>
-      <c r="B119" s="43">
+      <c r="B119" s="46">
         <f>Dashboard!$C$5+(115-1)/12</f>
         <v/>
       </c>
@@ -6470,10 +6531,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="42" t="n">
+      <c r="A120" s="45" t="n">
         <v>116</v>
       </c>
-      <c r="B120" s="43">
+      <c r="B120" s="46">
         <f>Dashboard!$C$5+(116-1)/12</f>
         <v/>
       </c>
@@ -6499,10 +6560,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="42" t="n">
+      <c r="A121" s="45" t="n">
         <v>117</v>
       </c>
-      <c r="B121" s="43">
+      <c r="B121" s="46">
         <f>Dashboard!$C$5+(117-1)/12</f>
         <v/>
       </c>
@@ -6528,10 +6589,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="42" t="n">
+      <c r="A122" s="45" t="n">
         <v>118</v>
       </c>
-      <c r="B122" s="43">
+      <c r="B122" s="46">
         <f>Dashboard!$C$5+(118-1)/12</f>
         <v/>
       </c>
@@ -6557,10 +6618,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="42" t="n">
+      <c r="A123" s="45" t="n">
         <v>119</v>
       </c>
-      <c r="B123" s="43">
+      <c r="B123" s="46">
         <f>Dashboard!$C$5+(119-1)/12</f>
         <v/>
       </c>
@@ -6586,10 +6647,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="42" t="n">
+      <c r="A124" s="45" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="43">
+      <c r="B124" s="46">
         <f>Dashboard!$C$5+(120-1)/12</f>
         <v/>
       </c>
@@ -6615,10 +6676,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="42" t="n">
+      <c r="A125" s="45" t="n">
         <v>121</v>
       </c>
-      <c r="B125" s="43">
+      <c r="B125" s="46">
         <f>Dashboard!$C$5+(121-1)/12</f>
         <v/>
       </c>
@@ -6644,10 +6705,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="42" t="n">
+      <c r="A126" s="45" t="n">
         <v>122</v>
       </c>
-      <c r="B126" s="43">
+      <c r="B126" s="46">
         <f>Dashboard!$C$5+(122-1)/12</f>
         <v/>
       </c>
@@ -6673,10 +6734,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="42" t="n">
+      <c r="A127" s="45" t="n">
         <v>123</v>
       </c>
-      <c r="B127" s="43">
+      <c r="B127" s="46">
         <f>Dashboard!$C$5+(123-1)/12</f>
         <v/>
       </c>
@@ -6702,10 +6763,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="42" t="n">
+      <c r="A128" s="45" t="n">
         <v>124</v>
       </c>
-      <c r="B128" s="43">
+      <c r="B128" s="46">
         <f>Dashboard!$C$5+(124-1)/12</f>
         <v/>
       </c>
@@ -6731,10 +6792,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="42" t="n">
+      <c r="A129" s="45" t="n">
         <v>125</v>
       </c>
-      <c r="B129" s="43">
+      <c r="B129" s="46">
         <f>Dashboard!$C$5+(125-1)/12</f>
         <v/>
       </c>
@@ -6760,10 +6821,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="42" t="n">
+      <c r="A130" s="45" t="n">
         <v>126</v>
       </c>
-      <c r="B130" s="43">
+      <c r="B130" s="46">
         <f>Dashboard!$C$5+(126-1)/12</f>
         <v/>
       </c>
@@ -6789,10 +6850,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="42" t="n">
+      <c r="A131" s="45" t="n">
         <v>127</v>
       </c>
-      <c r="B131" s="43">
+      <c r="B131" s="46">
         <f>Dashboard!$C$5+(127-1)/12</f>
         <v/>
       </c>
@@ -6818,10 +6879,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="42" t="n">
+      <c r="A132" s="45" t="n">
         <v>128</v>
       </c>
-      <c r="B132" s="43">
+      <c r="B132" s="46">
         <f>Dashboard!$C$5+(128-1)/12</f>
         <v/>
       </c>
@@ -6847,10 +6908,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="42" t="n">
+      <c r="A133" s="45" t="n">
         <v>129</v>
       </c>
-      <c r="B133" s="43">
+      <c r="B133" s="46">
         <f>Dashboard!$C$5+(129-1)/12</f>
         <v/>
       </c>
@@ -6876,10 +6937,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="42" t="n">
+      <c r="A134" s="45" t="n">
         <v>130</v>
       </c>
-      <c r="B134" s="43">
+      <c r="B134" s="46">
         <f>Dashboard!$C$5+(130-1)/12</f>
         <v/>
       </c>
@@ -6905,10 +6966,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="42" t="n">
+      <c r="A135" s="45" t="n">
         <v>131</v>
       </c>
-      <c r="B135" s="43">
+      <c r="B135" s="46">
         <f>Dashboard!$C$5+(131-1)/12</f>
         <v/>
       </c>
@@ -6934,10 +6995,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="42" t="n">
+      <c r="A136" s="45" t="n">
         <v>132</v>
       </c>
-      <c r="B136" s="43">
+      <c r="B136" s="46">
         <f>Dashboard!$C$5+(132-1)/12</f>
         <v/>
       </c>
@@ -6963,10 +7024,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="42" t="n">
+      <c r="A137" s="45" t="n">
         <v>133</v>
       </c>
-      <c r="B137" s="43">
+      <c r="B137" s="46">
         <f>Dashboard!$C$5+(133-1)/12</f>
         <v/>
       </c>
@@ -6992,10 +7053,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="42" t="n">
+      <c r="A138" s="45" t="n">
         <v>134</v>
       </c>
-      <c r="B138" s="43">
+      <c r="B138" s="46">
         <f>Dashboard!$C$5+(134-1)/12</f>
         <v/>
       </c>
@@ -7021,10 +7082,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="42" t="n">
+      <c r="A139" s="45" t="n">
         <v>135</v>
       </c>
-      <c r="B139" s="43">
+      <c r="B139" s="46">
         <f>Dashboard!$C$5+(135-1)/12</f>
         <v/>
       </c>
@@ -7050,10 +7111,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="42" t="n">
+      <c r="A140" s="45" t="n">
         <v>136</v>
       </c>
-      <c r="B140" s="43">
+      <c r="B140" s="46">
         <f>Dashboard!$C$5+(136-1)/12</f>
         <v/>
       </c>
@@ -7079,10 +7140,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="42" t="n">
+      <c r="A141" s="45" t="n">
         <v>137</v>
       </c>
-      <c r="B141" s="43">
+      <c r="B141" s="46">
         <f>Dashboard!$C$5+(137-1)/12</f>
         <v/>
       </c>
@@ -7108,10 +7169,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="42" t="n">
+      <c r="A142" s="45" t="n">
         <v>138</v>
       </c>
-      <c r="B142" s="43">
+      <c r="B142" s="46">
         <f>Dashboard!$C$5+(138-1)/12</f>
         <v/>
       </c>
@@ -7137,10 +7198,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="42" t="n">
+      <c r="A143" s="45" t="n">
         <v>139</v>
       </c>
-      <c r="B143" s="43">
+      <c r="B143" s="46">
         <f>Dashboard!$C$5+(139-1)/12</f>
         <v/>
       </c>
@@ -7166,10 +7227,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="42" t="n">
+      <c r="A144" s="45" t="n">
         <v>140</v>
       </c>
-      <c r="B144" s="43">
+      <c r="B144" s="46">
         <f>Dashboard!$C$5+(140-1)/12</f>
         <v/>
       </c>
@@ -7195,10 +7256,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="42" t="n">
+      <c r="A145" s="45" t="n">
         <v>141</v>
       </c>
-      <c r="B145" s="43">
+      <c r="B145" s="46">
         <f>Dashboard!$C$5+(141-1)/12</f>
         <v/>
       </c>
@@ -7224,10 +7285,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="42" t="n">
+      <c r="A146" s="45" t="n">
         <v>142</v>
       </c>
-      <c r="B146" s="43">
+      <c r="B146" s="46">
         <f>Dashboard!$C$5+(142-1)/12</f>
         <v/>
       </c>
@@ -7253,10 +7314,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="42" t="n">
+      <c r="A147" s="45" t="n">
         <v>143</v>
       </c>
-      <c r="B147" s="43">
+      <c r="B147" s="46">
         <f>Dashboard!$C$5+(143-1)/12</f>
         <v/>
       </c>
@@ -7282,10 +7343,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="42" t="n">
+      <c r="A148" s="45" t="n">
         <v>144</v>
       </c>
-      <c r="B148" s="43">
+      <c r="B148" s="46">
         <f>Dashboard!$C$5+(144-1)/12</f>
         <v/>
       </c>
@@ -7311,10 +7372,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="42" t="n">
+      <c r="A149" s="45" t="n">
         <v>145</v>
       </c>
-      <c r="B149" s="43">
+      <c r="B149" s="46">
         <f>Dashboard!$C$5+(145-1)/12</f>
         <v/>
       </c>
@@ -7340,10 +7401,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="42" t="n">
+      <c r="A150" s="45" t="n">
         <v>146</v>
       </c>
-      <c r="B150" s="43">
+      <c r="B150" s="46">
         <f>Dashboard!$C$5+(146-1)/12</f>
         <v/>
       </c>
@@ -7369,10 +7430,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="42" t="n">
+      <c r="A151" s="45" t="n">
         <v>147</v>
       </c>
-      <c r="B151" s="43">
+      <c r="B151" s="46">
         <f>Dashboard!$C$5+(147-1)/12</f>
         <v/>
       </c>
@@ -7398,10 +7459,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="42" t="n">
+      <c r="A152" s="45" t="n">
         <v>148</v>
       </c>
-      <c r="B152" s="43">
+      <c r="B152" s="46">
         <f>Dashboard!$C$5+(148-1)/12</f>
         <v/>
       </c>
@@ -7427,10 +7488,10 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="42" t="n">
+      <c r="A153" s="45" t="n">
         <v>149</v>
       </c>
-      <c r="B153" s="43">
+      <c r="B153" s="46">
         <f>Dashboard!$C$5+(149-1)/12</f>
         <v/>
       </c>
@@ -7456,10 +7517,10 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="42" t="n">
+      <c r="A154" s="45" t="n">
         <v>150</v>
       </c>
-      <c r="B154" s="43">
+      <c r="B154" s="46">
         <f>Dashboard!$C$5+(150-1)/12</f>
         <v/>
       </c>
@@ -7485,10 +7546,10 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="42" t="n">
+      <c r="A155" s="45" t="n">
         <v>151</v>
       </c>
-      <c r="B155" s="43">
+      <c r="B155" s="46">
         <f>Dashboard!$C$5+(151-1)/12</f>
         <v/>
       </c>
@@ -7514,10 +7575,10 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="42" t="n">
+      <c r="A156" s="45" t="n">
         <v>152</v>
       </c>
-      <c r="B156" s="43">
+      <c r="B156" s="46">
         <f>Dashboard!$C$5+(152-1)/12</f>
         <v/>
       </c>
@@ -7543,10 +7604,10 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="42" t="n">
+      <c r="A157" s="45" t="n">
         <v>153</v>
       </c>
-      <c r="B157" s="43">
+      <c r="B157" s="46">
         <f>Dashboard!$C$5+(153-1)/12</f>
         <v/>
       </c>
@@ -7572,10 +7633,10 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="42" t="n">
+      <c r="A158" s="45" t="n">
         <v>154</v>
       </c>
-      <c r="B158" s="43">
+      <c r="B158" s="46">
         <f>Dashboard!$C$5+(154-1)/12</f>
         <v/>
       </c>
@@ -7601,10 +7662,10 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="42" t="n">
+      <c r="A159" s="45" t="n">
         <v>155</v>
       </c>
-      <c r="B159" s="43">
+      <c r="B159" s="46">
         <f>Dashboard!$C$5+(155-1)/12</f>
         <v/>
       </c>
@@ -7630,10 +7691,10 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="42" t="n">
+      <c r="A160" s="45" t="n">
         <v>156</v>
       </c>
-      <c r="B160" s="43">
+      <c r="B160" s="46">
         <f>Dashboard!$C$5+(156-1)/12</f>
         <v/>
       </c>
@@ -7659,10 +7720,10 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="42" t="n">
+      <c r="A161" s="45" t="n">
         <v>157</v>
       </c>
-      <c r="B161" s="43">
+      <c r="B161" s="46">
         <f>Dashboard!$C$5+(157-1)/12</f>
         <v/>
       </c>
@@ -7688,10 +7749,10 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="42" t="n">
+      <c r="A162" s="45" t="n">
         <v>158</v>
       </c>
-      <c r="B162" s="43">
+      <c r="B162" s="46">
         <f>Dashboard!$C$5+(158-1)/12</f>
         <v/>
       </c>
@@ -7717,10 +7778,10 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="42" t="n">
+      <c r="A163" s="45" t="n">
         <v>159</v>
       </c>
-      <c r="B163" s="43">
+      <c r="B163" s="46">
         <f>Dashboard!$C$5+(159-1)/12</f>
         <v/>
       </c>
@@ -7746,10 +7807,10 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="42" t="n">
+      <c r="A164" s="45" t="n">
         <v>160</v>
       </c>
-      <c r="B164" s="43">
+      <c r="B164" s="46">
         <f>Dashboard!$C$5+(160-1)/12</f>
         <v/>
       </c>
@@ -7775,10 +7836,10 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="42" t="n">
+      <c r="A165" s="45" t="n">
         <v>161</v>
       </c>
-      <c r="B165" s="43">
+      <c r="B165" s="46">
         <f>Dashboard!$C$5+(161-1)/12</f>
         <v/>
       </c>
@@ -7804,10 +7865,10 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="42" t="n">
+      <c r="A166" s="45" t="n">
         <v>162</v>
       </c>
-      <c r="B166" s="43">
+      <c r="B166" s="46">
         <f>Dashboard!$C$5+(162-1)/12</f>
         <v/>
       </c>
@@ -7833,10 +7894,10 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="42" t="n">
+      <c r="A167" s="45" t="n">
         <v>163</v>
       </c>
-      <c r="B167" s="43">
+      <c r="B167" s="46">
         <f>Dashboard!$C$5+(163-1)/12</f>
         <v/>
       </c>
@@ -7862,10 +7923,10 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="42" t="n">
+      <c r="A168" s="45" t="n">
         <v>164</v>
       </c>
-      <c r="B168" s="43">
+      <c r="B168" s="46">
         <f>Dashboard!$C$5+(164-1)/12</f>
         <v/>
       </c>
@@ -7891,10 +7952,10 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="42" t="n">
+      <c r="A169" s="45" t="n">
         <v>165</v>
       </c>
-      <c r="B169" s="43">
+      <c r="B169" s="46">
         <f>Dashboard!$C$5+(165-1)/12</f>
         <v/>
       </c>
@@ -7920,10 +7981,10 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="42" t="n">
+      <c r="A170" s="45" t="n">
         <v>166</v>
       </c>
-      <c r="B170" s="43">
+      <c r="B170" s="46">
         <f>Dashboard!$C$5+(166-1)/12</f>
         <v/>
       </c>
@@ -7949,10 +8010,10 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="42" t="n">
+      <c r="A171" s="45" t="n">
         <v>167</v>
       </c>
-      <c r="B171" s="43">
+      <c r="B171" s="46">
         <f>Dashboard!$C$5+(167-1)/12</f>
         <v/>
       </c>
@@ -7978,10 +8039,10 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="42" t="n">
+      <c r="A172" s="45" t="n">
         <v>168</v>
       </c>
-      <c r="B172" s="43">
+      <c r="B172" s="46">
         <f>Dashboard!$C$5+(168-1)/12</f>
         <v/>
       </c>
@@ -8007,10 +8068,10 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="42" t="n">
+      <c r="A173" s="45" t="n">
         <v>169</v>
       </c>
-      <c r="B173" s="43">
+      <c r="B173" s="46">
         <f>Dashboard!$C$5+(169-1)/12</f>
         <v/>
       </c>
@@ -8036,10 +8097,10 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="42" t="n">
+      <c r="A174" s="45" t="n">
         <v>170</v>
       </c>
-      <c r="B174" s="43">
+      <c r="B174" s="46">
         <f>Dashboard!$C$5+(170-1)/12</f>
         <v/>
       </c>
@@ -8065,10 +8126,10 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="42" t="n">
+      <c r="A175" s="45" t="n">
         <v>171</v>
       </c>
-      <c r="B175" s="43">
+      <c r="B175" s="46">
         <f>Dashboard!$C$5+(171-1)/12</f>
         <v/>
       </c>
@@ -8094,10 +8155,10 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="42" t="n">
+      <c r="A176" s="45" t="n">
         <v>172</v>
       </c>
-      <c r="B176" s="43">
+      <c r="B176" s="46">
         <f>Dashboard!$C$5+(172-1)/12</f>
         <v/>
       </c>
@@ -8123,10 +8184,10 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="42" t="n">
+      <c r="A177" s="45" t="n">
         <v>173</v>
       </c>
-      <c r="B177" s="43">
+      <c r="B177" s="46">
         <f>Dashboard!$C$5+(173-1)/12</f>
         <v/>
       </c>
@@ -8152,10 +8213,10 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="42" t="n">
+      <c r="A178" s="45" t="n">
         <v>174</v>
       </c>
-      <c r="B178" s="43">
+      <c r="B178" s="46">
         <f>Dashboard!$C$5+(174-1)/12</f>
         <v/>
       </c>
@@ -8181,10 +8242,10 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="42" t="n">
+      <c r="A179" s="45" t="n">
         <v>175</v>
       </c>
-      <c r="B179" s="43">
+      <c r="B179" s="46">
         <f>Dashboard!$C$5+(175-1)/12</f>
         <v/>
       </c>
@@ -8210,10 +8271,10 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="42" t="n">
+      <c r="A180" s="45" t="n">
         <v>176</v>
       </c>
-      <c r="B180" s="43">
+      <c r="B180" s="46">
         <f>Dashboard!$C$5+(176-1)/12</f>
         <v/>
       </c>
@@ -8239,10 +8300,10 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="42" t="n">
+      <c r="A181" s="45" t="n">
         <v>177</v>
       </c>
-      <c r="B181" s="43">
+      <c r="B181" s="46">
         <f>Dashboard!$C$5+(177-1)/12</f>
         <v/>
       </c>
@@ -8268,10 +8329,10 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="42" t="n">
+      <c r="A182" s="45" t="n">
         <v>178</v>
       </c>
-      <c r="B182" s="43">
+      <c r="B182" s="46">
         <f>Dashboard!$C$5+(178-1)/12</f>
         <v/>
       </c>
@@ -8297,10 +8358,10 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="42" t="n">
+      <c r="A183" s="45" t="n">
         <v>179</v>
       </c>
-      <c r="B183" s="43">
+      <c r="B183" s="46">
         <f>Dashboard!$C$5+(179-1)/12</f>
         <v/>
       </c>
@@ -8326,10 +8387,10 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="42" t="n">
+      <c r="A184" s="45" t="n">
         <v>180</v>
       </c>
-      <c r="B184" s="43">
+      <c r="B184" s="46">
         <f>Dashboard!$C$5+(180-1)/12</f>
         <v/>
       </c>
@@ -8355,10 +8416,10 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="42" t="n">
+      <c r="A185" s="45" t="n">
         <v>181</v>
       </c>
-      <c r="B185" s="43">
+      <c r="B185" s="46">
         <f>Dashboard!$C$5+(181-1)/12</f>
         <v/>
       </c>
@@ -8384,10 +8445,10 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="42" t="n">
+      <c r="A186" s="45" t="n">
         <v>182</v>
       </c>
-      <c r="B186" s="43">
+      <c r="B186" s="46">
         <f>Dashboard!$C$5+(182-1)/12</f>
         <v/>
       </c>
@@ -8413,10 +8474,10 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="42" t="n">
+      <c r="A187" s="45" t="n">
         <v>183</v>
       </c>
-      <c r="B187" s="43">
+      <c r="B187" s="46">
         <f>Dashboard!$C$5+(183-1)/12</f>
         <v/>
       </c>
@@ -8442,10 +8503,10 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="42" t="n">
+      <c r="A188" s="45" t="n">
         <v>184</v>
       </c>
-      <c r="B188" s="43">
+      <c r="B188" s="46">
         <f>Dashboard!$C$5+(184-1)/12</f>
         <v/>
       </c>
@@ -8471,10 +8532,10 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="42" t="n">
+      <c r="A189" s="45" t="n">
         <v>185</v>
       </c>
-      <c r="B189" s="43">
+      <c r="B189" s="46">
         <f>Dashboard!$C$5+(185-1)/12</f>
         <v/>
       </c>
@@ -8500,10 +8561,10 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="42" t="n">
+      <c r="A190" s="45" t="n">
         <v>186</v>
       </c>
-      <c r="B190" s="43">
+      <c r="B190" s="46">
         <f>Dashboard!$C$5+(186-1)/12</f>
         <v/>
       </c>
@@ -8529,10 +8590,10 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="42" t="n">
+      <c r="A191" s="45" t="n">
         <v>187</v>
       </c>
-      <c r="B191" s="43">
+      <c r="B191" s="46">
         <f>Dashboard!$C$5+(187-1)/12</f>
         <v/>
       </c>
@@ -8558,10 +8619,10 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="42" t="n">
+      <c r="A192" s="45" t="n">
         <v>188</v>
       </c>
-      <c r="B192" s="43">
+      <c r="B192" s="46">
         <f>Dashboard!$C$5+(188-1)/12</f>
         <v/>
       </c>
@@ -8587,10 +8648,10 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="42" t="n">
+      <c r="A193" s="45" t="n">
         <v>189</v>
       </c>
-      <c r="B193" s="43">
+      <c r="B193" s="46">
         <f>Dashboard!$C$5+(189-1)/12</f>
         <v/>
       </c>
@@ -8616,10 +8677,10 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="42" t="n">
+      <c r="A194" s="45" t="n">
         <v>190</v>
       </c>
-      <c r="B194" s="43">
+      <c r="B194" s="46">
         <f>Dashboard!$C$5+(190-1)/12</f>
         <v/>
       </c>
@@ -8645,10 +8706,10 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="42" t="n">
+      <c r="A195" s="45" t="n">
         <v>191</v>
       </c>
-      <c r="B195" s="43">
+      <c r="B195" s="46">
         <f>Dashboard!$C$5+(191-1)/12</f>
         <v/>
       </c>
@@ -8674,10 +8735,10 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="42" t="n">
+      <c r="A196" s="45" t="n">
         <v>192</v>
       </c>
-      <c r="B196" s="43">
+      <c r="B196" s="46">
         <f>Dashboard!$C$5+(192-1)/12</f>
         <v/>
       </c>
@@ -8703,10 +8764,10 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="42" t="n">
+      <c r="A197" s="45" t="n">
         <v>193</v>
       </c>
-      <c r="B197" s="43">
+      <c r="B197" s="46">
         <f>Dashboard!$C$5+(193-1)/12</f>
         <v/>
       </c>
@@ -8732,10 +8793,10 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="42" t="n">
+      <c r="A198" s="45" t="n">
         <v>194</v>
       </c>
-      <c r="B198" s="43">
+      <c r="B198" s="46">
         <f>Dashboard!$C$5+(194-1)/12</f>
         <v/>
       </c>
@@ -8761,10 +8822,10 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="42" t="n">
+      <c r="A199" s="45" t="n">
         <v>195</v>
       </c>
-      <c r="B199" s="43">
+      <c r="B199" s="46">
         <f>Dashboard!$C$5+(195-1)/12</f>
         <v/>
       </c>
@@ -8790,10 +8851,10 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="42" t="n">
+      <c r="A200" s="45" t="n">
         <v>196</v>
       </c>
-      <c r="B200" s="43">
+      <c r="B200" s="46">
         <f>Dashboard!$C$5+(196-1)/12</f>
         <v/>
       </c>
@@ -8819,10 +8880,10 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="42" t="n">
+      <c r="A201" s="45" t="n">
         <v>197</v>
       </c>
-      <c r="B201" s="43">
+      <c r="B201" s="46">
         <f>Dashboard!$C$5+(197-1)/12</f>
         <v/>
       </c>
@@ -8848,10 +8909,10 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="42" t="n">
+      <c r="A202" s="45" t="n">
         <v>198</v>
       </c>
-      <c r="B202" s="43">
+      <c r="B202" s="46">
         <f>Dashboard!$C$5+(198-1)/12</f>
         <v/>
       </c>
@@ -8877,10 +8938,10 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="42" t="n">
+      <c r="A203" s="45" t="n">
         <v>199</v>
       </c>
-      <c r="B203" s="43">
+      <c r="B203" s="46">
         <f>Dashboard!$C$5+(199-1)/12</f>
         <v/>
       </c>
@@ -8906,10 +8967,10 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="42" t="n">
+      <c r="A204" s="45" t="n">
         <v>200</v>
       </c>
-      <c r="B204" s="43">
+      <c r="B204" s="46">
         <f>Dashboard!$C$5+(200-1)/12</f>
         <v/>
       </c>
@@ -8935,10 +8996,10 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="42" t="n">
+      <c r="A205" s="45" t="n">
         <v>201</v>
       </c>
-      <c r="B205" s="43">
+      <c r="B205" s="46">
         <f>Dashboard!$C$5+(201-1)/12</f>
         <v/>
       </c>
@@ -8964,10 +9025,10 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="42" t="n">
+      <c r="A206" s="45" t="n">
         <v>202</v>
       </c>
-      <c r="B206" s="43">
+      <c r="B206" s="46">
         <f>Dashboard!$C$5+(202-1)/12</f>
         <v/>
       </c>
@@ -8993,10 +9054,10 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="42" t="n">
+      <c r="A207" s="45" t="n">
         <v>203</v>
       </c>
-      <c r="B207" s="43">
+      <c r="B207" s="46">
         <f>Dashboard!$C$5+(203-1)/12</f>
         <v/>
       </c>
@@ -9022,10 +9083,10 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="42" t="n">
+      <c r="A208" s="45" t="n">
         <v>204</v>
       </c>
-      <c r="B208" s="43">
+      <c r="B208" s="46">
         <f>Dashboard!$C$5+(204-1)/12</f>
         <v/>
       </c>
@@ -9051,10 +9112,10 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="42" t="n">
+      <c r="A209" s="45" t="n">
         <v>205</v>
       </c>
-      <c r="B209" s="43">
+      <c r="B209" s="46">
         <f>Dashboard!$C$5+(205-1)/12</f>
         <v/>
       </c>
@@ -9080,10 +9141,10 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="42" t="n">
+      <c r="A210" s="45" t="n">
         <v>206</v>
       </c>
-      <c r="B210" s="43">
+      <c r="B210" s="46">
         <f>Dashboard!$C$5+(206-1)/12</f>
         <v/>
       </c>
@@ -9109,10 +9170,10 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="42" t="n">
+      <c r="A211" s="45" t="n">
         <v>207</v>
       </c>
-      <c r="B211" s="43">
+      <c r="B211" s="46">
         <f>Dashboard!$C$5+(207-1)/12</f>
         <v/>
       </c>
@@ -9138,10 +9199,10 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="42" t="n">
+      <c r="A212" s="45" t="n">
         <v>208</v>
       </c>
-      <c r="B212" s="43">
+      <c r="B212" s="46">
         <f>Dashboard!$C$5+(208-1)/12</f>
         <v/>
       </c>
@@ -9167,10 +9228,10 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="42" t="n">
+      <c r="A213" s="45" t="n">
         <v>209</v>
       </c>
-      <c r="B213" s="43">
+      <c r="B213" s="46">
         <f>Dashboard!$C$5+(209-1)/12</f>
         <v/>
       </c>
@@ -9196,10 +9257,10 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="42" t="n">
+      <c r="A214" s="45" t="n">
         <v>210</v>
       </c>
-      <c r="B214" s="43">
+      <c r="B214" s="46">
         <f>Dashboard!$C$5+(210-1)/12</f>
         <v/>
       </c>
@@ -9225,10 +9286,10 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="42" t="n">
+      <c r="A215" s="45" t="n">
         <v>211</v>
       </c>
-      <c r="B215" s="43">
+      <c r="B215" s="46">
         <f>Dashboard!$C$5+(211-1)/12</f>
         <v/>
       </c>
@@ -9254,10 +9315,10 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="42" t="n">
+      <c r="A216" s="45" t="n">
         <v>212</v>
       </c>
-      <c r="B216" s="43">
+      <c r="B216" s="46">
         <f>Dashboard!$C$5+(212-1)/12</f>
         <v/>
       </c>
@@ -9283,10 +9344,10 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="42" t="n">
+      <c r="A217" s="45" t="n">
         <v>213</v>
       </c>
-      <c r="B217" s="43">
+      <c r="B217" s="46">
         <f>Dashboard!$C$5+(213-1)/12</f>
         <v/>
       </c>
@@ -9312,10 +9373,10 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="42" t="n">
+      <c r="A218" s="45" t="n">
         <v>214</v>
       </c>
-      <c r="B218" s="43">
+      <c r="B218" s="46">
         <f>Dashboard!$C$5+(214-1)/12</f>
         <v/>
       </c>
@@ -9341,10 +9402,10 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="42" t="n">
+      <c r="A219" s="45" t="n">
         <v>215</v>
       </c>
-      <c r="B219" s="43">
+      <c r="B219" s="46">
         <f>Dashboard!$C$5+(215-1)/12</f>
         <v/>
       </c>
@@ -9370,10 +9431,10 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="42" t="n">
+      <c r="A220" s="45" t="n">
         <v>216</v>
       </c>
-      <c r="B220" s="43">
+      <c r="B220" s="46">
         <f>Dashboard!$C$5+(216-1)/12</f>
         <v/>
       </c>
@@ -9399,10 +9460,10 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="42" t="n">
+      <c r="A221" s="45" t="n">
         <v>217</v>
       </c>
-      <c r="B221" s="43">
+      <c r="B221" s="46">
         <f>Dashboard!$C$5+(217-1)/12</f>
         <v/>
       </c>
@@ -9428,10 +9489,10 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="42" t="n">
+      <c r="A222" s="45" t="n">
         <v>218</v>
       </c>
-      <c r="B222" s="43">
+      <c r="B222" s="46">
         <f>Dashboard!$C$5+(218-1)/12</f>
         <v/>
       </c>
@@ -9457,10 +9518,10 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="42" t="n">
+      <c r="A223" s="45" t="n">
         <v>219</v>
       </c>
-      <c r="B223" s="43">
+      <c r="B223" s="46">
         <f>Dashboard!$C$5+(219-1)/12</f>
         <v/>
       </c>
@@ -9486,10 +9547,10 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="42" t="n">
+      <c r="A224" s="45" t="n">
         <v>220</v>
       </c>
-      <c r="B224" s="43">
+      <c r="B224" s="46">
         <f>Dashboard!$C$5+(220-1)/12</f>
         <v/>
       </c>
@@ -9515,10 +9576,10 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="42" t="n">
+      <c r="A225" s="45" t="n">
         <v>221</v>
       </c>
-      <c r="B225" s="43">
+      <c r="B225" s="46">
         <f>Dashboard!$C$5+(221-1)/12</f>
         <v/>
       </c>
@@ -9544,10 +9605,10 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="42" t="n">
+      <c r="A226" s="45" t="n">
         <v>222</v>
       </c>
-      <c r="B226" s="43">
+      <c r="B226" s="46">
         <f>Dashboard!$C$5+(222-1)/12</f>
         <v/>
       </c>
@@ -9573,10 +9634,10 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="42" t="n">
+      <c r="A227" s="45" t="n">
         <v>223</v>
       </c>
-      <c r="B227" s="43">
+      <c r="B227" s="46">
         <f>Dashboard!$C$5+(223-1)/12</f>
         <v/>
       </c>
@@ -9602,10 +9663,10 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="42" t="n">
+      <c r="A228" s="45" t="n">
         <v>224</v>
       </c>
-      <c r="B228" s="43">
+      <c r="B228" s="46">
         <f>Dashboard!$C$5+(224-1)/12</f>
         <v/>
       </c>
@@ -9631,10 +9692,10 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="42" t="n">
+      <c r="A229" s="45" t="n">
         <v>225</v>
       </c>
-      <c r="B229" s="43">
+      <c r="B229" s="46">
         <f>Dashboard!$C$5+(225-1)/12</f>
         <v/>
       </c>
@@ -9660,10 +9721,10 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="42" t="n">
+      <c r="A230" s="45" t="n">
         <v>226</v>
       </c>
-      <c r="B230" s="43">
+      <c r="B230" s="46">
         <f>Dashboard!$C$5+(226-1)/12</f>
         <v/>
       </c>
@@ -9689,10 +9750,10 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="42" t="n">
+      <c r="A231" s="45" t="n">
         <v>227</v>
       </c>
-      <c r="B231" s="43">
+      <c r="B231" s="46">
         <f>Dashboard!$C$5+(227-1)/12</f>
         <v/>
       </c>
@@ -9718,10 +9779,10 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="42" t="n">
+      <c r="A232" s="45" t="n">
         <v>228</v>
       </c>
-      <c r="B232" s="43">
+      <c r="B232" s="46">
         <f>Dashboard!$C$5+(228-1)/12</f>
         <v/>
       </c>
@@ -9747,10 +9808,10 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="42" t="n">
+      <c r="A233" s="45" t="n">
         <v>229</v>
       </c>
-      <c r="B233" s="43">
+      <c r="B233" s="46">
         <f>Dashboard!$C$5+(229-1)/12</f>
         <v/>
       </c>
@@ -9776,10 +9837,10 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="42" t="n">
+      <c r="A234" s="45" t="n">
         <v>230</v>
       </c>
-      <c r="B234" s="43">
+      <c r="B234" s="46">
         <f>Dashboard!$C$5+(230-1)/12</f>
         <v/>
       </c>
@@ -9805,10 +9866,10 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="42" t="n">
+      <c r="A235" s="45" t="n">
         <v>231</v>
       </c>
-      <c r="B235" s="43">
+      <c r="B235" s="46">
         <f>Dashboard!$C$5+(231-1)/12</f>
         <v/>
       </c>
@@ -9834,10 +9895,10 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="42" t="n">
+      <c r="A236" s="45" t="n">
         <v>232</v>
       </c>
-      <c r="B236" s="43">
+      <c r="B236" s="46">
         <f>Dashboard!$C$5+(232-1)/12</f>
         <v/>
       </c>
@@ -9863,10 +9924,10 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="42" t="n">
+      <c r="A237" s="45" t="n">
         <v>233</v>
       </c>
-      <c r="B237" s="43">
+      <c r="B237" s="46">
         <f>Dashboard!$C$5+(233-1)/12</f>
         <v/>
       </c>
@@ -9892,10 +9953,10 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="42" t="n">
+      <c r="A238" s="45" t="n">
         <v>234</v>
       </c>
-      <c r="B238" s="43">
+      <c r="B238" s="46">
         <f>Dashboard!$C$5+(234-1)/12</f>
         <v/>
       </c>
@@ -9921,10 +9982,10 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="42" t="n">
+      <c r="A239" s="45" t="n">
         <v>235</v>
       </c>
-      <c r="B239" s="43">
+      <c r="B239" s="46">
         <f>Dashboard!$C$5+(235-1)/12</f>
         <v/>
       </c>
@@ -9950,10 +10011,10 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="42" t="n">
+      <c r="A240" s="45" t="n">
         <v>236</v>
       </c>
-      <c r="B240" s="43">
+      <c r="B240" s="46">
         <f>Dashboard!$C$5+(236-1)/12</f>
         <v/>
       </c>
@@ -9979,10 +10040,10 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="42" t="n">
+      <c r="A241" s="45" t="n">
         <v>237</v>
       </c>
-      <c r="B241" s="43">
+      <c r="B241" s="46">
         <f>Dashboard!$C$5+(237-1)/12</f>
         <v/>
       </c>
@@ -10008,10 +10069,10 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="42" t="n">
+      <c r="A242" s="45" t="n">
         <v>238</v>
       </c>
-      <c r="B242" s="43">
+      <c r="B242" s="46">
         <f>Dashboard!$C$5+(238-1)/12</f>
         <v/>
       </c>
@@ -10037,10 +10098,10 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="42" t="n">
+      <c r="A243" s="45" t="n">
         <v>239</v>
       </c>
-      <c r="B243" s="43">
+      <c r="B243" s="46">
         <f>Dashboard!$C$5+(239-1)/12</f>
         <v/>
       </c>
@@ -10066,10 +10127,10 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="42" t="n">
+      <c r="A244" s="45" t="n">
         <v>240</v>
       </c>
-      <c r="B244" s="43">
+      <c r="B244" s="46">
         <f>Dashboard!$C$5+(240-1)/12</f>
         <v/>
       </c>
@@ -10095,10 +10156,10 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="42" t="n">
+      <c r="A245" s="45" t="n">
         <v>241</v>
       </c>
-      <c r="B245" s="43">
+      <c r="B245" s="46">
         <f>Dashboard!$C$5+(241-1)/12</f>
         <v/>
       </c>
@@ -10124,10 +10185,10 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="42" t="n">
+      <c r="A246" s="45" t="n">
         <v>242</v>
       </c>
-      <c r="B246" s="43">
+      <c r="B246" s="46">
         <f>Dashboard!$C$5+(242-1)/12</f>
         <v/>
       </c>
@@ -10153,10 +10214,10 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="42" t="n">
+      <c r="A247" s="45" t="n">
         <v>243</v>
       </c>
-      <c r="B247" s="43">
+      <c r="B247" s="46">
         <f>Dashboard!$C$5+(243-1)/12</f>
         <v/>
       </c>
@@ -10182,10 +10243,10 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="42" t="n">
+      <c r="A248" s="45" t="n">
         <v>244</v>
       </c>
-      <c r="B248" s="43">
+      <c r="B248" s="46">
         <f>Dashboard!$C$5+(244-1)/12</f>
         <v/>
       </c>
@@ -10211,10 +10272,10 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="42" t="n">
+      <c r="A249" s="45" t="n">
         <v>245</v>
       </c>
-      <c r="B249" s="43">
+      <c r="B249" s="46">
         <f>Dashboard!$C$5+(245-1)/12</f>
         <v/>
       </c>
@@ -10240,10 +10301,10 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="42" t="n">
+      <c r="A250" s="45" t="n">
         <v>246</v>
       </c>
-      <c r="B250" s="43">
+      <c r="B250" s="46">
         <f>Dashboard!$C$5+(246-1)/12</f>
         <v/>
       </c>
@@ -10269,10 +10330,10 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="42" t="n">
+      <c r="A251" s="45" t="n">
         <v>247</v>
       </c>
-      <c r="B251" s="43">
+      <c r="B251" s="46">
         <f>Dashboard!$C$5+(247-1)/12</f>
         <v/>
       </c>
@@ -10298,10 +10359,10 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="42" t="n">
+      <c r="A252" s="45" t="n">
         <v>248</v>
       </c>
-      <c r="B252" s="43">
+      <c r="B252" s="46">
         <f>Dashboard!$C$5+(248-1)/12</f>
         <v/>
       </c>
@@ -10327,10 +10388,10 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="42" t="n">
+      <c r="A253" s="45" t="n">
         <v>249</v>
       </c>
-      <c r="B253" s="43">
+      <c r="B253" s="46">
         <f>Dashboard!$C$5+(249-1)/12</f>
         <v/>
       </c>
@@ -10356,10 +10417,10 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="42" t="n">
+      <c r="A254" s="45" t="n">
         <v>250</v>
       </c>
-      <c r="B254" s="43">
+      <c r="B254" s="46">
         <f>Dashboard!$C$5+(250-1)/12</f>
         <v/>
       </c>
@@ -10385,10 +10446,10 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="42" t="n">
+      <c r="A255" s="45" t="n">
         <v>251</v>
       </c>
-      <c r="B255" s="43">
+      <c r="B255" s="46">
         <f>Dashboard!$C$5+(251-1)/12</f>
         <v/>
       </c>
@@ -10414,10 +10475,10 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="42" t="n">
+      <c r="A256" s="45" t="n">
         <v>252</v>
       </c>
-      <c r="B256" s="43">
+      <c r="B256" s="46">
         <f>Dashboard!$C$5+(252-1)/12</f>
         <v/>
       </c>
@@ -10443,10 +10504,10 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="42" t="n">
+      <c r="A257" s="45" t="n">
         <v>253</v>
       </c>
-      <c r="B257" s="43">
+      <c r="B257" s="46">
         <f>Dashboard!$C$5+(253-1)/12</f>
         <v/>
       </c>
@@ -10472,10 +10533,10 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="42" t="n">
+      <c r="A258" s="45" t="n">
         <v>254</v>
       </c>
-      <c r="B258" s="43">
+      <c r="B258" s="46">
         <f>Dashboard!$C$5+(254-1)/12</f>
         <v/>
       </c>
@@ -10501,10 +10562,10 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="42" t="n">
+      <c r="A259" s="45" t="n">
         <v>255</v>
       </c>
-      <c r="B259" s="43">
+      <c r="B259" s="46">
         <f>Dashboard!$C$5+(255-1)/12</f>
         <v/>
       </c>
@@ -10530,10 +10591,10 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="42" t="n">
+      <c r="A260" s="45" t="n">
         <v>256</v>
       </c>
-      <c r="B260" s="43">
+      <c r="B260" s="46">
         <f>Dashboard!$C$5+(256-1)/12</f>
         <v/>
       </c>
@@ -10559,10 +10620,10 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="42" t="n">
+      <c r="A261" s="45" t="n">
         <v>257</v>
       </c>
-      <c r="B261" s="43">
+      <c r="B261" s="46">
         <f>Dashboard!$C$5+(257-1)/12</f>
         <v/>
       </c>
@@ -10588,10 +10649,10 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="42" t="n">
+      <c r="A262" s="45" t="n">
         <v>258</v>
       </c>
-      <c r="B262" s="43">
+      <c r="B262" s="46">
         <f>Dashboard!$C$5+(258-1)/12</f>
         <v/>
       </c>
@@ -10617,10 +10678,10 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="42" t="n">
+      <c r="A263" s="45" t="n">
         <v>259</v>
       </c>
-      <c r="B263" s="43">
+      <c r="B263" s="46">
         <f>Dashboard!$C$5+(259-1)/12</f>
         <v/>
       </c>
@@ -10646,10 +10707,10 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="42" t="n">
+      <c r="A264" s="45" t="n">
         <v>260</v>
       </c>
-      <c r="B264" s="43">
+      <c r="B264" s="46">
         <f>Dashboard!$C$5+(260-1)/12</f>
         <v/>
       </c>
@@ -10675,10 +10736,10 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="42" t="n">
+      <c r="A265" s="45" t="n">
         <v>261</v>
       </c>
-      <c r="B265" s="43">
+      <c r="B265" s="46">
         <f>Dashboard!$C$5+(261-1)/12</f>
         <v/>
       </c>
@@ -10704,10 +10765,10 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="42" t="n">
+      <c r="A266" s="45" t="n">
         <v>262</v>
       </c>
-      <c r="B266" s="43">
+      <c r="B266" s="46">
         <f>Dashboard!$C$5+(262-1)/12</f>
         <v/>
       </c>
@@ -10733,10 +10794,10 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="42" t="n">
+      <c r="A267" s="45" t="n">
         <v>263</v>
       </c>
-      <c r="B267" s="43">
+      <c r="B267" s="46">
         <f>Dashboard!$C$5+(263-1)/12</f>
         <v/>
       </c>
@@ -10762,10 +10823,10 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="42" t="n">
+      <c r="A268" s="45" t="n">
         <v>264</v>
       </c>
-      <c r="B268" s="43">
+      <c r="B268" s="46">
         <f>Dashboard!$C$5+(264-1)/12</f>
         <v/>
       </c>
@@ -10791,10 +10852,10 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="42" t="n">
+      <c r="A269" s="45" t="n">
         <v>265</v>
       </c>
-      <c r="B269" s="43">
+      <c r="B269" s="46">
         <f>Dashboard!$C$5+(265-1)/12</f>
         <v/>
       </c>
@@ -10820,10 +10881,10 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="42" t="n">
+      <c r="A270" s="45" t="n">
         <v>266</v>
       </c>
-      <c r="B270" s="43">
+      <c r="B270" s="46">
         <f>Dashboard!$C$5+(266-1)/12</f>
         <v/>
       </c>
@@ -10849,10 +10910,10 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="42" t="n">
+      <c r="A271" s="45" t="n">
         <v>267</v>
       </c>
-      <c r="B271" s="43">
+      <c r="B271" s="46">
         <f>Dashboard!$C$5+(267-1)/12</f>
         <v/>
       </c>
@@ -10878,10 +10939,10 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="42" t="n">
+      <c r="A272" s="45" t="n">
         <v>268</v>
       </c>
-      <c r="B272" s="43">
+      <c r="B272" s="46">
         <f>Dashboard!$C$5+(268-1)/12</f>
         <v/>
       </c>
@@ -10907,10 +10968,10 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="42" t="n">
+      <c r="A273" s="45" t="n">
         <v>269</v>
       </c>
-      <c r="B273" s="43">
+      <c r="B273" s="46">
         <f>Dashboard!$C$5+(269-1)/12</f>
         <v/>
       </c>
@@ -10936,10 +10997,10 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="42" t="n">
+      <c r="A274" s="45" t="n">
         <v>270</v>
       </c>
-      <c r="B274" s="43">
+      <c r="B274" s="46">
         <f>Dashboard!$C$5+(270-1)/12</f>
         <v/>
       </c>
@@ -10965,10 +11026,10 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="42" t="n">
+      <c r="A275" s="45" t="n">
         <v>271</v>
       </c>
-      <c r="B275" s="43">
+      <c r="B275" s="46">
         <f>Dashboard!$C$5+(271-1)/12</f>
         <v/>
       </c>
@@ -10994,10 +11055,10 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="42" t="n">
+      <c r="A276" s="45" t="n">
         <v>272</v>
       </c>
-      <c r="B276" s="43">
+      <c r="B276" s="46">
         <f>Dashboard!$C$5+(272-1)/12</f>
         <v/>
       </c>
@@ -11023,10 +11084,10 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="42" t="n">
+      <c r="A277" s="45" t="n">
         <v>273</v>
       </c>
-      <c r="B277" s="43">
+      <c r="B277" s="46">
         <f>Dashboard!$C$5+(273-1)/12</f>
         <v/>
       </c>
@@ -11052,10 +11113,10 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="42" t="n">
+      <c r="A278" s="45" t="n">
         <v>274</v>
       </c>
-      <c r="B278" s="43">
+      <c r="B278" s="46">
         <f>Dashboard!$C$5+(274-1)/12</f>
         <v/>
       </c>
@@ -11081,10 +11142,10 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="42" t="n">
+      <c r="A279" s="45" t="n">
         <v>275</v>
       </c>
-      <c r="B279" s="43">
+      <c r="B279" s="46">
         <f>Dashboard!$C$5+(275-1)/12</f>
         <v/>
       </c>
@@ -11110,10 +11171,10 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="42" t="n">
+      <c r="A280" s="45" t="n">
         <v>276</v>
       </c>
-      <c r="B280" s="43">
+      <c r="B280" s="46">
         <f>Dashboard!$C$5+(276-1)/12</f>
         <v/>
       </c>
@@ -11139,10 +11200,10 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="42" t="n">
+      <c r="A281" s="45" t="n">
         <v>277</v>
       </c>
-      <c r="B281" s="43">
+      <c r="B281" s="46">
         <f>Dashboard!$C$5+(277-1)/12</f>
         <v/>
       </c>
@@ -11168,10 +11229,10 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="42" t="n">
+      <c r="A282" s="45" t="n">
         <v>278</v>
       </c>
-      <c r="B282" s="43">
+      <c r="B282" s="46">
         <f>Dashboard!$C$5+(278-1)/12</f>
         <v/>
       </c>
@@ -11197,10 +11258,10 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="42" t="n">
+      <c r="A283" s="45" t="n">
         <v>279</v>
       </c>
-      <c r="B283" s="43">
+      <c r="B283" s="46">
         <f>Dashboard!$C$5+(279-1)/12</f>
         <v/>
       </c>
@@ -11226,10 +11287,10 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="42" t="n">
+      <c r="A284" s="45" t="n">
         <v>280</v>
       </c>
-      <c r="B284" s="43">
+      <c r="B284" s="46">
         <f>Dashboard!$C$5+(280-1)/12</f>
         <v/>
       </c>
@@ -11255,10 +11316,10 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="42" t="n">
+      <c r="A285" s="45" t="n">
         <v>281</v>
       </c>
-      <c r="B285" s="43">
+      <c r="B285" s="46">
         <f>Dashboard!$C$5+(281-1)/12</f>
         <v/>
       </c>
@@ -11284,10 +11345,10 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="42" t="n">
+      <c r="A286" s="45" t="n">
         <v>282</v>
       </c>
-      <c r="B286" s="43">
+      <c r="B286" s="46">
         <f>Dashboard!$C$5+(282-1)/12</f>
         <v/>
       </c>
@@ -11313,10 +11374,10 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="42" t="n">
+      <c r="A287" s="45" t="n">
         <v>283</v>
       </c>
-      <c r="B287" s="43">
+      <c r="B287" s="46">
         <f>Dashboard!$C$5+(283-1)/12</f>
         <v/>
       </c>
@@ -11342,10 +11403,10 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="42" t="n">
+      <c r="A288" s="45" t="n">
         <v>284</v>
       </c>
-      <c r="B288" s="43">
+      <c r="B288" s="46">
         <f>Dashboard!$C$5+(284-1)/12</f>
         <v/>
       </c>
@@ -11371,10 +11432,10 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="42" t="n">
+      <c r="A289" s="45" t="n">
         <v>285</v>
       </c>
-      <c r="B289" s="43">
+      <c r="B289" s="46">
         <f>Dashboard!$C$5+(285-1)/12</f>
         <v/>
       </c>
@@ -11400,10 +11461,10 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="42" t="n">
+      <c r="A290" s="45" t="n">
         <v>286</v>
       </c>
-      <c r="B290" s="43">
+      <c r="B290" s="46">
         <f>Dashboard!$C$5+(286-1)/12</f>
         <v/>
       </c>
@@ -11429,10 +11490,10 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="42" t="n">
+      <c r="A291" s="45" t="n">
         <v>287</v>
       </c>
-      <c r="B291" s="43">
+      <c r="B291" s="46">
         <f>Dashboard!$C$5+(287-1)/12</f>
         <v/>
       </c>
@@ -11458,10 +11519,10 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="42" t="n">
+      <c r="A292" s="45" t="n">
         <v>288</v>
       </c>
-      <c r="B292" s="43">
+      <c r="B292" s="46">
         <f>Dashboard!$C$5+(288-1)/12</f>
         <v/>
       </c>
@@ -11487,10 +11548,10 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="42" t="n">
+      <c r="A293" s="45" t="n">
         <v>289</v>
       </c>
-      <c r="B293" s="43">
+      <c r="B293" s="46">
         <f>Dashboard!$C$5+(289-1)/12</f>
         <v/>
       </c>
@@ -11516,10 +11577,10 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="42" t="n">
+      <c r="A294" s="45" t="n">
         <v>290</v>
       </c>
-      <c r="B294" s="43">
+      <c r="B294" s="46">
         <f>Dashboard!$C$5+(290-1)/12</f>
         <v/>
       </c>
@@ -11545,10 +11606,10 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="42" t="n">
+      <c r="A295" s="45" t="n">
         <v>291</v>
       </c>
-      <c r="B295" s="43">
+      <c r="B295" s="46">
         <f>Dashboard!$C$5+(291-1)/12</f>
         <v/>
       </c>
@@ -11574,10 +11635,10 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="42" t="n">
+      <c r="A296" s="45" t="n">
         <v>292</v>
       </c>
-      <c r="B296" s="43">
+      <c r="B296" s="46">
         <f>Dashboard!$C$5+(292-1)/12</f>
         <v/>
       </c>
@@ -11603,10 +11664,10 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="42" t="n">
+      <c r="A297" s="45" t="n">
         <v>293</v>
       </c>
-      <c r="B297" s="43">
+      <c r="B297" s="46">
         <f>Dashboard!$C$5+(293-1)/12</f>
         <v/>
       </c>
@@ -11632,10 +11693,10 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="42" t="n">
+      <c r="A298" s="45" t="n">
         <v>294</v>
       </c>
-      <c r="B298" s="43">
+      <c r="B298" s="46">
         <f>Dashboard!$C$5+(294-1)/12</f>
         <v/>
       </c>
@@ -11661,10 +11722,10 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="42" t="n">
+      <c r="A299" s="45" t="n">
         <v>295</v>
       </c>
-      <c r="B299" s="43">
+      <c r="B299" s="46">
         <f>Dashboard!$C$5+(295-1)/12</f>
         <v/>
       </c>
@@ -11690,10 +11751,10 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="42" t="n">
+      <c r="A300" s="45" t="n">
         <v>296</v>
       </c>
-      <c r="B300" s="43">
+      <c r="B300" s="46">
         <f>Dashboard!$C$5+(296-1)/12</f>
         <v/>
       </c>
@@ -11719,10 +11780,10 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="42" t="n">
+      <c r="A301" s="45" t="n">
         <v>297</v>
       </c>
-      <c r="B301" s="43">
+      <c r="B301" s="46">
         <f>Dashboard!$C$5+(297-1)/12</f>
         <v/>
       </c>
@@ -11748,10 +11809,10 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="42" t="n">
+      <c r="A302" s="45" t="n">
         <v>298</v>
       </c>
-      <c r="B302" s="43">
+      <c r="B302" s="46">
         <f>Dashboard!$C$5+(298-1)/12</f>
         <v/>
       </c>
@@ -11777,10 +11838,10 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="42" t="n">
+      <c r="A303" s="45" t="n">
         <v>299</v>
       </c>
-      <c r="B303" s="43">
+      <c r="B303" s="46">
         <f>Dashboard!$C$5+(299-1)/12</f>
         <v/>
       </c>
@@ -11806,10 +11867,10 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="42" t="n">
+      <c r="A304" s="45" t="n">
         <v>300</v>
       </c>
-      <c r="B304" s="43">
+      <c r="B304" s="46">
         <f>Dashboard!$C$5+(300-1)/12</f>
         <v/>
       </c>
@@ -11835,10 +11896,10 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="42" t="n">
+      <c r="A305" s="45" t="n">
         <v>301</v>
       </c>
-      <c r="B305" s="43">
+      <c r="B305" s="46">
         <f>Dashboard!$C$5+(301-1)/12</f>
         <v/>
       </c>
@@ -11864,10 +11925,10 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="42" t="n">
+      <c r="A306" s="45" t="n">
         <v>302</v>
       </c>
-      <c r="B306" s="43">
+      <c r="B306" s="46">
         <f>Dashboard!$C$5+(302-1)/12</f>
         <v/>
       </c>
@@ -11893,10 +11954,10 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="42" t="n">
+      <c r="A307" s="45" t="n">
         <v>303</v>
       </c>
-      <c r="B307" s="43">
+      <c r="B307" s="46">
         <f>Dashboard!$C$5+(303-1)/12</f>
         <v/>
       </c>
@@ -11922,10 +11983,10 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="42" t="n">
+      <c r="A308" s="45" t="n">
         <v>304</v>
       </c>
-      <c r="B308" s="43">
+      <c r="B308" s="46">
         <f>Dashboard!$C$5+(304-1)/12</f>
         <v/>
       </c>
@@ -11951,10 +12012,10 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="42" t="n">
+      <c r="A309" s="45" t="n">
         <v>305</v>
       </c>
-      <c r="B309" s="43">
+      <c r="B309" s="46">
         <f>Dashboard!$C$5+(305-1)/12</f>
         <v/>
       </c>
@@ -11980,10 +12041,10 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="42" t="n">
+      <c r="A310" s="45" t="n">
         <v>306</v>
       </c>
-      <c r="B310" s="43">
+      <c r="B310" s="46">
         <f>Dashboard!$C$5+(306-1)/12</f>
         <v/>
       </c>
@@ -12009,10 +12070,10 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="42" t="n">
+      <c r="A311" s="45" t="n">
         <v>307</v>
       </c>
-      <c r="B311" s="43">
+      <c r="B311" s="46">
         <f>Dashboard!$C$5+(307-1)/12</f>
         <v/>
       </c>
@@ -12038,10 +12099,10 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="42" t="n">
+      <c r="A312" s="45" t="n">
         <v>308</v>
       </c>
-      <c r="B312" s="43">
+      <c r="B312" s="46">
         <f>Dashboard!$C$5+(308-1)/12</f>
         <v/>
       </c>
@@ -12067,10 +12128,10 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="42" t="n">
+      <c r="A313" s="45" t="n">
         <v>309</v>
       </c>
-      <c r="B313" s="43">
+      <c r="B313" s="46">
         <f>Dashboard!$C$5+(309-1)/12</f>
         <v/>
       </c>
@@ -12096,10 +12157,10 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="42" t="n">
+      <c r="A314" s="45" t="n">
         <v>310</v>
       </c>
-      <c r="B314" s="43">
+      <c r="B314" s="46">
         <f>Dashboard!$C$5+(310-1)/12</f>
         <v/>
       </c>
@@ -12125,10 +12186,10 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="42" t="n">
+      <c r="A315" s="45" t="n">
         <v>311</v>
       </c>
-      <c r="B315" s="43">
+      <c r="B315" s="46">
         <f>Dashboard!$C$5+(311-1)/12</f>
         <v/>
       </c>
@@ -12154,10 +12215,10 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="42" t="n">
+      <c r="A316" s="45" t="n">
         <v>312</v>
       </c>
-      <c r="B316" s="43">
+      <c r="B316" s="46">
         <f>Dashboard!$C$5+(312-1)/12</f>
         <v/>
       </c>
@@ -12183,10 +12244,10 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="42" t="n">
+      <c r="A317" s="45" t="n">
         <v>313</v>
       </c>
-      <c r="B317" s="43">
+      <c r="B317" s="46">
         <f>Dashboard!$C$5+(313-1)/12</f>
         <v/>
       </c>
@@ -12212,10 +12273,10 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="42" t="n">
+      <c r="A318" s="45" t="n">
         <v>314</v>
       </c>
-      <c r="B318" s="43">
+      <c r="B318" s="46">
         <f>Dashboard!$C$5+(314-1)/12</f>
         <v/>
       </c>
@@ -12241,10 +12302,10 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="42" t="n">
+      <c r="A319" s="45" t="n">
         <v>315</v>
       </c>
-      <c r="B319" s="43">
+      <c r="B319" s="46">
         <f>Dashboard!$C$5+(315-1)/12</f>
         <v/>
       </c>
@@ -12270,10 +12331,10 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="42" t="n">
+      <c r="A320" s="45" t="n">
         <v>316</v>
       </c>
-      <c r="B320" s="43">
+      <c r="B320" s="46">
         <f>Dashboard!$C$5+(316-1)/12</f>
         <v/>
       </c>
@@ -12299,10 +12360,10 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="42" t="n">
+      <c r="A321" s="45" t="n">
         <v>317</v>
       </c>
-      <c r="B321" s="43">
+      <c r="B321" s="46">
         <f>Dashboard!$C$5+(317-1)/12</f>
         <v/>
       </c>
@@ -12328,10 +12389,10 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="42" t="n">
+      <c r="A322" s="45" t="n">
         <v>318</v>
       </c>
-      <c r="B322" s="43">
+      <c r="B322" s="46">
         <f>Dashboard!$C$5+(318-1)/12</f>
         <v/>
       </c>
@@ -12357,10 +12418,10 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="42" t="n">
+      <c r="A323" s="45" t="n">
         <v>319</v>
       </c>
-      <c r="B323" s="43">
+      <c r="B323" s="46">
         <f>Dashboard!$C$5+(319-1)/12</f>
         <v/>
       </c>
@@ -12386,10 +12447,10 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="42" t="n">
+      <c r="A324" s="45" t="n">
         <v>320</v>
       </c>
-      <c r="B324" s="43">
+      <c r="B324" s="46">
         <f>Dashboard!$C$5+(320-1)/12</f>
         <v/>
       </c>
@@ -12415,10 +12476,10 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="42" t="n">
+      <c r="A325" s="45" t="n">
         <v>321</v>
       </c>
-      <c r="B325" s="43">
+      <c r="B325" s="46">
         <f>Dashboard!$C$5+(321-1)/12</f>
         <v/>
       </c>
@@ -12444,10 +12505,10 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="42" t="n">
+      <c r="A326" s="45" t="n">
         <v>322</v>
       </c>
-      <c r="B326" s="43">
+      <c r="B326" s="46">
         <f>Dashboard!$C$5+(322-1)/12</f>
         <v/>
       </c>
@@ -12473,10 +12534,10 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="42" t="n">
+      <c r="A327" s="45" t="n">
         <v>323</v>
       </c>
-      <c r="B327" s="43">
+      <c r="B327" s="46">
         <f>Dashboard!$C$5+(323-1)/12</f>
         <v/>
       </c>
@@ -12502,10 +12563,10 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="42" t="n">
+      <c r="A328" s="45" t="n">
         <v>324</v>
       </c>
-      <c r="B328" s="43">
+      <c r="B328" s="46">
         <f>Dashboard!$C$5+(324-1)/12</f>
         <v/>
       </c>
@@ -12531,10 +12592,10 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="42" t="n">
+      <c r="A329" s="45" t="n">
         <v>325</v>
       </c>
-      <c r="B329" s="43">
+      <c r="B329" s="46">
         <f>Dashboard!$C$5+(325-1)/12</f>
         <v/>
       </c>
@@ -12560,10 +12621,10 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="42" t="n">
+      <c r="A330" s="45" t="n">
         <v>326</v>
       </c>
-      <c r="B330" s="43">
+      <c r="B330" s="46">
         <f>Dashboard!$C$5+(326-1)/12</f>
         <v/>
       </c>
@@ -12589,10 +12650,10 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="42" t="n">
+      <c r="A331" s="45" t="n">
         <v>327</v>
       </c>
-      <c r="B331" s="43">
+      <c r="B331" s="46">
         <f>Dashboard!$C$5+(327-1)/12</f>
         <v/>
       </c>
@@ -12618,10 +12679,10 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="42" t="n">
+      <c r="A332" s="45" t="n">
         <v>328</v>
       </c>
-      <c r="B332" s="43">
+      <c r="B332" s="46">
         <f>Dashboard!$C$5+(328-1)/12</f>
         <v/>
       </c>
@@ -12647,10 +12708,10 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="42" t="n">
+      <c r="A333" s="45" t="n">
         <v>329</v>
       </c>
-      <c r="B333" s="43">
+      <c r="B333" s="46">
         <f>Dashboard!$C$5+(329-1)/12</f>
         <v/>
       </c>
@@ -12676,10 +12737,10 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="42" t="n">
+      <c r="A334" s="45" t="n">
         <v>330</v>
       </c>
-      <c r="B334" s="43">
+      <c r="B334" s="46">
         <f>Dashboard!$C$5+(330-1)/12</f>
         <v/>
       </c>
@@ -12705,10 +12766,10 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="42" t="n">
+      <c r="A335" s="45" t="n">
         <v>331</v>
       </c>
-      <c r="B335" s="43">
+      <c r="B335" s="46">
         <f>Dashboard!$C$5+(331-1)/12</f>
         <v/>
       </c>
@@ -12734,10 +12795,10 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="42" t="n">
+      <c r="A336" s="45" t="n">
         <v>332</v>
       </c>
-      <c r="B336" s="43">
+      <c r="B336" s="46">
         <f>Dashboard!$C$5+(332-1)/12</f>
         <v/>
       </c>
@@ -12763,10 +12824,10 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="42" t="n">
+      <c r="A337" s="45" t="n">
         <v>333</v>
       </c>
-      <c r="B337" s="43">
+      <c r="B337" s="46">
         <f>Dashboard!$C$5+(333-1)/12</f>
         <v/>
       </c>
@@ -12792,10 +12853,10 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="42" t="n">
+      <c r="A338" s="45" t="n">
         <v>334</v>
       </c>
-      <c r="B338" s="43">
+      <c r="B338" s="46">
         <f>Dashboard!$C$5+(334-1)/12</f>
         <v/>
       </c>
@@ -12821,10 +12882,10 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="42" t="n">
+      <c r="A339" s="45" t="n">
         <v>335</v>
       </c>
-      <c r="B339" s="43">
+      <c r="B339" s="46">
         <f>Dashboard!$C$5+(335-1)/12</f>
         <v/>
       </c>
@@ -12850,10 +12911,10 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="42" t="n">
+      <c r="A340" s="45" t="n">
         <v>336</v>
       </c>
-      <c r="B340" s="43">
+      <c r="B340" s="46">
         <f>Dashboard!$C$5+(336-1)/12</f>
         <v/>
       </c>
@@ -12879,10 +12940,10 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="42" t="n">
+      <c r="A341" s="45" t="n">
         <v>337</v>
       </c>
-      <c r="B341" s="43">
+      <c r="B341" s="46">
         <f>Dashboard!$C$5+(337-1)/12</f>
         <v/>
       </c>
@@ -12908,10 +12969,10 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="42" t="n">
+      <c r="A342" s="45" t="n">
         <v>338</v>
       </c>
-      <c r="B342" s="43">
+      <c r="B342" s="46">
         <f>Dashboard!$C$5+(338-1)/12</f>
         <v/>
       </c>
@@ -12937,10 +12998,10 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="42" t="n">
+      <c r="A343" s="45" t="n">
         <v>339</v>
       </c>
-      <c r="B343" s="43">
+      <c r="B343" s="46">
         <f>Dashboard!$C$5+(339-1)/12</f>
         <v/>
       </c>
@@ -12966,10 +13027,10 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="42" t="n">
+      <c r="A344" s="45" t="n">
         <v>340</v>
       </c>
-      <c r="B344" s="43">
+      <c r="B344" s="46">
         <f>Dashboard!$C$5+(340-1)/12</f>
         <v/>
       </c>
@@ -12995,10 +13056,10 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="42" t="n">
+      <c r="A345" s="45" t="n">
         <v>341</v>
       </c>
-      <c r="B345" s="43">
+      <c r="B345" s="46">
         <f>Dashboard!$C$5+(341-1)/12</f>
         <v/>
       </c>
@@ -13024,10 +13085,10 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="42" t="n">
+      <c r="A346" s="45" t="n">
         <v>342</v>
       </c>
-      <c r="B346" s="43">
+      <c r="B346" s="46">
         <f>Dashboard!$C$5+(342-1)/12</f>
         <v/>
       </c>
@@ -13053,10 +13114,10 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="42" t="n">
+      <c r="A347" s="45" t="n">
         <v>343</v>
       </c>
-      <c r="B347" s="43">
+      <c r="B347" s="46">
         <f>Dashboard!$C$5+(343-1)/12</f>
         <v/>
       </c>
@@ -13082,10 +13143,10 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="42" t="n">
+      <c r="A348" s="45" t="n">
         <v>344</v>
       </c>
-      <c r="B348" s="43">
+      <c r="B348" s="46">
         <f>Dashboard!$C$5+(344-1)/12</f>
         <v/>
       </c>
@@ -13111,10 +13172,10 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="42" t="n">
+      <c r="A349" s="45" t="n">
         <v>345</v>
       </c>
-      <c r="B349" s="43">
+      <c r="B349" s="46">
         <f>Dashboard!$C$5+(345-1)/12</f>
         <v/>
       </c>
@@ -13140,10 +13201,10 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="42" t="n">
+      <c r="A350" s="45" t="n">
         <v>346</v>
       </c>
-      <c r="B350" s="43">
+      <c r="B350" s="46">
         <f>Dashboard!$C$5+(346-1)/12</f>
         <v/>
       </c>
@@ -13169,10 +13230,10 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="42" t="n">
+      <c r="A351" s="45" t="n">
         <v>347</v>
       </c>
-      <c r="B351" s="43">
+      <c r="B351" s="46">
         <f>Dashboard!$C$5+(347-1)/12</f>
         <v/>
       </c>
@@ -13198,10 +13259,10 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="42" t="n">
+      <c r="A352" s="45" t="n">
         <v>348</v>
       </c>
-      <c r="B352" s="43">
+      <c r="B352" s="46">
         <f>Dashboard!$C$5+(348-1)/12</f>
         <v/>
       </c>
@@ -13227,10 +13288,10 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="42" t="n">
+      <c r="A353" s="45" t="n">
         <v>349</v>
       </c>
-      <c r="B353" s="43">
+      <c r="B353" s="46">
         <f>Dashboard!$C$5+(349-1)/12</f>
         <v/>
       </c>
@@ -13256,10 +13317,10 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="42" t="n">
+      <c r="A354" s="45" t="n">
         <v>350</v>
       </c>
-      <c r="B354" s="43">
+      <c r="B354" s="46">
         <f>Dashboard!$C$5+(350-1)/12</f>
         <v/>
       </c>
@@ -13285,10 +13346,10 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="42" t="n">
+      <c r="A355" s="45" t="n">
         <v>351</v>
       </c>
-      <c r="B355" s="43">
+      <c r="B355" s="46">
         <f>Dashboard!$C$5+(351-1)/12</f>
         <v/>
       </c>
@@ -13314,10 +13375,10 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="42" t="n">
+      <c r="A356" s="45" t="n">
         <v>352</v>
       </c>
-      <c r="B356" s="43">
+      <c r="B356" s="46">
         <f>Dashboard!$C$5+(352-1)/12</f>
         <v/>
       </c>
@@ -13343,10 +13404,10 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="42" t="n">
+      <c r="A357" s="45" t="n">
         <v>353</v>
       </c>
-      <c r="B357" s="43">
+      <c r="B357" s="46">
         <f>Dashboard!$C$5+(353-1)/12</f>
         <v/>
       </c>
@@ -13372,10 +13433,10 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="42" t="n">
+      <c r="A358" s="45" t="n">
         <v>354</v>
       </c>
-      <c r="B358" s="43">
+      <c r="B358" s="46">
         <f>Dashboard!$C$5+(354-1)/12</f>
         <v/>
       </c>
@@ -13401,10 +13462,10 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="42" t="n">
+      <c r="A359" s="45" t="n">
         <v>355</v>
       </c>
-      <c r="B359" s="43">
+      <c r="B359" s="46">
         <f>Dashboard!$C$5+(355-1)/12</f>
         <v/>
       </c>
@@ -13430,10 +13491,10 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="42" t="n">
+      <c r="A360" s="45" t="n">
         <v>356</v>
       </c>
-      <c r="B360" s="43">
+      <c r="B360" s="46">
         <f>Dashboard!$C$5+(356-1)/12</f>
         <v/>
       </c>
@@ -13459,10 +13520,10 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="42" t="n">
+      <c r="A361" s="45" t="n">
         <v>357</v>
       </c>
-      <c r="B361" s="43">
+      <c r="B361" s="46">
         <f>Dashboard!$C$5+(357-1)/12</f>
         <v/>
       </c>
@@ -13488,10 +13549,10 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="42" t="n">
+      <c r="A362" s="45" t="n">
         <v>358</v>
       </c>
-      <c r="B362" s="43">
+      <c r="B362" s="46">
         <f>Dashboard!$C$5+(358-1)/12</f>
         <v/>
       </c>
@@ -13517,10 +13578,10 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="42" t="n">
+      <c r="A363" s="45" t="n">
         <v>359</v>
       </c>
-      <c r="B363" s="43">
+      <c r="B363" s="46">
         <f>Dashboard!$C$5+(359-1)/12</f>
         <v/>
       </c>
@@ -13546,10 +13607,10 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="42" t="n">
+      <c r="A364" s="45" t="n">
         <v>360</v>
       </c>
-      <c r="B364" s="43">
+      <c r="B364" s="46">
         <f>Dashboard!$C$5+(360-1)/12</f>
         <v/>
       </c>
@@ -13575,10 +13636,10 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="42" t="n">
+      <c r="A365" s="45" t="n">
         <v>361</v>
       </c>
-      <c r="B365" s="43">
+      <c r="B365" s="46">
         <f>Dashboard!$C$5+(361-1)/12</f>
         <v/>
       </c>
@@ -13604,10 +13665,10 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="42" t="n">
+      <c r="A366" s="45" t="n">
         <v>362</v>
       </c>
-      <c r="B366" s="43">
+      <c r="B366" s="46">
         <f>Dashboard!$C$5+(362-1)/12</f>
         <v/>
       </c>
@@ -13633,10 +13694,10 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="42" t="n">
+      <c r="A367" s="45" t="n">
         <v>363</v>
       </c>
-      <c r="B367" s="43">
+      <c r="B367" s="46">
         <f>Dashboard!$C$5+(363-1)/12</f>
         <v/>
       </c>
@@ -13662,10 +13723,10 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="42" t="n">
+      <c r="A368" s="45" t="n">
         <v>364</v>
       </c>
-      <c r="B368" s="43">
+      <c r="B368" s="46">
         <f>Dashboard!$C$5+(364-1)/12</f>
         <v/>
       </c>
@@ -13691,10 +13752,10 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="42" t="n">
+      <c r="A369" s="45" t="n">
         <v>365</v>
       </c>
-      <c r="B369" s="43">
+      <c r="B369" s="46">
         <f>Dashboard!$C$5+(365-1)/12</f>
         <v/>
       </c>
@@ -13720,10 +13781,10 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="42" t="n">
+      <c r="A370" s="45" t="n">
         <v>366</v>
       </c>
-      <c r="B370" s="43">
+      <c r="B370" s="46">
         <f>Dashboard!$C$5+(366-1)/12</f>
         <v/>
       </c>
@@ -13749,10 +13810,10 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="42" t="n">
+      <c r="A371" s="45" t="n">
         <v>367</v>
       </c>
-      <c r="B371" s="43">
+      <c r="B371" s="46">
         <f>Dashboard!$C$5+(367-1)/12</f>
         <v/>
       </c>
@@ -13778,10 +13839,10 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="42" t="n">
+      <c r="A372" s="45" t="n">
         <v>368</v>
       </c>
-      <c r="B372" s="43">
+      <c r="B372" s="46">
         <f>Dashboard!$C$5+(368-1)/12</f>
         <v/>
       </c>
@@ -13807,10 +13868,10 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="42" t="n">
+      <c r="A373" s="45" t="n">
         <v>369</v>
       </c>
-      <c r="B373" s="43">
+      <c r="B373" s="46">
         <f>Dashboard!$C$5+(369-1)/12</f>
         <v/>
       </c>
@@ -13836,10 +13897,10 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="42" t="n">
+      <c r="A374" s="45" t="n">
         <v>370</v>
       </c>
-      <c r="B374" s="43">
+      <c r="B374" s="46">
         <f>Dashboard!$C$5+(370-1)/12</f>
         <v/>
       </c>
@@ -13865,10 +13926,10 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="42" t="n">
+      <c r="A375" s="45" t="n">
         <v>371</v>
       </c>
-      <c r="B375" s="43">
+      <c r="B375" s="46">
         <f>Dashboard!$C$5+(371-1)/12</f>
         <v/>
       </c>
@@ -13894,10 +13955,10 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="42" t="n">
+      <c r="A376" s="45" t="n">
         <v>372</v>
       </c>
-      <c r="B376" s="43">
+      <c r="B376" s="46">
         <f>Dashboard!$C$5+(372-1)/12</f>
         <v/>
       </c>
@@ -13923,10 +13984,10 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="42" t="n">
+      <c r="A377" s="45" t="n">
         <v>373</v>
       </c>
-      <c r="B377" s="43">
+      <c r="B377" s="46">
         <f>Dashboard!$C$5+(373-1)/12</f>
         <v/>
       </c>
@@ -13952,10 +14013,10 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="42" t="n">
+      <c r="A378" s="45" t="n">
         <v>374</v>
       </c>
-      <c r="B378" s="43">
+      <c r="B378" s="46">
         <f>Dashboard!$C$5+(374-1)/12</f>
         <v/>
       </c>
@@ -13981,10 +14042,10 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="42" t="n">
+      <c r="A379" s="45" t="n">
         <v>375</v>
       </c>
-      <c r="B379" s="43">
+      <c r="B379" s="46">
         <f>Dashboard!$C$5+(375-1)/12</f>
         <v/>
       </c>
@@ -14010,10 +14071,10 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="42" t="n">
+      <c r="A380" s="45" t="n">
         <v>376</v>
       </c>
-      <c r="B380" s="43">
+      <c r="B380" s="46">
         <f>Dashboard!$C$5+(376-1)/12</f>
         <v/>
       </c>
@@ -14039,10 +14100,10 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="42" t="n">
+      <c r="A381" s="45" t="n">
         <v>377</v>
       </c>
-      <c r="B381" s="43">
+      <c r="B381" s="46">
         <f>Dashboard!$C$5+(377-1)/12</f>
         <v/>
       </c>
@@ -14068,10 +14129,10 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="42" t="n">
+      <c r="A382" s="45" t="n">
         <v>378</v>
       </c>
-      <c r="B382" s="43">
+      <c r="B382" s="46">
         <f>Dashboard!$C$5+(378-1)/12</f>
         <v/>
       </c>
@@ -14097,10 +14158,10 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="42" t="n">
+      <c r="A383" s="45" t="n">
         <v>379</v>
       </c>
-      <c r="B383" s="43">
+      <c r="B383" s="46">
         <f>Dashboard!$C$5+(379-1)/12</f>
         <v/>
       </c>
@@ -14126,10 +14187,10 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="42" t="n">
+      <c r="A384" s="45" t="n">
         <v>380</v>
       </c>
-      <c r="B384" s="43">
+      <c r="B384" s="46">
         <f>Dashboard!$C$5+(380-1)/12</f>
         <v/>
       </c>
@@ -14155,10 +14216,10 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="42" t="n">
+      <c r="A385" s="45" t="n">
         <v>381</v>
       </c>
-      <c r="B385" s="43">
+      <c r="B385" s="46">
         <f>Dashboard!$C$5+(381-1)/12</f>
         <v/>
       </c>
@@ -14184,10 +14245,10 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="42" t="n">
+      <c r="A386" s="45" t="n">
         <v>382</v>
       </c>
-      <c r="B386" s="43">
+      <c r="B386" s="46">
         <f>Dashboard!$C$5+(382-1)/12</f>
         <v/>
       </c>
@@ -14213,10 +14274,10 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="42" t="n">
+      <c r="A387" s="45" t="n">
         <v>383</v>
       </c>
-      <c r="B387" s="43">
+      <c r="B387" s="46">
         <f>Dashboard!$C$5+(383-1)/12</f>
         <v/>
       </c>
@@ -14242,10 +14303,10 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="42" t="n">
+      <c r="A388" s="45" t="n">
         <v>384</v>
       </c>
-      <c r="B388" s="43">
+      <c r="B388" s="46">
         <f>Dashboard!$C$5+(384-1)/12</f>
         <v/>
       </c>
@@ -14271,10 +14332,10 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="42" t="n">
+      <c r="A389" s="45" t="n">
         <v>385</v>
       </c>
-      <c r="B389" s="43">
+      <c r="B389" s="46">
         <f>Dashboard!$C$5+(385-1)/12</f>
         <v/>
       </c>
@@ -14300,10 +14361,10 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="42" t="n">
+      <c r="A390" s="45" t="n">
         <v>386</v>
       </c>
-      <c r="B390" s="43">
+      <c r="B390" s="46">
         <f>Dashboard!$C$5+(386-1)/12</f>
         <v/>
       </c>
@@ -14329,10 +14390,10 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="42" t="n">
+      <c r="A391" s="45" t="n">
         <v>387</v>
       </c>
-      <c r="B391" s="43">
+      <c r="B391" s="46">
         <f>Dashboard!$C$5+(387-1)/12</f>
         <v/>
       </c>
@@ -14358,10 +14419,10 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="42" t="n">
+      <c r="A392" s="45" t="n">
         <v>388</v>
       </c>
-      <c r="B392" s="43">
+      <c r="B392" s="46">
         <f>Dashboard!$C$5+(388-1)/12</f>
         <v/>
       </c>
@@ -14387,10 +14448,10 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="42" t="n">
+      <c r="A393" s="45" t="n">
         <v>389</v>
       </c>
-      <c r="B393" s="43">
+      <c r="B393" s="46">
         <f>Dashboard!$C$5+(389-1)/12</f>
         <v/>
       </c>
@@ -14416,10 +14477,10 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="42" t="n">
+      <c r="A394" s="45" t="n">
         <v>390</v>
       </c>
-      <c r="B394" s="43">
+      <c r="B394" s="46">
         <f>Dashboard!$C$5+(390-1)/12</f>
         <v/>
       </c>
@@ -14445,10 +14506,10 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="42" t="n">
+      <c r="A395" s="45" t="n">
         <v>391</v>
       </c>
-      <c r="B395" s="43">
+      <c r="B395" s="46">
         <f>Dashboard!$C$5+(391-1)/12</f>
         <v/>
       </c>
@@ -14474,10 +14535,10 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="42" t="n">
+      <c r="A396" s="45" t="n">
         <v>392</v>
       </c>
-      <c r="B396" s="43">
+      <c r="B396" s="46">
         <f>Dashboard!$C$5+(392-1)/12</f>
         <v/>
       </c>
@@ -14503,10 +14564,10 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="42" t="n">
+      <c r="A397" s="45" t="n">
         <v>393</v>
       </c>
-      <c r="B397" s="43">
+      <c r="B397" s="46">
         <f>Dashboard!$C$5+(393-1)/12</f>
         <v/>
       </c>
@@ -14532,10 +14593,10 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="42" t="n">
+      <c r="A398" s="45" t="n">
         <v>394</v>
       </c>
-      <c r="B398" s="43">
+      <c r="B398" s="46">
         <f>Dashboard!$C$5+(394-1)/12</f>
         <v/>
       </c>
@@ -14561,10 +14622,10 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="42" t="n">
+      <c r="A399" s="45" t="n">
         <v>395</v>
       </c>
-      <c r="B399" s="43">
+      <c r="B399" s="46">
         <f>Dashboard!$C$5+(395-1)/12</f>
         <v/>
       </c>
@@ -14590,10 +14651,10 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="42" t="n">
+      <c r="A400" s="45" t="n">
         <v>396</v>
       </c>
-      <c r="B400" s="43">
+      <c r="B400" s="46">
         <f>Dashboard!$C$5+(396-1)/12</f>
         <v/>
       </c>
@@ -14619,10 +14680,10 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="42" t="n">
+      <c r="A401" s="45" t="n">
         <v>397</v>
       </c>
-      <c r="B401" s="43">
+      <c r="B401" s="46">
         <f>Dashboard!$C$5+(397-1)/12</f>
         <v/>
       </c>
@@ -14648,10 +14709,10 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="42" t="n">
+      <c r="A402" s="45" t="n">
         <v>398</v>
       </c>
-      <c r="B402" s="43">
+      <c r="B402" s="46">
         <f>Dashboard!$C$5+(398-1)/12</f>
         <v/>
       </c>
@@ -14677,10 +14738,10 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="42" t="n">
+      <c r="A403" s="45" t="n">
         <v>399</v>
       </c>
-      <c r="B403" s="43">
+      <c r="B403" s="46">
         <f>Dashboard!$C$5+(399-1)/12</f>
         <v/>
       </c>
@@ -14706,10 +14767,10 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="42" t="n">
+      <c r="A404" s="45" t="n">
         <v>400</v>
       </c>
-      <c r="B404" s="43">
+      <c r="B404" s="46">
         <f>Dashboard!$C$5+(400-1)/12</f>
         <v/>
       </c>
@@ -14735,10 +14796,10 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="42" t="n">
+      <c r="A405" s="45" t="n">
         <v>401</v>
       </c>
-      <c r="B405" s="43">
+      <c r="B405" s="46">
         <f>Dashboard!$C$5+(401-1)/12</f>
         <v/>
       </c>
@@ -14764,10 +14825,10 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="42" t="n">
+      <c r="A406" s="45" t="n">
         <v>402</v>
       </c>
-      <c r="B406" s="43">
+      <c r="B406" s="46">
         <f>Dashboard!$C$5+(402-1)/12</f>
         <v/>
       </c>
@@ -14793,10 +14854,10 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="42" t="n">
+      <c r="A407" s="45" t="n">
         <v>403</v>
       </c>
-      <c r="B407" s="43">
+      <c r="B407" s="46">
         <f>Dashboard!$C$5+(403-1)/12</f>
         <v/>
       </c>
@@ -14822,10 +14883,10 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="42" t="n">
+      <c r="A408" s="45" t="n">
         <v>404</v>
       </c>
-      <c r="B408" s="43">
+      <c r="B408" s="46">
         <f>Dashboard!$C$5+(404-1)/12</f>
         <v/>
       </c>
@@ -14851,10 +14912,10 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="42" t="n">
+      <c r="A409" s="45" t="n">
         <v>405</v>
       </c>
-      <c r="B409" s="43">
+      <c r="B409" s="46">
         <f>Dashboard!$C$5+(405-1)/12</f>
         <v/>
       </c>
@@ -14880,10 +14941,10 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="42" t="n">
+      <c r="A410" s="45" t="n">
         <v>406</v>
       </c>
-      <c r="B410" s="43">
+      <c r="B410" s="46">
         <f>Dashboard!$C$5+(406-1)/12</f>
         <v/>
       </c>
@@ -14909,10 +14970,10 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="42" t="n">
+      <c r="A411" s="45" t="n">
         <v>407</v>
       </c>
-      <c r="B411" s="43">
+      <c r="B411" s="46">
         <f>Dashboard!$C$5+(407-1)/12</f>
         <v/>
       </c>
@@ -14938,10 +14999,10 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="42" t="n">
+      <c r="A412" s="45" t="n">
         <v>408</v>
       </c>
-      <c r="B412" s="43">
+      <c r="B412" s="46">
         <f>Dashboard!$C$5+(408-1)/12</f>
         <v/>
       </c>
@@ -14967,10 +15028,10 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="42" t="n">
+      <c r="A413" s="45" t="n">
         <v>409</v>
       </c>
-      <c r="B413" s="43">
+      <c r="B413" s="46">
         <f>Dashboard!$C$5+(409-1)/12</f>
         <v/>
       </c>
@@ -14996,10 +15057,10 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="42" t="n">
+      <c r="A414" s="45" t="n">
         <v>410</v>
       </c>
-      <c r="B414" s="43">
+      <c r="B414" s="46">
         <f>Dashboard!$C$5+(410-1)/12</f>
         <v/>
       </c>
@@ -15025,10 +15086,10 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="42" t="n">
+      <c r="A415" s="45" t="n">
         <v>411</v>
       </c>
-      <c r="B415" s="43">
+      <c r="B415" s="46">
         <f>Dashboard!$C$5+(411-1)/12</f>
         <v/>
       </c>
@@ -15054,10 +15115,10 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="42" t="n">
+      <c r="A416" s="45" t="n">
         <v>412</v>
       </c>
-      <c r="B416" s="43">
+      <c r="B416" s="46">
         <f>Dashboard!$C$5+(412-1)/12</f>
         <v/>
       </c>
@@ -15083,10 +15144,10 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="42" t="n">
+      <c r="A417" s="45" t="n">
         <v>413</v>
       </c>
-      <c r="B417" s="43">
+      <c r="B417" s="46">
         <f>Dashboard!$C$5+(413-1)/12</f>
         <v/>
       </c>
@@ -15112,10 +15173,10 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="42" t="n">
+      <c r="A418" s="45" t="n">
         <v>414</v>
       </c>
-      <c r="B418" s="43">
+      <c r="B418" s="46">
         <f>Dashboard!$C$5+(414-1)/12</f>
         <v/>
       </c>
@@ -15141,10 +15202,10 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="42" t="n">
+      <c r="A419" s="45" t="n">
         <v>415</v>
       </c>
-      <c r="B419" s="43">
+      <c r="B419" s="46">
         <f>Dashboard!$C$5+(415-1)/12</f>
         <v/>
       </c>
@@ -15170,10 +15231,10 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="42" t="n">
+      <c r="A420" s="45" t="n">
         <v>416</v>
       </c>
-      <c r="B420" s="43">
+      <c r="B420" s="46">
         <f>Dashboard!$C$5+(416-1)/12</f>
         <v/>
       </c>
@@ -15199,10 +15260,10 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="42" t="n">
+      <c r="A421" s="45" t="n">
         <v>417</v>
       </c>
-      <c r="B421" s="43">
+      <c r="B421" s="46">
         <f>Dashboard!$C$5+(417-1)/12</f>
         <v/>
       </c>
@@ -15228,10 +15289,10 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="42" t="n">
+      <c r="A422" s="45" t="n">
         <v>418</v>
       </c>
-      <c r="B422" s="43">
+      <c r="B422" s="46">
         <f>Dashboard!$C$5+(418-1)/12</f>
         <v/>
       </c>
@@ -15257,10 +15318,10 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="42" t="n">
+      <c r="A423" s="45" t="n">
         <v>419</v>
       </c>
-      <c r="B423" s="43">
+      <c r="B423" s="46">
         <f>Dashboard!$C$5+(419-1)/12</f>
         <v/>
       </c>
@@ -15286,10 +15347,10 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="42" t="n">
+      <c r="A424" s="45" t="n">
         <v>420</v>
       </c>
-      <c r="B424" s="43">
+      <c r="B424" s="46">
         <f>Dashboard!$C$5+(420-1)/12</f>
         <v/>
       </c>
@@ -15315,10 +15376,10 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="42" t="n">
+      <c r="A425" s="45" t="n">
         <v>421</v>
       </c>
-      <c r="B425" s="43">
+      <c r="B425" s="46">
         <f>Dashboard!$C$5+(421-1)/12</f>
         <v/>
       </c>
@@ -15344,10 +15405,10 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="42" t="n">
+      <c r="A426" s="45" t="n">
         <v>422</v>
       </c>
-      <c r="B426" s="43">
+      <c r="B426" s="46">
         <f>Dashboard!$C$5+(422-1)/12</f>
         <v/>
       </c>
@@ -15373,10 +15434,10 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="42" t="n">
+      <c r="A427" s="45" t="n">
         <v>423</v>
       </c>
-      <c r="B427" s="43">
+      <c r="B427" s="46">
         <f>Dashboard!$C$5+(423-1)/12</f>
         <v/>
       </c>
@@ -15402,10 +15463,10 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="42" t="n">
+      <c r="A428" s="45" t="n">
         <v>424</v>
       </c>
-      <c r="B428" s="43">
+      <c r="B428" s="46">
         <f>Dashboard!$C$5+(424-1)/12</f>
         <v/>
       </c>
@@ -15431,10 +15492,10 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="42" t="n">
+      <c r="A429" s="45" t="n">
         <v>425</v>
       </c>
-      <c r="B429" s="43">
+      <c r="B429" s="46">
         <f>Dashboard!$C$5+(425-1)/12</f>
         <v/>
       </c>
@@ -15460,10 +15521,10 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="42" t="n">
+      <c r="A430" s="45" t="n">
         <v>426</v>
       </c>
-      <c r="B430" s="43">
+      <c r="B430" s="46">
         <f>Dashboard!$C$5+(426-1)/12</f>
         <v/>
       </c>
@@ -15489,10 +15550,10 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="42" t="n">
+      <c r="A431" s="45" t="n">
         <v>427</v>
       </c>
-      <c r="B431" s="43">
+      <c r="B431" s="46">
         <f>Dashboard!$C$5+(427-1)/12</f>
         <v/>
       </c>
@@ -15518,10 +15579,10 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="42" t="n">
+      <c r="A432" s="45" t="n">
         <v>428</v>
       </c>
-      <c r="B432" s="43">
+      <c r="B432" s="46">
         <f>Dashboard!$C$5+(428-1)/12</f>
         <v/>
       </c>
@@ -15547,10 +15608,10 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="42" t="n">
+      <c r="A433" s="45" t="n">
         <v>429</v>
       </c>
-      <c r="B433" s="43">
+      <c r="B433" s="46">
         <f>Dashboard!$C$5+(429-1)/12</f>
         <v/>
       </c>
@@ -15576,10 +15637,10 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="42" t="n">
+      <c r="A434" s="45" t="n">
         <v>430</v>
       </c>
-      <c r="B434" s="43">
+      <c r="B434" s="46">
         <f>Dashboard!$C$5+(430-1)/12</f>
         <v/>
       </c>
@@ -15605,10 +15666,10 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="42" t="n">
+      <c r="A435" s="45" t="n">
         <v>431</v>
       </c>
-      <c r="B435" s="43">
+      <c r="B435" s="46">
         <f>Dashboard!$C$5+(431-1)/12</f>
         <v/>
       </c>
@@ -15634,10 +15695,10 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="42" t="n">
+      <c r="A436" s="45" t="n">
         <v>432</v>
       </c>
-      <c r="B436" s="43">
+      <c r="B436" s="46">
         <f>Dashboard!$C$5+(432-1)/12</f>
         <v/>
       </c>
@@ -15663,10 +15724,10 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="42" t="n">
+      <c r="A437" s="45" t="n">
         <v>433</v>
       </c>
-      <c r="B437" s="43">
+      <c r="B437" s="46">
         <f>Dashboard!$C$5+(433-1)/12</f>
         <v/>
       </c>
@@ -15692,10 +15753,10 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="42" t="n">
+      <c r="A438" s="45" t="n">
         <v>434</v>
       </c>
-      <c r="B438" s="43">
+      <c r="B438" s="46">
         <f>Dashboard!$C$5+(434-1)/12</f>
         <v/>
       </c>
@@ -15721,10 +15782,10 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="42" t="n">
+      <c r="A439" s="45" t="n">
         <v>435</v>
       </c>
-      <c r="B439" s="43">
+      <c r="B439" s="46">
         <f>Dashboard!$C$5+(435-1)/12</f>
         <v/>
       </c>
@@ -15750,10 +15811,10 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="42" t="n">
+      <c r="A440" s="45" t="n">
         <v>436</v>
       </c>
-      <c r="B440" s="43">
+      <c r="B440" s="46">
         <f>Dashboard!$C$5+(436-1)/12</f>
         <v/>
       </c>
@@ -15779,10 +15840,10 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="42" t="n">
+      <c r="A441" s="45" t="n">
         <v>437</v>
       </c>
-      <c r="B441" s="43">
+      <c r="B441" s="46">
         <f>Dashboard!$C$5+(437-1)/12</f>
         <v/>
       </c>
@@ -15808,10 +15869,10 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="42" t="n">
+      <c r="A442" s="45" t="n">
         <v>438</v>
       </c>
-      <c r="B442" s="43">
+      <c r="B442" s="46">
         <f>Dashboard!$C$5+(438-1)/12</f>
         <v/>
       </c>
@@ -15837,10 +15898,10 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="42" t="n">
+      <c r="A443" s="45" t="n">
         <v>439</v>
       </c>
-      <c r="B443" s="43">
+      <c r="B443" s="46">
         <f>Dashboard!$C$5+(439-1)/12</f>
         <v/>
       </c>
@@ -15866,10 +15927,10 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="42" t="n">
+      <c r="A444" s="45" t="n">
         <v>440</v>
       </c>
-      <c r="B444" s="43">
+      <c r="B444" s="46">
         <f>Dashboard!$C$5+(440-1)/12</f>
         <v/>
       </c>
@@ -15895,10 +15956,10 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="42" t="n">
+      <c r="A445" s="45" t="n">
         <v>441</v>
       </c>
-      <c r="B445" s="43">
+      <c r="B445" s="46">
         <f>Dashboard!$C$5+(441-1)/12</f>
         <v/>
       </c>
@@ -15924,10 +15985,10 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="42" t="n">
+      <c r="A446" s="45" t="n">
         <v>442</v>
       </c>
-      <c r="B446" s="43">
+      <c r="B446" s="46">
         <f>Dashboard!$C$5+(442-1)/12</f>
         <v/>
       </c>
@@ -15953,10 +16014,10 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="42" t="n">
+      <c r="A447" s="45" t="n">
         <v>443</v>
       </c>
-      <c r="B447" s="43">
+      <c r="B447" s="46">
         <f>Dashboard!$C$5+(443-1)/12</f>
         <v/>
       </c>
@@ -15982,10 +16043,10 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="42" t="n">
+      <c r="A448" s="45" t="n">
         <v>444</v>
       </c>
-      <c r="B448" s="43">
+      <c r="B448" s="46">
         <f>Dashboard!$C$5+(444-1)/12</f>
         <v/>
       </c>
@@ -16011,10 +16072,10 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="42" t="n">
+      <c r="A449" s="45" t="n">
         <v>445</v>
       </c>
-      <c r="B449" s="43">
+      <c r="B449" s="46">
         <f>Dashboard!$C$5+(445-1)/12</f>
         <v/>
       </c>
@@ -16040,10 +16101,10 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="42" t="n">
+      <c r="A450" s="45" t="n">
         <v>446</v>
       </c>
-      <c r="B450" s="43">
+      <c r="B450" s="46">
         <f>Dashboard!$C$5+(446-1)/12</f>
         <v/>
       </c>
@@ -16069,10 +16130,10 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="42" t="n">
+      <c r="A451" s="45" t="n">
         <v>447</v>
       </c>
-      <c r="B451" s="43">
+      <c r="B451" s="46">
         <f>Dashboard!$C$5+(447-1)/12</f>
         <v/>
       </c>
@@ -16098,10 +16159,10 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="42" t="n">
+      <c r="A452" s="45" t="n">
         <v>448</v>
       </c>
-      <c r="B452" s="43">
+      <c r="B452" s="46">
         <f>Dashboard!$C$5+(448-1)/12</f>
         <v/>
       </c>
@@ -16127,10 +16188,10 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="42" t="n">
+      <c r="A453" s="45" t="n">
         <v>449</v>
       </c>
-      <c r="B453" s="43">
+      <c r="B453" s="46">
         <f>Dashboard!$C$5+(449-1)/12</f>
         <v/>
       </c>
@@ -16156,10 +16217,10 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="42" t="n">
+      <c r="A454" s="45" t="n">
         <v>450</v>
       </c>
-      <c r="B454" s="43">
+      <c r="B454" s="46">
         <f>Dashboard!$C$5+(450-1)/12</f>
         <v/>
       </c>
@@ -16185,10 +16246,10 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="42" t="n">
+      <c r="A455" s="45" t="n">
         <v>451</v>
       </c>
-      <c r="B455" s="43">
+      <c r="B455" s="46">
         <f>Dashboard!$C$5+(451-1)/12</f>
         <v/>
       </c>
@@ -16214,10 +16275,10 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="42" t="n">
+      <c r="A456" s="45" t="n">
         <v>452</v>
       </c>
-      <c r="B456" s="43">
+      <c r="B456" s="46">
         <f>Dashboard!$C$5+(452-1)/12</f>
         <v/>
       </c>
@@ -16243,10 +16304,10 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="42" t="n">
+      <c r="A457" s="45" t="n">
         <v>453</v>
       </c>
-      <c r="B457" s="43">
+      <c r="B457" s="46">
         <f>Dashboard!$C$5+(453-1)/12</f>
         <v/>
       </c>
@@ -16272,10 +16333,10 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="42" t="n">
+      <c r="A458" s="45" t="n">
         <v>454</v>
       </c>
-      <c r="B458" s="43">
+      <c r="B458" s="46">
         <f>Dashboard!$C$5+(454-1)/12</f>
         <v/>
       </c>
@@ -16301,10 +16362,10 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="42" t="n">
+      <c r="A459" s="45" t="n">
         <v>455</v>
       </c>
-      <c r="B459" s="43">
+      <c r="B459" s="46">
         <f>Dashboard!$C$5+(455-1)/12</f>
         <v/>
       </c>
@@ -16330,10 +16391,10 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="42" t="n">
+      <c r="A460" s="45" t="n">
         <v>456</v>
       </c>
-      <c r="B460" s="43">
+      <c r="B460" s="46">
         <f>Dashboard!$C$5+(456-1)/12</f>
         <v/>
       </c>
@@ -16359,10 +16420,10 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="42" t="n">
+      <c r="A461" s="45" t="n">
         <v>457</v>
       </c>
-      <c r="B461" s="43">
+      <c r="B461" s="46">
         <f>Dashboard!$C$5+(457-1)/12</f>
         <v/>
       </c>
@@ -16388,10 +16449,10 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="42" t="n">
+      <c r="A462" s="45" t="n">
         <v>458</v>
       </c>
-      <c r="B462" s="43">
+      <c r="B462" s="46">
         <f>Dashboard!$C$5+(458-1)/12</f>
         <v/>
       </c>
@@ -16417,10 +16478,10 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="42" t="n">
+      <c r="A463" s="45" t="n">
         <v>459</v>
       </c>
-      <c r="B463" s="43">
+      <c r="B463" s="46">
         <f>Dashboard!$C$5+(459-1)/12</f>
         <v/>
       </c>
@@ -16446,10 +16507,10 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="42" t="n">
+      <c r="A464" s="45" t="n">
         <v>460</v>
       </c>
-      <c r="B464" s="43">
+      <c r="B464" s="46">
         <f>Dashboard!$C$5+(460-1)/12</f>
         <v/>
       </c>
@@ -16475,10 +16536,10 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="42" t="n">
+      <c r="A465" s="45" t="n">
         <v>461</v>
       </c>
-      <c r="B465" s="43">
+      <c r="B465" s="46">
         <f>Dashboard!$C$5+(461-1)/12</f>
         <v/>
       </c>
@@ -16504,10 +16565,10 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="42" t="n">
+      <c r="A466" s="45" t="n">
         <v>462</v>
       </c>
-      <c r="B466" s="43">
+      <c r="B466" s="46">
         <f>Dashboard!$C$5+(462-1)/12</f>
         <v/>
       </c>
@@ -16533,10 +16594,10 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="42" t="n">
+      <c r="A467" s="45" t="n">
         <v>463</v>
       </c>
-      <c r="B467" s="43">
+      <c r="B467" s="46">
         <f>Dashboard!$C$5+(463-1)/12</f>
         <v/>
       </c>
@@ -16562,10 +16623,10 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="42" t="n">
+      <c r="A468" s="45" t="n">
         <v>464</v>
       </c>
-      <c r="B468" s="43">
+      <c r="B468" s="46">
         <f>Dashboard!$C$5+(464-1)/12</f>
         <v/>
       </c>
@@ -16591,10 +16652,10 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="42" t="n">
+      <c r="A469" s="45" t="n">
         <v>465</v>
       </c>
-      <c r="B469" s="43">
+      <c r="B469" s="46">
         <f>Dashboard!$C$5+(465-1)/12</f>
         <v/>
       </c>
@@ -16620,10 +16681,10 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="42" t="n">
+      <c r="A470" s="45" t="n">
         <v>466</v>
       </c>
-      <c r="B470" s="43">
+      <c r="B470" s="46">
         <f>Dashboard!$C$5+(466-1)/12</f>
         <v/>
       </c>
@@ -16649,10 +16710,10 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="42" t="n">
+      <c r="A471" s="45" t="n">
         <v>467</v>
       </c>
-      <c r="B471" s="43">
+      <c r="B471" s="46">
         <f>Dashboard!$C$5+(467-1)/12</f>
         <v/>
       </c>
@@ -16678,10 +16739,10 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="42" t="n">
+      <c r="A472" s="45" t="n">
         <v>468</v>
       </c>
-      <c r="B472" s="43">
+      <c r="B472" s="46">
         <f>Dashboard!$C$5+(468-1)/12</f>
         <v/>
       </c>
@@ -16707,10 +16768,10 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="42" t="n">
+      <c r="A473" s="45" t="n">
         <v>469</v>
       </c>
-      <c r="B473" s="43">
+      <c r="B473" s="46">
         <f>Dashboard!$C$5+(469-1)/12</f>
         <v/>
       </c>
@@ -16736,10 +16797,10 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="42" t="n">
+      <c r="A474" s="45" t="n">
         <v>470</v>
       </c>
-      <c r="B474" s="43">
+      <c r="B474" s="46">
         <f>Dashboard!$C$5+(470-1)/12</f>
         <v/>
       </c>
@@ -16765,10 +16826,10 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="42" t="n">
+      <c r="A475" s="45" t="n">
         <v>471</v>
       </c>
-      <c r="B475" s="43">
+      <c r="B475" s="46">
         <f>Dashboard!$C$5+(471-1)/12</f>
         <v/>
       </c>
@@ -16794,10 +16855,10 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="42" t="n">
+      <c r="A476" s="45" t="n">
         <v>472</v>
       </c>
-      <c r="B476" s="43">
+      <c r="B476" s="46">
         <f>Dashboard!$C$5+(472-1)/12</f>
         <v/>
       </c>
@@ -16823,10 +16884,10 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="42" t="n">
+      <c r="A477" s="45" t="n">
         <v>473</v>
       </c>
-      <c r="B477" s="43">
+      <c r="B477" s="46">
         <f>Dashboard!$C$5+(473-1)/12</f>
         <v/>
       </c>
@@ -16852,10 +16913,10 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="42" t="n">
+      <c r="A478" s="45" t="n">
         <v>474</v>
       </c>
-      <c r="B478" s="43">
+      <c r="B478" s="46">
         <f>Dashboard!$C$5+(474-1)/12</f>
         <v/>
       </c>
@@ -16881,10 +16942,10 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="42" t="n">
+      <c r="A479" s="45" t="n">
         <v>475</v>
       </c>
-      <c r="B479" s="43">
+      <c r="B479" s="46">
         <f>Dashboard!$C$5+(475-1)/12</f>
         <v/>
       </c>
@@ -16910,10 +16971,10 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="42" t="n">
+      <c r="A480" s="45" t="n">
         <v>476</v>
       </c>
-      <c r="B480" s="43">
+      <c r="B480" s="46">
         <f>Dashboard!$C$5+(476-1)/12</f>
         <v/>
       </c>
@@ -16939,10 +17000,10 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="42" t="n">
+      <c r="A481" s="45" t="n">
         <v>477</v>
       </c>
-      <c r="B481" s="43">
+      <c r="B481" s="46">
         <f>Dashboard!$C$5+(477-1)/12</f>
         <v/>
       </c>
@@ -16968,10 +17029,10 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="42" t="n">
+      <c r="A482" s="45" t="n">
         <v>478</v>
       </c>
-      <c r="B482" s="43">
+      <c r="B482" s="46">
         <f>Dashboard!$C$5+(478-1)/12</f>
         <v/>
       </c>
@@ -16997,10 +17058,10 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="42" t="n">
+      <c r="A483" s="45" t="n">
         <v>479</v>
       </c>
-      <c r="B483" s="43">
+      <c r="B483" s="46">
         <f>Dashboard!$C$5+(479-1)/12</f>
         <v/>
       </c>
@@ -17026,10 +17087,10 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="42" t="n">
+      <c r="A484" s="45" t="n">
         <v>480</v>
       </c>
-      <c r="B484" s="43">
+      <c r="B484" s="46">
         <f>Dashboard!$C$5+(480-1)/12</f>
         <v/>
       </c>
@@ -17080,7 +17141,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>Advanced Settings</t>
         </is>
@@ -17106,22 +17167,22 @@
       <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr">
+      <c r="C5" s="47" t="inlineStr">
         <is>
           <t>Reflation</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
+      <c r="D5" s="47" t="inlineStr">
         <is>
           <t>Stagflation</t>
         </is>
       </c>
-      <c r="E5" s="44" t="inlineStr">
+      <c r="E5" s="47" t="inlineStr">
         <is>
           <t>Deflation</t>
         </is>
@@ -17149,7 +17210,7 @@
         <f>SUM(B6:E6)</f>
         <v/>
       </c>
-      <c r="G6" s="45">
+      <c r="G6" s="48">
         <f>IF(ABS(F6-1)&gt;0.005,"← must sum to 100%","")</f>
         <v/>
       </c>
@@ -17170,7 +17231,7 @@
           <t>Horizon (years, from Dashboard ages)</t>
         </is>
       </c>
-      <c r="B9" s="46">
+      <c r="B9" s="49">
         <f>Dashboard!$C$6-Dashboard!$C$5</f>
         <v/>
       </c>
@@ -17201,183 +17262,183 @@
       <c r="H11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>Mean monthly</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="D12" s="38" t="inlineStr">
         <is>
           <t>Monthly sd</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E12" s="38" t="inlineStr">
         <is>
           <t>Annual sd</t>
         </is>
       </c>
-      <c r="F12" s="35" t="inlineStr">
+      <c r="F12" s="38" t="inlineStr">
         <is>
           <t>S.E. (avg, horizon)</t>
         </is>
       </c>
-      <c r="G12" s="35" t="inlineStr">
+      <c r="G12" s="38" t="inlineStr">
         <is>
           <t>Low monthly</t>
         </is>
       </c>
-      <c r="H12" s="35" t="inlineStr">
+      <c r="H12" s="38" t="inlineStr">
         <is>
           <t>High monthly</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="47" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>CONS</t>
         </is>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="39">
         <f>(SUMPRODUCT($B$6:$E$6,Data!$B$6:$E$6)-$B$8/10000/12)*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="51">
         <f>(1+B13)^12-1</f>
         <v/>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="39">
         <f>SUMPRODUCT($B$6:$E$6,Data!$B$13:$E$13)</f>
         <v/>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="51">
         <f>D13*SQRT(12)</f>
         <v/>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="51">
         <f>E13/SQRT(MAX(1,$B$9))</f>
         <v/>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="39">
         <f>(1+C13-F13)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="39">
         <f>(1+C13+F13)^(1/12)-1</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="39">
         <f>(SUMPRODUCT($B$6:$E$6,Data!$B$7:$E$7)-$B$8/10000/12)*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="C14" s="48">
+      <c r="C14" s="51">
         <f>(1+B14)^12-1</f>
         <v/>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="39">
         <f>SUMPRODUCT($B$6:$E$6,Data!$B$14:$E$14)</f>
         <v/>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="51">
         <f>D14*SQRT(12)</f>
         <v/>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="51">
         <f>E14/SQRT(MAX(1,$B$9))</f>
         <v/>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="39">
         <f>(1+C14-F14)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="39">
         <f>(1+C14+F14)^(1/12)-1</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>AGG</t>
         </is>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="39">
         <f>(SUMPRODUCT($B$6:$E$6,Data!$B$8:$E$8)-$B$8/10000/12)*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="C15" s="48">
+      <c r="C15" s="51">
         <f>(1+B15)^12-1</f>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="39">
         <f>SUMPRODUCT($B$6:$E$6,Data!$B$15:$E$15)</f>
         <v/>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="51">
         <f>D15*SQRT(12)</f>
         <v/>
       </c>
-      <c r="F15" s="48">
+      <c r="F15" s="51">
         <f>E15/SQRT(MAX(1,$B$9))</f>
         <v/>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="39">
         <f>(1+C15-F15)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="39">
         <f>(1+C15+F15)^(1/12)-1</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="47" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>VAGG</t>
         </is>
       </c>
-      <c r="B16" s="36">
+      <c r="B16" s="39">
         <f>(SUMPRODUCT($B$6:$E$6,Data!$B$9:$E$9)-$B$8/10000/12)*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="51">
         <f>(1+B16)^12-1</f>
         <v/>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="39">
         <f>SUMPRODUCT($B$6:$E$6,Data!$B$16:$E$16)</f>
         <v/>
       </c>
-      <c r="E16" s="48">
+      <c r="E16" s="51">
         <f>D16*SQRT(12)</f>
         <v/>
       </c>
-      <c r="F16" s="48">
+      <c r="F16" s="51">
         <f>E16/SQRT(MAX(1,$B$9))</f>
         <v/>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="39">
         <f>(1+C16-F16)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="H16" s="36">
+      <c r="H16" s="39">
         <f>(1+C16+F16)^(1/12)-1</f>
         <v/>
       </c>
@@ -17397,7 +17458,7 @@
           <t>Year 1</t>
         </is>
       </c>
-      <c r="B19" s="49">
+      <c r="B19" s="52">
         <f>Dashboard!$C$8</f>
         <v/>
       </c>
@@ -17805,7 +17866,7 @@
           <t>Implied contribution growth, monthly (yr1 → horizon)</t>
         </is>
       </c>
-      <c r="B60" s="50">
+      <c r="B60" s="53">
         <f>(INDEX($B$19:$B$58,MIN(40,MAX(1,$B$9)))/Dashboard!$C$8)^(1/MAX(1,(MIN(40,$B$9)-1)*12))-1</f>
         <v/>
       </c>
@@ -17833,7 +17894,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>Model Data — per-regime return statistics (v2 rotation backtest, Jun 2007–Aug 2026)</t>
         </is>
@@ -17858,100 +17919,100 @@
       <c r="E4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr">
+      <c r="C5" s="47" t="inlineStr">
         <is>
           <t>Reflation</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
+      <c r="D5" s="47" t="inlineStr">
         <is>
           <t>Stagflation</t>
         </is>
       </c>
-      <c r="E5" s="44" t="inlineStr">
+      <c r="E5" s="47" t="inlineStr">
         <is>
           <t>Deflation</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>CONS</t>
         </is>
       </c>
-      <c r="B6" s="52" t="n">
+      <c r="B6" s="55" t="n">
         <v>0.00731</v>
       </c>
-      <c r="C6" s="52" t="n">
+      <c r="C6" s="55" t="n">
         <v>0.00769</v>
       </c>
-      <c r="D6" s="52" t="n">
+      <c r="D6" s="55" t="n">
         <v>-0.00047</v>
       </c>
-      <c r="E6" s="52" t="n">
+      <c r="E6" s="55" t="n">
         <v>0.007820000000000001</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="B7" s="52" t="n">
+      <c r="B7" s="55" t="n">
         <v>0.01397</v>
       </c>
-      <c r="C7" s="52" t="n">
+      <c r="C7" s="55" t="n">
         <v>0.01033</v>
       </c>
-      <c r="D7" s="52" t="n">
+      <c r="D7" s="55" t="n">
         <v>-0.0011</v>
       </c>
-      <c r="E7" s="52" t="n">
+      <c r="E7" s="55" t="n">
         <v>0.01283</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>AGG</t>
         </is>
       </c>
-      <c r="B8" s="52" t="n">
+      <c r="B8" s="55" t="n">
         <v>0.03406</v>
       </c>
-      <c r="C8" s="52" t="n">
+      <c r="C8" s="55" t="n">
         <v>0.01138</v>
       </c>
-      <c r="D8" s="52" t="n">
+      <c r="D8" s="55" t="n">
         <v>-0.00554</v>
       </c>
-      <c r="E8" s="52" t="n">
+      <c r="E8" s="55" t="n">
         <v>0.01183</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>VAGG</t>
         </is>
       </c>
-      <c r="B9" s="52" t="n">
+      <c r="B9" s="55" t="n">
         <v>0.05004</v>
       </c>
-      <c r="C9" s="52" t="n">
+      <c r="C9" s="55" t="n">
         <v>0.01556</v>
       </c>
-      <c r="D9" s="52" t="n">
+      <c r="D9" s="55" t="n">
         <v>-0.00698</v>
       </c>
-      <c r="E9" s="52" t="n">
+      <c r="E9" s="55" t="n">
         <v>0.01445</v>
       </c>
     </row>
@@ -17967,100 +18028,100 @@
       <c r="E11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C12" s="44" t="inlineStr">
+      <c r="C12" s="47" t="inlineStr">
         <is>
           <t>Reflation</t>
         </is>
       </c>
-      <c r="D12" s="44" t="inlineStr">
+      <c r="D12" s="47" t="inlineStr">
         <is>
           <t>Stagflation</t>
         </is>
       </c>
-      <c r="E12" s="44" t="inlineStr">
+      <c r="E12" s="47" t="inlineStr">
         <is>
           <t>Deflation</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="47" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>CONS</t>
         </is>
       </c>
-      <c r="B13" s="52" t="n">
+      <c r="B13" s="55" t="n">
         <v>0.01765</v>
       </c>
-      <c r="C13" s="52" t="n">
+      <c r="C13" s="55" t="n">
         <v>0.0223</v>
       </c>
-      <c r="D13" s="52" t="n">
+      <c r="D13" s="55" t="n">
         <v>0.01283</v>
       </c>
-      <c r="E13" s="52" t="n">
+      <c r="E13" s="55" t="n">
         <v>0.0278</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="B14" s="52" t="n">
+      <c r="B14" s="55" t="n">
         <v>0.03064</v>
       </c>
-      <c r="C14" s="52" t="n">
+      <c r="C14" s="55" t="n">
         <v>0.03189</v>
       </c>
-      <c r="D14" s="52" t="n">
+      <c r="D14" s="55" t="n">
         <v>0.01504</v>
       </c>
-      <c r="E14" s="52" t="n">
+      <c r="E14" s="55" t="n">
         <v>0.03919</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>AGG</t>
         </is>
       </c>
-      <c r="B15" s="52" t="n">
+      <c r="B15" s="55" t="n">
         <v>0.09061</v>
       </c>
-      <c r="C15" s="52" t="n">
+      <c r="C15" s="55" t="n">
         <v>0.04874</v>
       </c>
-      <c r="D15" s="52" t="n">
+      <c r="D15" s="55" t="n">
         <v>0.02913</v>
       </c>
-      <c r="E15" s="52" t="n">
+      <c r="E15" s="55" t="n">
         <v>0.0717</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="47" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>VAGG</t>
         </is>
       </c>
-      <c r="B16" s="52" t="n">
+      <c r="B16" s="55" t="n">
         <v>0.13741</v>
       </c>
-      <c r="C16" s="52" t="n">
+      <c r="C16" s="55" t="n">
         <v>0.06776</v>
       </c>
-      <c r="D16" s="52" t="n">
+      <c r="D16" s="55" t="n">
         <v>0.03462</v>
       </c>
-      <c r="E16" s="52" t="n">
+      <c r="E16" s="55" t="n">
         <v>0.1052</v>
       </c>
     </row>
@@ -18076,22 +18137,22 @@
       <c r="E18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B19" s="47" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C19" s="44" t="inlineStr">
+      <c r="C19" s="47" t="inlineStr">
         <is>
           <t>Reflation</t>
         </is>
       </c>
-      <c r="D19" s="44" t="inlineStr">
+      <c r="D19" s="47" t="inlineStr">
         <is>
           <t>Stagflation</t>
         </is>
       </c>
-      <c r="E19" s="44" t="inlineStr">
+      <c r="E19" s="47" t="inlineStr">
         <is>
           <t>Deflation</t>
         </is>
@@ -18103,16 +18164,16 @@
           <t>Share of months</t>
         </is>
       </c>
-      <c r="B20" s="53" t="n">
+      <c r="B20" s="56" t="n">
         <v>0.323</v>
       </c>
-      <c r="C20" s="53" t="n">
+      <c r="C20" s="56" t="n">
         <v>0.466</v>
       </c>
-      <c r="D20" s="53" t="n">
+      <c r="D20" s="56" t="n">
         <v>0.082</v>
       </c>
-      <c r="E20" s="53" t="n">
+      <c r="E20" s="56" t="n">
         <v>0.129</v>
       </c>
     </row>
@@ -18122,16 +18183,16 @@
           <t>Avg duration (months)</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n">
+      <c r="B21" s="57" t="n">
         <v>3.3</v>
       </c>
-      <c r="C21" s="54" t="n">
+      <c r="C21" s="57" t="n">
         <v>5.4</v>
       </c>
-      <c r="D21" s="54" t="n">
+      <c r="D21" s="57" t="n">
         <v>2.7</v>
       </c>
-      <c r="E21" s="54" t="n">
+      <c r="E21" s="57" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -18141,7 +18202,7 @@
           <t>Risk-free rate (annual)</t>
         </is>
       </c>
-      <c r="B23" s="53" t="n">
+      <c r="B23" s="56" t="n">
         <v>0.019</v>
       </c>
     </row>
@@ -18164,133 +18225,133 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>Methodology &amp; Assumptions</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="38" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Glide path</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="55" t="inlineStr">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>The Dashboard assigns a risk tier to each 5-year age block (age 25→65 = 8 decision points). The projection applies each block's tier return, switching automatically at block boundaries. Defaults de-risk with age: VAGG→AGG→MOD→CONS.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>Framework</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="58" t="inlineStr">
         <is>
           <t>Four macro regimes (growth x inflation) classified monthly ex-ante (SPY &amp; DBC vs 10-month SMAs, locked). Each tier = fixed allocation per regime (matrix v2). Per-tier expected returns blend per-regime statistics by the Settings regime mix, minus switch-cost drag.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>Contributions</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>Year-by-year monthly schedule on Settings (defaults: $500 yr1, $800 by yr3, +12%/yr to yr15 as income scales to ~$500k, +8%/yr after), capped on the Dashboard. Projection applies the exact schedule.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>Uncertainty</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="55" t="inlineStr">
+      <c r="A13" s="58" t="inlineStr">
         <is>
           <t>Low/High paths and Statistics percentiles band the uncertainty of the AVERAGE growth rate (+/- s.e. = annual sd / sqrt(horizon years)). They are not drawdown bounds: backtested max drawdowns are CONS -13%, MOD -15%, AGG -37%, VAGG -51%, and a VAGG-heavy early glide will experience them.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>Return haircut</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="55" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>Long-horizon compounding of raw backtest returns is not credible (edges decay; regimes shift; capacity and execution erode results). The Dashboard haircut (default 25%) scales all tier returns down before projecting. Set 0% to see raw-backtest numbers; treat those as an upper bound, not a plan.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t>Evidence quality</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="55" t="inlineStr">
+      <c r="A19" s="58" t="inlineStr">
         <is>
           <t>Backtest Jun 2007-Aug 2026; leveraged instruments simulated pre-2010; playbooks partly second-generation designs. The append-only monthly paper ledger is the binding forward test. Statistics percentiles additionally approximate contributions as smooth growth (cap ignored).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>Comparison</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="55" t="inlineStr">
-        <is>
-          <t>Benchmark historical stats computed on the identical window/method as the tiers (source: Yahoo adjusted closes). Forward balances use the same start, contribution schedule approximation, and horizon; benchmarks default to raw historical CAGR while rotation rows are haircut - edit either.</t>
+      <c r="A22" s="58" t="inlineStr">
+        <is>
+          <t>Benchmark historical stats computed on the identical window/method as the tiers (source: Yahoo adjusted closes). Forward balances apply ONE haircut to every row - benchmarks and strategies alike (the benchmark haircut cell links to the Dashboard input; override only to argue a deliberate difference). Same start, same contribution schedule approximation, same horizon.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="inlineStr">
+      <c r="A24" s="41" t="inlineStr">
         <is>
           <t>Colors</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="55" t="inlineStr">
+      <c r="A25" s="58" t="inlineStr">
         <is>
           <t>Yellow = inputs. Blue = editable assumptions. Green = derived/links. Navy bars = sections. Grey columns on the glide table are helpers used by Statistics.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="inlineStr">
+      <c r="A27" s="41" t="inlineStr">
         <is>
           <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="55" t="inlineStr">
+      <c r="A28" s="58" t="inlineStr">
         <is>
           <t>Personal research tooling; not investment advice. Past and simulated performance do not guarantee future results.</t>
         </is>

--- a/GrowthProjection.xlsx
+++ b/GrowthProjection.xlsx
@@ -1598,7 +1598,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jun 2007 – Aug 2026 daily data, dividends included. Leveraged instruments simulated pre-2010. Forward validation: paper/ledger.csv (monthly, automated).</t>
+          <t>Matrix v4 (conditional-duration S, D-cell gold, R momentum tilt), monthly-only execution — intra-month mechanisms tested and rejected under honest T+1 modeling. Leveraged instruments simulated pre-2010. Out-of-sample framework validation: 1987-2007 replication. Forward: paper/ledger.csv.</t>
         </is>
       </c>
     </row>
@@ -1683,34 +1683,34 @@
         </is>
       </c>
       <c r="B6" s="18" t="n">
-        <v>0.0837</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>1.1858</v>
+        <v>1.3173</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>0.8632</v>
+        <v>0.9536</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>-0.1306</v>
+        <v>-0.1059</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>0.1749</v>
+        <v>0.1604</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.1381</v>
+        <v>0.1315</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.1228</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>-0.0127</v>
+        <v>0.021</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>0.1949</v>
+        <v>0.204</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>0.1357</v>
+        <v>0.1268</v>
       </c>
     </row>
     <row r="7">
@@ -1720,34 +1720,34 @@
         </is>
       </c>
       <c r="B7" s="20" t="n">
-        <v>0.1327</v>
+        <v>0.1443</v>
       </c>
       <c r="C7" s="21" t="n">
-        <v>1.3476</v>
+        <v>1.4307</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>0.9798</v>
+        <v>1.0503</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>-0.1496</v>
+        <v>-0.16</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>0.3065</v>
+        <v>0.3077</v>
       </c>
       <c r="G7" s="20" t="n">
-        <v>0.1541</v>
+        <v>0.1133</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>0.2216</v>
+        <v>0.2458</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>-0.0292</v>
+        <v>0.0221</v>
       </c>
       <c r="J7" s="20" t="n">
-        <v>0.2553</v>
+        <v>0.2703</v>
       </c>
       <c r="K7" s="20" t="n">
-        <v>0.1916</v>
+        <v>0.1771</v>
       </c>
     </row>
     <row r="8">
@@ -1757,34 +1757,34 @@
         </is>
       </c>
       <c r="B8" s="18" t="n">
-        <v>0.1985</v>
+        <v>0.2271</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>1.0121</v>
+        <v>1.122</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>0.7635</v>
+        <v>0.878</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-0.365</v>
+        <v>-0.3565</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>0.5868</v>
+        <v>0.6299</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>0.33</v>
+        <v>0.2365</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0.6318</v>
+        <v>0.6504</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-0.2428</v>
+        <v>-0.2259</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0.3696</v>
+        <v>0.4798</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>0.2083</v>
+        <v>0.2039</v>
       </c>
     </row>
     <row r="9">
@@ -1794,34 +1794,34 @@
         </is>
       </c>
       <c r="B9" s="20" t="n">
-        <v>0.267</v>
+        <v>0.3096</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>1.0056</v>
+        <v>1.1049</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>0.7679</v>
+        <v>0.8754</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>-0.5102</v>
+        <v>-0.5002</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>0.8663</v>
+        <v>0.96</v>
       </c>
       <c r="G9" s="20" t="n">
-        <v>0.5061</v>
+        <v>0.3016</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9754</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>-0.3465</v>
+        <v>-0.3142</v>
       </c>
       <c r="J9" s="20" t="n">
-        <v>0.4406</v>
+        <v>0.5814</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>0.3146</v>
+        <v>0.3244</v>
       </c>
     </row>
     <row r="10">
@@ -18022,7 +18022,7 @@
     <row r="1">
       <c r="A1" s="54" t="inlineStr">
         <is>
-          <t>Model Data — per-regime return statistics (v2 rotation backtest, Jun 2007–Aug 2026)</t>
+          <t>Model Data — per-regime return statistics (matrix v4, monthly-only execution, Jun 2007–Aug 2026)</t>
         </is>
       </c>
     </row>
@@ -18073,16 +18073,16 @@
         </is>
       </c>
       <c r="B6" s="55" t="n">
-        <v>0.00731</v>
+        <v>0.00726</v>
       </c>
       <c r="C6" s="55" t="n">
-        <v>0.00769</v>
+        <v>0.00796</v>
       </c>
       <c r="D6" s="55" t="n">
-        <v>-0.00047</v>
+        <v>0.00399</v>
       </c>
       <c r="E6" s="55" t="n">
-        <v>0.007820000000000001</v>
+        <v>0.01116</v>
       </c>
     </row>
     <row r="7">
@@ -18092,16 +18092,16 @@
         </is>
       </c>
       <c r="B7" s="55" t="n">
-        <v>0.01397</v>
+        <v>0.01392</v>
       </c>
       <c r="C7" s="55" t="n">
-        <v>0.01033</v>
+        <v>0.01076</v>
       </c>
       <c r="D7" s="55" t="n">
-        <v>-0.0011</v>
+        <v>0.00463</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>0.01283</v>
+        <v>0.01446</v>
       </c>
     </row>
     <row r="8">
@@ -18114,13 +18114,13 @@
         <v>0.03406</v>
       </c>
       <c r="C8" s="55" t="n">
-        <v>0.01138</v>
+        <v>0.01205</v>
       </c>
       <c r="D8" s="55" t="n">
-        <v>-0.00554</v>
+        <v>0.00528</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>0.01183</v>
+        <v>0.0167</v>
       </c>
     </row>
     <row r="9">
@@ -18133,13 +18133,13 @@
         <v>0.05004</v>
       </c>
       <c r="C9" s="55" t="n">
-        <v>0.01556</v>
+        <v>0.01622</v>
       </c>
       <c r="D9" s="55" t="n">
-        <v>-0.00698</v>
+        <v>0.00593</v>
       </c>
       <c r="E9" s="55" t="n">
-        <v>0.01445</v>
+        <v>0.02286</v>
       </c>
     </row>
     <row r="11">
@@ -18182,16 +18182,16 @@
         </is>
       </c>
       <c r="B13" s="55" t="n">
-        <v>0.01765</v>
+        <v>0.01763</v>
       </c>
       <c r="C13" s="55" t="n">
-        <v>0.0223</v>
+        <v>0.02288</v>
       </c>
       <c r="D13" s="55" t="n">
-        <v>0.01283</v>
+        <v>0.01537</v>
       </c>
       <c r="E13" s="55" t="n">
-        <v>0.0278</v>
+        <v>0.03214</v>
       </c>
     </row>
     <row r="14">
@@ -18201,16 +18201,16 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.03064</v>
+        <v>0.0307</v>
       </c>
       <c r="C14" s="55" t="n">
-        <v>0.03189</v>
+        <v>0.03269</v>
       </c>
       <c r="D14" s="55" t="n">
-        <v>0.01504</v>
+        <v>0.01819</v>
       </c>
       <c r="E14" s="55" t="n">
-        <v>0.03919</v>
+        <v>0.03913</v>
       </c>
     </row>
     <row r="15">
@@ -18223,13 +18223,13 @@
         <v>0.09061</v>
       </c>
       <c r="C15" s="55" t="n">
-        <v>0.04874</v>
+        <v>0.04889</v>
       </c>
       <c r="D15" s="55" t="n">
-        <v>0.02913</v>
+        <v>0.02114</v>
       </c>
       <c r="E15" s="55" t="n">
-        <v>0.0717</v>
+        <v>0.05551</v>
       </c>
     </row>
     <row r="16">
@@ -18242,13 +18242,13 @@
         <v>0.13741</v>
       </c>
       <c r="C16" s="55" t="n">
-        <v>0.06776</v>
+        <v>0.06826</v>
       </c>
       <c r="D16" s="55" t="n">
-        <v>0.03462</v>
+        <v>0.02416</v>
       </c>
       <c r="E16" s="55" t="n">
-        <v>0.1052</v>
+        <v>0.07714</v>
       </c>
     </row>
     <row r="18">

--- a/GrowthProjection.xlsx
+++ b/GrowthProjection.xlsx
@@ -1144,7 +1144,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Age-based risk glide with regime-conditional return engine  |  Backtest Jun 2007–Aug 2026  |  Prepared August 20, 2026  |  Forward ledger live</t>
+          <t>Age-based risk glide with regime-conditional return engine  |  Backtest Jun 2007–Aug 2026  |  Prepared August 21, 2026  |  Forward ledger live</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Matrix v4 (conditional-duration S, D-cell gold, R momentum tilt), monthly-only execution — intra-month mechanisms tested and rejected under honest T+1 modeling. Leveraged instruments simulated pre-2010. Out-of-sample framework validation: 1987-2007 replication. Forward: paper/ledger.csv.</t>
+          <t>Matrix v6 (conditional-duration S, D-cell gold, R momentum tilt, regime-gated short book: oil in Deflation + energy equities in Stagflation behind a global include-shorts switch), monthly-only execution — intra-month mechanisms tested and rejected under honest T+1 modeling. Leveraged instruments simulated pre-2010. Out-of-sample framework validation: 1987-2007 replication. Forward: paper/ledger.csv.</t>
         </is>
       </c>
     </row>
@@ -1683,34 +1683,34 @@
         </is>
       </c>
       <c r="B6" s="18" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>1.3173</v>
+        <v>1.5983</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>0.9536</v>
+        <v>1.1522</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>-0.1059</v>
+        <v>-0.1021</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>0.1604</v>
+        <v>0.1671</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.1315</v>
+        <v>0.1382</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>0.1228</v>
+        <v>0.1297</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>0.021</v>
+        <v>0.0187</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>0.204</v>
+        <v>0.2063</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>0.1268</v>
+        <v>0.1283</v>
       </c>
     </row>
     <row r="7">
@@ -1720,34 +1720,34 @@
         </is>
       </c>
       <c r="B7" s="20" t="n">
-        <v>0.1443</v>
+        <v>0.1528</v>
       </c>
       <c r="C7" s="21" t="n">
-        <v>1.4307</v>
+        <v>1.7335</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>1.0503</v>
+        <v>1.2456</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>-0.16</v>
+        <v>-0.1431</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>0.3077</v>
+        <v>0.2789</v>
       </c>
       <c r="G7" s="20" t="n">
-        <v>0.1133</v>
+        <v>0.2075</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>0.2458</v>
+        <v>0.36</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>0.0221</v>
+        <v>0.0002</v>
       </c>
       <c r="J7" s="20" t="n">
-        <v>0.2703</v>
+        <v>0.2861</v>
       </c>
       <c r="K7" s="20" t="n">
-        <v>0.1771</v>
+        <v>0.1833</v>
       </c>
     </row>
     <row r="8">
@@ -1757,34 +1757,34 @@
         </is>
       </c>
       <c r="B8" s="18" t="n">
-        <v>0.2271</v>
+        <v>0.2408</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>1.122</v>
+        <v>1.2244</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>0.878</v>
+        <v>0.9427</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-0.3565</v>
+        <v>-0.3375</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>0.6299</v>
+        <v>0.5864</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>0.2365</v>
+        <v>0.38</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0.6504</v>
+        <v>0.9095</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-0.2259</v>
+        <v>-0.2531</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0.4798</v>
+        <v>0.4978</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>0.2039</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="9">
@@ -1794,34 +1794,34 @@
         </is>
       </c>
       <c r="B9" s="20" t="n">
-        <v>0.3096</v>
+        <v>0.338</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>1.1049</v>
+        <v>1.1173</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>0.8754</v>
+        <v>0.8657</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>-0.5002</v>
+        <v>-0.489</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>0.96</v>
+        <v>0.9979</v>
       </c>
       <c r="G9" s="20" t="n">
-        <v>0.3016</v>
+        <v>0.4634</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>0.9754</v>
+        <v>1.1018</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>-0.3142</v>
+        <v>-0.3122</v>
       </c>
       <c r="J9" s="20" t="n">
-        <v>0.5814</v>
+        <v>0.6196</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>0.3244</v>
+        <v>0.4992</v>
       </c>
     </row>
     <row r="10">
@@ -1834,16 +1834,16 @@
         <v>0.1082</v>
       </c>
       <c r="C10" s="19" t="n">
-        <v>0.6697</v>
+        <v>0.6728</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>0.5458</v>
+        <v>0.5484</v>
       </c>
       <c r="E10" s="18" t="n">
         <v>-0.5518999999999999</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>1.0002</v>
+        <v>1</v>
       </c>
       <c r="G10" s="18" t="n">
         <v>-0.368</v>
@@ -1871,16 +1871,16 @@
         <v>0.1625</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>0.9358</v>
+        <v>0.9438</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>0.7202</v>
+        <v>0.7264</v>
       </c>
       <c r="E11" s="18" t="n">
         <v>-0.534</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>1.0467</v>
+        <v>1.0465</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>-0.4173</v>
@@ -18022,7 +18022,7 @@
     <row r="1">
       <c r="A1" s="54" t="inlineStr">
         <is>
-          <t>Model Data — per-regime return statistics (matrix v4, monthly-only execution, Jun 2007–Aug 2026)</t>
+          <t>Model Data — per-regime return statistics (matrix v6, monthly-only execution, Jun 2007–Aug 2026)</t>
         </is>
       </c>
     </row>
@@ -18073,16 +18073,16 @@
         </is>
       </c>
       <c r="B6" s="55" t="n">
-        <v>0.00726</v>
+        <v>0.00731</v>
       </c>
       <c r="C6" s="55" t="n">
-        <v>0.00796</v>
+        <v>0.00805</v>
       </c>
       <c r="D6" s="55" t="n">
-        <v>0.00399</v>
+        <v>0.00398</v>
       </c>
       <c r="E6" s="55" t="n">
-        <v>0.01116</v>
+        <v>0.01164</v>
       </c>
     </row>
     <row r="7">
@@ -18092,16 +18092,16 @@
         </is>
       </c>
       <c r="B7" s="55" t="n">
-        <v>0.01392</v>
+        <v>0.01397</v>
       </c>
       <c r="C7" s="55" t="n">
-        <v>0.01076</v>
+        <v>0.01084</v>
       </c>
       <c r="D7" s="55" t="n">
-        <v>0.00463</v>
+        <v>0.00648</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>0.01446</v>
+        <v>0.01783</v>
       </c>
     </row>
     <row r="8">
@@ -18114,13 +18114,13 @@
         <v>0.03406</v>
       </c>
       <c r="C8" s="55" t="n">
-        <v>0.01205</v>
+        <v>0.01229</v>
       </c>
       <c r="D8" s="55" t="n">
-        <v>0.00528</v>
+        <v>0.00804</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>0.0167</v>
+        <v>0.02193</v>
       </c>
     </row>
     <row r="9">
@@ -18133,13 +18133,13 @@
         <v>0.05004</v>
       </c>
       <c r="C9" s="55" t="n">
-        <v>0.01622</v>
+        <v>0.01867</v>
       </c>
       <c r="D9" s="55" t="n">
-        <v>0.00593</v>
+        <v>0.00869</v>
       </c>
       <c r="E9" s="55" t="n">
-        <v>0.02286</v>
+        <v>0.02982</v>
       </c>
     </row>
     <row r="11">
@@ -18182,16 +18182,16 @@
         </is>
       </c>
       <c r="B13" s="55" t="n">
-        <v>0.01763</v>
+        <v>0.01765</v>
       </c>
       <c r="C13" s="55" t="n">
-        <v>0.02288</v>
+        <v>0.02286</v>
       </c>
       <c r="D13" s="55" t="n">
-        <v>0.01537</v>
+        <v>0.01519</v>
       </c>
       <c r="E13" s="55" t="n">
-        <v>0.03214</v>
+        <v>0.0323</v>
       </c>
     </row>
     <row r="14">
@@ -18201,16 +18201,16 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.0307</v>
+        <v>0.03064</v>
       </c>
       <c r="C14" s="55" t="n">
-        <v>0.03269</v>
+        <v>0.0327</v>
       </c>
       <c r="D14" s="55" t="n">
-        <v>0.01819</v>
+        <v>0.02411</v>
       </c>
       <c r="E14" s="55" t="n">
-        <v>0.03913</v>
+        <v>0.04132</v>
       </c>
     </row>
     <row r="15">
@@ -18223,13 +18223,13 @@
         <v>0.09061</v>
       </c>
       <c r="C15" s="55" t="n">
-        <v>0.04889</v>
+        <v>0.04896</v>
       </c>
       <c r="D15" s="55" t="n">
-        <v>0.02114</v>
+        <v>0.03079</v>
       </c>
       <c r="E15" s="55" t="n">
-        <v>0.05551</v>
+        <v>0.06388000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -18242,13 +18242,13 @@
         <v>0.13741</v>
       </c>
       <c r="C16" s="55" t="n">
-        <v>0.06826</v>
+        <v>0.07905</v>
       </c>
       <c r="D16" s="55" t="n">
-        <v>0.02416</v>
+        <v>0.03353</v>
       </c>
       <c r="E16" s="55" t="n">
-        <v>0.07714</v>
+        <v>0.08375</v>
       </c>
     </row>
     <row r="18">

--- a/GrowthProjection.xlsx
+++ b/GrowthProjection.xlsx
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>8000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="8">
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="9">
@@ -17596,7 +17596,7 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>650</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="21">
@@ -17606,7 +17606,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>800</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="22">
@@ -17616,7 +17616,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>900</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="23">
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>1000</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="24">
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>1125</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="25">
@@ -17646,7 +17646,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>1250</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="26">
@@ -17656,7 +17656,7 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>1400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="27">
@@ -17666,7 +17666,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>1575</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="28">
@@ -17676,7 +17676,7 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>1775</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="29">
@@ -17686,7 +17686,7 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>1975</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="30">
@@ -17696,7 +17696,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>2225</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="31">
@@ -17706,7 +17706,7 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>2475</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="32">
@@ -17716,7 +17716,7 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>2775</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="33">
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>3125</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="34">
@@ -17736,7 +17736,7 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>3375</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="35">
@@ -17746,7 +17746,7 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>3625</v>
+        <v>5125</v>
       </c>
     </row>
     <row r="36">
@@ -17756,7 +17756,7 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>3925</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="37">
@@ -17766,7 +17766,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>4250</v>
+        <v>5975</v>
       </c>
     </row>
     <row r="38">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>4575</v>
+        <v>6475</v>
       </c>
     </row>
     <row r="39">
@@ -17786,7 +17786,7 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>4950</v>
+        <v>6975</v>
       </c>
     </row>
     <row r="40">
@@ -17796,7 +17796,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>5350</v>
+        <v>7550</v>
       </c>
     </row>
     <row r="41">
@@ -17806,7 +17806,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>5775</v>
+        <v>8150</v>
       </c>
     </row>
     <row r="42">
@@ -17816,7 +17816,7 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>6225</v>
+        <v>8800</v>
       </c>
     </row>
     <row r="43">
@@ -17826,7 +17826,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>6725</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="44">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>7275</v>
+        <v>10250</v>
       </c>
     </row>
     <row r="45">
@@ -17846,7 +17846,7 @@
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>7850</v>
+        <v>11075</v>
       </c>
     </row>
     <row r="46">
@@ -17856,7 +17856,7 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>8475</v>
+        <v>11950</v>
       </c>
     </row>
     <row r="47">
@@ -17866,7 +17866,7 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>9150</v>
+        <v>12925</v>
       </c>
     </row>
     <row r="48">
@@ -17876,7 +17876,7 @@
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>9875</v>
+        <v>13950</v>
       </c>
     </row>
     <row r="49">
@@ -17886,7 +17886,7 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>10675</v>
+        <v>15075</v>
       </c>
     </row>
     <row r="50">
@@ -17896,7 +17896,7 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>11525</v>
+        <v>16275</v>
       </c>
     </row>
     <row r="51">
@@ -17906,7 +17906,7 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>12450</v>
+        <v>17575</v>
       </c>
     </row>
     <row r="52">
@@ -17916,7 +17916,7 @@
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>13450</v>
+        <v>18975</v>
       </c>
     </row>
     <row r="53">
@@ -17926,7 +17926,7 @@
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>14525</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="54">
@@ -17936,7 +17936,7 @@
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>15700</v>
+        <v>22150</v>
       </c>
     </row>
     <row r="55">
@@ -17946,7 +17946,7 @@
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>16950</v>
+        <v>23900</v>
       </c>
     </row>
     <row r="56">
@@ -17956,7 +17956,7 @@
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>18300</v>
+        <v>25825</v>
       </c>
     </row>
     <row r="57">
@@ -17966,7 +17966,7 @@
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>19775</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="58">
@@ -17976,13 +17976,13 @@
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>21350</v>
+        <v>30125</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>Defaults: $800/mo by yr 3 (user), +12%/yr to yr 15 (income → ~$500k), +8%/yr after. Cap on Dashboard applies.</t>
+          <t>Defaults: $900/mo yr 1 (user, 2026), +12%/yr to yr 15 (income → ~$500k), +8%/yr after. Cap on Dashboard applies.</t>
         </is>
       </c>
     </row>
@@ -18395,7 +18395,7 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="58" t="inlineStr">
         <is>
-          <t>Year-by-year monthly schedule on Settings (defaults: $500 yr1, $800 by yr3, +12%/yr to yr15 as income scales to ~$500k, +8%/yr after), capped on the Dashboard. Projection applies the exact schedule.</t>
+          <t>Year-by-year monthly schedule on Settings (defaults: $900/mo yr1 per user 2026 update, +12%/yr to yr15 as income scales to ~$500k, +8%/yr after), capped on the Dashboard. Projection applies the exact schedule.</t>
         </is>
       </c>
     </row>

--- a/GrowthProjection.xlsx
+++ b/GrowthProjection.xlsx
@@ -1598,7 +1598,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Matrix v6 (conditional-duration S, D-cell gold, R momentum tilt, regime-gated short book: oil in Deflation + energy equities in Stagflation behind a global include-shorts switch), monthly-only execution — intra-month mechanisms tested and rejected under honest T+1 modeling. Leveraged instruments simulated pre-2010. Out-of-sample framework validation: 1987-2007 replication. Forward: paper/ledger.csv.</t>
+          <t>Matrix v7 (conditional-duration S, D-cell gold + washout-conditional rebound slice, R momentum tilt, regime-gated short book: oil in Deflation + energy equities in Stagflation behind a global include-shorts switch), monthly-only execution — intra-month mechanisms tested and rejected under honest T+1 modeling. Leveraged instruments simulated pre-2010. Out-of-sample framework validation: 1987-2007 replication. Forward: paper/ledger.csv.</t>
         </is>
       </c>
     </row>
@@ -1720,31 +1720,31 @@
         </is>
       </c>
       <c r="B7" s="20" t="n">
-        <v>0.1528</v>
+        <v>0.1559</v>
       </c>
       <c r="C7" s="21" t="n">
-        <v>1.7335</v>
+        <v>1.7527</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>1.2456</v>
+        <v>1.2658</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>-0.1431</v>
+        <v>-0.143</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>0.2789</v>
+        <v>0.3274</v>
       </c>
       <c r="G7" s="20" t="n">
-        <v>0.2075</v>
+        <v>0.1545</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>0.36</v>
+        <v>0.3509</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>0.0002</v>
+        <v>0.0129</v>
       </c>
       <c r="J7" s="20" t="n">
-        <v>0.2861</v>
+        <v>0.2984</v>
       </c>
       <c r="K7" s="20" t="n">
         <v>0.1833</v>
@@ -1757,31 +1757,31 @@
         </is>
       </c>
       <c r="B8" s="18" t="n">
-        <v>0.2408</v>
+        <v>0.2461</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>1.2244</v>
+        <v>1.2515</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>0.9427</v>
+        <v>0.9688</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-0.3375</v>
+        <v>-0.3338</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>0.5864</v>
+        <v>0.6321</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>0.38</v>
+        <v>0.3177</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0.9095</v>
+        <v>0.9175</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-0.2531</v>
+        <v>-0.2463</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0.4978</v>
+        <v>0.5163</v>
       </c>
       <c r="K8" s="18" t="n">
         <v>0.217</v>
@@ -1794,31 +1794,31 @@
         </is>
       </c>
       <c r="B9" s="20" t="n">
-        <v>0.338</v>
+        <v>0.3436</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>1.1173</v>
+        <v>1.1346</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>0.8657</v>
+        <v>0.8812</v>
       </c>
       <c r="E9" s="20" t="n">
         <v>-0.489</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>0.9979</v>
+        <v>1.0393</v>
       </c>
       <c r="G9" s="20" t="n">
-        <v>0.4634</v>
+        <v>0.4131</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>1.1018</v>
+        <v>1.1186</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>-0.3122</v>
+        <v>-0.3062</v>
       </c>
       <c r="J9" s="20" t="n">
-        <v>0.6196</v>
+        <v>0.6364</v>
       </c>
       <c r="K9" s="20" t="n">
         <v>0.4992</v>
@@ -18022,7 +18022,7 @@
     <row r="1">
       <c r="A1" s="54" t="inlineStr">
         <is>
-          <t>Model Data — per-regime return statistics (matrix v6, monthly-only execution, Jun 2007–Aug 2026)</t>
+          <t>Model Data — per-regime return statistics (matrix v7, monthly-only execution, Jun 2007–Aug 2026)</t>
         </is>
       </c>
     </row>
@@ -18101,7 +18101,7 @@
         <v>0.00648</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>0.01783</v>
+        <v>0.01949</v>
       </c>
     </row>
     <row r="8">
@@ -18120,7 +18120,7 @@
         <v>0.00804</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>0.02193</v>
+        <v>0.02443</v>
       </c>
     </row>
     <row r="9">
@@ -18139,7 +18139,7 @@
         <v>0.00869</v>
       </c>
       <c r="E9" s="55" t="n">
-        <v>0.02982</v>
+        <v>0.03238</v>
       </c>
     </row>
     <row r="11">
@@ -18210,7 +18210,7 @@
         <v>0.02411</v>
       </c>
       <c r="E14" s="55" t="n">
-        <v>0.04132</v>
+        <v>0.03854</v>
       </c>
     </row>
     <row r="15">
@@ -18229,7 +18229,7 @@
         <v>0.03079</v>
       </c>
       <c r="E15" s="55" t="n">
-        <v>0.06388000000000001</v>
+        <v>0.05878</v>
       </c>
     </row>
     <row r="16">
@@ -18248,7 +18248,7 @@
         <v>0.03353</v>
       </c>
       <c r="E16" s="55" t="n">
-        <v>0.08375</v>
+        <v>0.08123</v>
       </c>
     </row>
     <row r="18">

--- a/GrowthProjection.xlsx
+++ b/GrowthProjection.xlsx
@@ -1794,34 +1794,34 @@
         </is>
       </c>
       <c r="B9" s="20" t="n">
-        <v>0.3436</v>
+        <v>0.3285</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>1.1346</v>
+        <v>1.1241</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>0.8812</v>
+        <v>0.8825</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>-0.489</v>
+        <v>-0.4693</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>1.0393</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="G9" s="20" t="n">
         <v>0.4131</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>1.1186</v>
+        <v>1.2807</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>-0.3062</v>
+        <v>-0.3418</v>
       </c>
       <c r="J9" s="20" t="n">
-        <v>0.6364</v>
+        <v>0.5962</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>0.4992</v>
+        <v>0.3673</v>
       </c>
     </row>
     <row r="10">
@@ -18133,7 +18133,7 @@
         <v>0.05004</v>
       </c>
       <c r="C9" s="55" t="n">
-        <v>0.01867</v>
+        <v>0.01582</v>
       </c>
       <c r="D9" s="55" t="n">
         <v>0.00869</v>
@@ -18242,7 +18242,7 @@
         <v>0.13741</v>
       </c>
       <c r="C16" s="55" t="n">
-        <v>0.07905</v>
+        <v>0.06832000000000001</v>
       </c>
       <c r="D16" s="55" t="n">
         <v>0.03353</v>

--- a/GrowthProjection.xlsx
+++ b/GrowthProjection.xlsx
@@ -1720,31 +1720,31 @@
         </is>
       </c>
       <c r="B7" s="20" t="n">
-        <v>0.1559</v>
+        <v>0.1534</v>
       </c>
       <c r="C7" s="21" t="n">
-        <v>1.7527</v>
+        <v>1.7215</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>1.2658</v>
+        <v>1.2463</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>-0.143</v>
+        <v>-0.1433</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>0.3274</v>
+        <v>0.3271</v>
       </c>
       <c r="G7" s="20" t="n">
-        <v>0.1545</v>
+        <v>0.1463</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>0.3509</v>
+        <v>0.2998</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>0.0129</v>
+        <v>0.0115</v>
       </c>
       <c r="J7" s="20" t="n">
-        <v>0.2984</v>
+        <v>0.3012</v>
       </c>
       <c r="K7" s="20" t="n">
         <v>0.1833</v>
@@ -1757,31 +1757,31 @@
         </is>
       </c>
       <c r="B8" s="18" t="n">
-        <v>0.2461</v>
+        <v>0.242</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>1.2515</v>
+        <v>1.2306</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>0.9688</v>
+        <v>0.9532</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-0.3338</v>
+        <v>-0.3342</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>0.6321</v>
+        <v>0.6317</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>0.3177</v>
+        <v>0.3038</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0.9175</v>
+        <v>0.8095</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-0.2463</v>
+        <v>-0.2478</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0.5163</v>
+        <v>0.5212</v>
       </c>
       <c r="K8" s="18" t="n">
         <v>0.217</v>
@@ -1794,31 +1794,31 @@
         </is>
       </c>
       <c r="B9" s="20" t="n">
-        <v>0.3285</v>
+        <v>0.3242</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>1.1241</v>
+        <v>1.1091</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>0.8825</v>
+        <v>0.8711</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>-0.4693</v>
+        <v>-0.4696</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.981</v>
       </c>
       <c r="G9" s="20" t="n">
-        <v>0.4131</v>
+        <v>0.3983</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>1.2807</v>
+        <v>1.1519</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>-0.3418</v>
+        <v>-0.3432</v>
       </c>
       <c r="J9" s="20" t="n">
-        <v>0.5962</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="K9" s="20" t="n">
         <v>0.3673</v>
@@ -18101,7 +18101,7 @@
         <v>0.00648</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>0.01949</v>
+        <v>0.01795</v>
       </c>
     </row>
     <row r="8">
@@ -18120,7 +18120,7 @@
         <v>0.00804</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>0.02443</v>
+        <v>0.02203</v>
       </c>
     </row>
     <row r="9">
@@ -18139,7 +18139,7 @@
         <v>0.00869</v>
       </c>
       <c r="E9" s="55" t="n">
-        <v>0.03238</v>
+        <v>0.02989</v>
       </c>
     </row>
     <row r="11">
@@ -18210,7 +18210,7 @@
         <v>0.02411</v>
       </c>
       <c r="E14" s="55" t="n">
-        <v>0.03854</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="15">
@@ -18229,7 +18229,7 @@
         <v>0.03079</v>
       </c>
       <c r="E15" s="55" t="n">
-        <v>0.05878</v>
+        <v>0.05344</v>
       </c>
     </row>
     <row r="16">
@@ -18248,7 +18248,7 @@
         <v>0.03353</v>
       </c>
       <c r="E16" s="55" t="n">
-        <v>0.08123</v>
+        <v>0.07621</v>
       </c>
     </row>
     <row r="18">

--- a/GrowthProjection.xlsx
+++ b/GrowthProjection.xlsx
@@ -1144,7 +1144,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Age-based risk glide with regime-conditional return engine  |  Backtest Jun 2007–Aug 2026  |  Prepared August 21, 2026  |  Forward ledger live</t>
+          <t>Age-based risk glide with regime-conditional return engine  |  Backtest Jun 2007–Aug 2026  |  Prepared August 26, 2026  |  Forward ledger live</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9">
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="10">
@@ -17596,7 +17596,7 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="21">
@@ -17606,7 +17606,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>1125</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="22">
@@ -17616,7 +17616,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>1275</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="23">
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>1425</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="24">
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>1575</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="25">
@@ -17646,7 +17646,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>1775</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="26">
@@ -17656,7 +17656,7 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>2000</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="27">
@@ -17666,7 +17666,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>2225</v>
+        <v>4075</v>
       </c>
     </row>
     <row r="28">
@@ -17676,7 +17676,7 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>2500</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="29">
@@ -17686,7 +17686,7 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>2800</v>
+        <v>4675</v>
       </c>
     </row>
     <row r="30">
@@ -17696,7 +17696,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>3125</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="31">
@@ -17706,7 +17706,7 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>3500</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="32">
@@ -17716,7 +17716,7 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>3925</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="33">
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>4400</v>
+        <v>6125</v>
       </c>
     </row>
     <row r="34">
@@ -17736,7 +17736,7 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>4750</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="35">
@@ -17746,7 +17746,7 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>5125</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="36">
@@ -17756,7 +17756,7 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>5550</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="37">
@@ -17766,7 +17766,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>5975</v>
+        <v>8025</v>
       </c>
     </row>
     <row r="38">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>6475</v>
+        <v>8575</v>
       </c>
     </row>
     <row r="39">
@@ -17786,7 +17786,7 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>6975</v>
+        <v>9175</v>
       </c>
     </row>
     <row r="40">
@@ -17796,7 +17796,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>7550</v>
+        <v>9825</v>
       </c>
     </row>
     <row r="41">
@@ -17806,7 +17806,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>8150</v>
+        <v>10525</v>
       </c>
     </row>
     <row r="42">
@@ -17816,7 +17816,7 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>8800</v>
+        <v>11250</v>
       </c>
     </row>
     <row r="43">
@@ -17826,7 +17826,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>9500</v>
+        <v>12025</v>
       </c>
     </row>
     <row r="44">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>10250</v>
+        <v>12875</v>
       </c>
     </row>
     <row r="45">
@@ -17846,7 +17846,7 @@
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>11075</v>
+        <v>13775</v>
       </c>
     </row>
     <row r="46">
@@ -17856,7 +17856,7 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>11950</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="47">
@@ -17866,7 +17866,7 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>12925</v>
+        <v>15775</v>
       </c>
     </row>
     <row r="48">
@@ -17876,7 +17876,7 @@
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>13950</v>
+        <v>16875</v>
       </c>
     </row>
     <row r="49">
@@ -17886,7 +17886,7 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>15075</v>
+        <v>18075</v>
       </c>
     </row>
     <row r="50">
@@ -17896,7 +17896,7 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>16275</v>
+        <v>19325</v>
       </c>
     </row>
     <row r="51">
@@ -17906,7 +17906,7 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>17575</v>
+        <v>20675</v>
       </c>
     </row>
     <row r="52">
@@ -17916,7 +17916,7 @@
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>18975</v>
+        <v>22125</v>
       </c>
     </row>
     <row r="53">
@@ -17926,7 +17926,7 @@
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>20500</v>
+        <v>23675</v>
       </c>
     </row>
     <row r="54">
@@ -17936,7 +17936,7 @@
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>22150</v>
+        <v>25325</v>
       </c>
     </row>
     <row r="55">
@@ -17946,7 +17946,7 @@
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>23900</v>
+        <v>27100</v>
       </c>
     </row>
     <row r="56">
@@ -17956,7 +17956,7 @@
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>25825</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="57">
@@ -17966,7 +17966,7 @@
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>27900</v>
+        <v>31025</v>
       </c>
     </row>
     <row r="58">
@@ -17976,13 +17976,13 @@
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>30125</v>
+        <v>33200</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>Defaults: $900/mo yr 1 (user, 2026), +12%/yr to yr 15 (income → ~$500k), +8%/yr after. Cap on Dashboard applies.</t>
+          <t>Defaults: $1,500/mo yr 1 (user, 2026); +20%/yr thru yr 5 (no-kids ramp), +7%/yr after — crosses $5k/mo early-mid 30s, $7k entering 40s, $10k+ mid-40s on. Cap on Dashboard applies.</t>
         </is>
       </c>
     </row>
@@ -18395,7 +18395,7 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="58" t="inlineStr">
         <is>
-          <t>Year-by-year monthly schedule on Settings (defaults: $900/mo yr1 per user 2026 update, +12%/yr to yr15 as income scales to ~$500k, +8%/yr after), capped on the Dashboard. Projection applies the exact schedule.</t>
+          <t>Year-by-year monthly schedule on Settings (defaults: $1,500/mo yr1 per user 2026 update; +20%/yr through yr5, +7%/yr after — anchored to user decade targets: &gt;$5k/mo in 30s, &gt;$7k in 40s, &gt;$10k in 50s), capped on the Dashboard. Projection applies the exact schedule.</t>
         </is>
       </c>
     </row>

--- a/GrowthProjection.xlsx
+++ b/GrowthProjection.xlsx
@@ -535,6 +535,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -545,7 +546,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Month</a:t>
+                  <a:t>Months from start (age 25 -&gt; 65)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -555,12 +556,15 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="60"/>
+        <tickMarkSkip val="60"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -572,12 +576,13 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Balance ($)</a:t>
+                  <a:t>Account balance ($)</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="$#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -641,6 +646,10 @@
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.0%"/>
+          <showVal val="1"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -650,7 +659,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Portfolio / benchmark</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -661,8 +686,25 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Compound annual return</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -718,6 +760,10 @@
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <numFmt formatCode="$#,##0"/>
+          <showVal val="1"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -727,7 +773,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Strategy / benchmark</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -738,8 +800,25 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>After-tax balance at end age ($)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="$#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -17572,11 +17651,15 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Contribution schedule — monthly $ by year (edit freely; year 1 links to Dashboard)</t>
+          <t>Contribution schedule — driven by the RAMP STAGES table (edit the yellow rates)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr"/>
       <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
@@ -17588,6 +17671,21 @@
         <f>Dashboard!$C$8</f>
         <v/>
       </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Ramp stage</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>From yr</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>Growth %/yr</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
@@ -17595,8 +17693,20 @@
           <t>Year 2</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
-        <v>1800</v>
+      <c r="B20" s="52">
+        <f>ROUND(B19*(1+INDEX($F$20:$F$32,MATCH(2,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>Ages 26-28</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="21">
@@ -17605,8 +17715,20 @@
           <t>Year 3</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>2150</v>
+      <c r="B21" s="52">
+        <f>ROUND(B20*(1+INDEX($F$20:$F$32,MATCH(3,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>Ages 29-31</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="22">
@@ -17615,8 +17737,20 @@
           <t>Year 4</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>2600</v>
+      <c r="B22" s="52">
+        <f>ROUND(B21*(1+INDEX($F$20:$F$32,MATCH(4,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>Ages 32-34</t>
+        </is>
+      </c>
+      <c r="E22" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="23">
@@ -17625,8 +17759,20 @@
           <t>Year 5</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>3100</v>
+      <c r="B23" s="52">
+        <f>ROUND(B22*(1+INDEX($F$20:$F$32,MATCH(5,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>Ages 35-37</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="24">
@@ -17635,8 +17781,20 @@
           <t>Year 6</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
-        <v>3325</v>
+      <c r="B24" s="52">
+        <f>ROUND(B23*(1+INDEX($F$20:$F$32,MATCH(6,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>Ages 38-40</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="25">
@@ -17645,8 +17803,20 @@
           <t>Year 7</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
-        <v>3550</v>
+      <c r="B25" s="52">
+        <f>ROUND(B24*(1+INDEX($F$20:$F$32,MATCH(7,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>Ages 41-43</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -17655,8 +17825,20 @@
           <t>Year 8</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
-        <v>3800</v>
+      <c r="B26" s="52">
+        <f>ROUND(B25*(1+INDEX($F$20:$F$32,MATCH(8,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>Ages 44-46</t>
+        </is>
+      </c>
+      <c r="E26" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -17665,8 +17847,20 @@
           <t>Year 9</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n">
-        <v>4075</v>
+      <c r="B27" s="52">
+        <f>ROUND(B26*(1+INDEX($F$20:$F$32,MATCH(9,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>Ages 47-49</t>
+        </is>
+      </c>
+      <c r="E27" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -17675,8 +17869,20 @@
           <t>Year 10</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
-        <v>4350</v>
+      <c r="B28" s="52">
+        <f>ROUND(B27*(1+INDEX($F$20:$F$32,MATCH(10,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>Ages 50-52</t>
+        </is>
+      </c>
+      <c r="E28" s="27" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="29">
@@ -17685,8 +17891,20 @@
           <t>Year 11</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n">
-        <v>4675</v>
+      <c r="B29" s="52">
+        <f>ROUND(B28*(1+INDEX($F$20:$F$32,MATCH(11,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>Ages 53-55</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="30">
@@ -17695,8 +17913,20 @@
           <t>Year 12</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
-        <v>5000</v>
+      <c r="B30" s="52">
+        <f>ROUND(B29*(1+INDEX($F$20:$F$32,MATCH(12,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>Ages 56-58</t>
+        </is>
+      </c>
+      <c r="E30" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="31">
@@ -17705,8 +17935,20 @@
           <t>Year 13</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n">
-        <v>5350</v>
+      <c r="B31" s="52">
+        <f>ROUND(B30*(1+INDEX($F$20:$F$32,MATCH(13,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>Ages 59-61</t>
+        </is>
+      </c>
+      <c r="E31" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="32">
@@ -17715,8 +17957,20 @@
           <t>Year 14</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n">
-        <v>5725</v>
+      <c r="B32" s="52">
+        <f>ROUND(B31*(1+INDEX($F$20:$F$32,MATCH(14,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>Ages 62-64</t>
+        </is>
+      </c>
+      <c r="E32" s="27" t="n">
+        <v>38</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="33">
@@ -17725,8 +17979,9 @@
           <t>Year 15</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n">
-        <v>6125</v>
+      <c r="B33" s="52">
+        <f>ROUND(B32*(1+INDEX($F$20:$F$32,MATCH(15,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -17735,8 +17990,9 @@
           <t>Year 16</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
-        <v>6550</v>
+      <c r="B34" s="52">
+        <f>ROUND(B33*(1+INDEX($F$20:$F$32,MATCH(16,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -17745,8 +18001,9 @@
           <t>Year 17</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
-        <v>7000</v>
+      <c r="B35" s="52">
+        <f>ROUND(B34*(1+INDEX($F$20:$F$32,MATCH(17,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -17755,8 +18012,9 @@
           <t>Year 18</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>7500</v>
+      <c r="B36" s="52">
+        <f>ROUND(B35*(1+INDEX($F$20:$F$32,MATCH(18,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -17765,8 +18023,9 @@
           <t>Year 19</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>8025</v>
+      <c r="B37" s="52">
+        <f>ROUND(B36*(1+INDEX($F$20:$F$32,MATCH(19,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -17775,8 +18034,9 @@
           <t>Year 20</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n">
-        <v>8575</v>
+      <c r="B38" s="52">
+        <f>ROUND(B37*(1+INDEX($F$20:$F$32,MATCH(20,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -17785,8 +18045,9 @@
           <t>Year 21</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>9175</v>
+      <c r="B39" s="52">
+        <f>ROUND(B38*(1+INDEX($F$20:$F$32,MATCH(21,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -17795,8 +18056,9 @@
           <t>Year 22</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n">
-        <v>9825</v>
+      <c r="B40" s="52">
+        <f>ROUND(B39*(1+INDEX($F$20:$F$32,MATCH(22,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -17805,8 +18067,9 @@
           <t>Year 23</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
-        <v>10525</v>
+      <c r="B41" s="52">
+        <f>ROUND(B40*(1+INDEX($F$20:$F$32,MATCH(23,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -17815,8 +18078,9 @@
           <t>Year 24</t>
         </is>
       </c>
-      <c r="B42" s="7" t="n">
-        <v>11250</v>
+      <c r="B42" s="52">
+        <f>ROUND(B41*(1+INDEX($F$20:$F$32,MATCH(24,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -17825,8 +18089,9 @@
           <t>Year 25</t>
         </is>
       </c>
-      <c r="B43" s="7" t="n">
-        <v>12025</v>
+      <c r="B43" s="52">
+        <f>ROUND(B42*(1+INDEX($F$20:$F$32,MATCH(25,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -17835,8 +18100,9 @@
           <t>Year 26</t>
         </is>
       </c>
-      <c r="B44" s="7" t="n">
-        <v>12875</v>
+      <c r="B44" s="52">
+        <f>ROUND(B43*(1+INDEX($F$20:$F$32,MATCH(26,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -17845,8 +18111,9 @@
           <t>Year 27</t>
         </is>
       </c>
-      <c r="B45" s="7" t="n">
-        <v>13775</v>
+      <c r="B45" s="52">
+        <f>ROUND(B44*(1+INDEX($F$20:$F$32,MATCH(27,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -17855,8 +18122,9 @@
           <t>Year 28</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
-        <v>14750</v>
+      <c r="B46" s="52">
+        <f>ROUND(B45*(1+INDEX($F$20:$F$32,MATCH(28,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -17865,8 +18133,9 @@
           <t>Year 29</t>
         </is>
       </c>
-      <c r="B47" s="7" t="n">
-        <v>15775</v>
+      <c r="B47" s="52">
+        <f>ROUND(B46*(1+INDEX($F$20:$F$32,MATCH(29,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -17875,8 +18144,9 @@
           <t>Year 30</t>
         </is>
       </c>
-      <c r="B48" s="7" t="n">
-        <v>16875</v>
+      <c r="B48" s="52">
+        <f>ROUND(B47*(1+INDEX($F$20:$F$32,MATCH(30,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -17885,8 +18155,9 @@
           <t>Year 31</t>
         </is>
       </c>
-      <c r="B49" s="7" t="n">
-        <v>18075</v>
+      <c r="B49" s="52">
+        <f>ROUND(B48*(1+INDEX($F$20:$F$32,MATCH(31,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -17895,8 +18166,9 @@
           <t>Year 32</t>
         </is>
       </c>
-      <c r="B50" s="7" t="n">
-        <v>19325</v>
+      <c r="B50" s="52">
+        <f>ROUND(B49*(1+INDEX($F$20:$F$32,MATCH(32,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -17905,8 +18177,9 @@
           <t>Year 33</t>
         </is>
       </c>
-      <c r="B51" s="7" t="n">
-        <v>20675</v>
+      <c r="B51" s="52">
+        <f>ROUND(B50*(1+INDEX($F$20:$F$32,MATCH(33,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -17915,8 +18188,9 @@
           <t>Year 34</t>
         </is>
       </c>
-      <c r="B52" s="7" t="n">
-        <v>22125</v>
+      <c r="B52" s="52">
+        <f>ROUND(B51*(1+INDEX($F$20:$F$32,MATCH(34,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -17925,8 +18199,9 @@
           <t>Year 35</t>
         </is>
       </c>
-      <c r="B53" s="7" t="n">
-        <v>23675</v>
+      <c r="B53" s="52">
+        <f>ROUND(B52*(1+INDEX($F$20:$F$32,MATCH(35,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -17935,8 +18210,9 @@
           <t>Year 36</t>
         </is>
       </c>
-      <c r="B54" s="7" t="n">
-        <v>25325</v>
+      <c r="B54" s="52">
+        <f>ROUND(B53*(1+INDEX($F$20:$F$32,MATCH(36,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -17945,8 +18221,9 @@
           <t>Year 37</t>
         </is>
       </c>
-      <c r="B55" s="7" t="n">
-        <v>27100</v>
+      <c r="B55" s="52">
+        <f>ROUND(B54*(1+INDEX($F$20:$F$32,MATCH(37,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -17955,8 +18232,9 @@
           <t>Year 38</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
-        <v>29000</v>
+      <c r="B56" s="52">
+        <f>ROUND(B55*(1+INDEX($F$20:$F$32,MATCH(38,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -17965,8 +18243,9 @@
           <t>Year 39</t>
         </is>
       </c>
-      <c r="B57" s="7" t="n">
-        <v>31025</v>
+      <c r="B57" s="52">
+        <f>ROUND(B56*(1+INDEX($F$20:$F$32,MATCH(39,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -17975,14 +18254,15 @@
           <t>Year 40</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
-        <v>33200</v>
+      <c r="B58" s="52">
+        <f>ROUND(B57*(1+INDEX($F$20:$F$32,MATCH(40,$E$20:$E$32,1)))/25,0)*25</f>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>Defaults: $1,500/mo yr 1 (user, 2026); +20%/yr thru yr 5 (no-kids ramp), +7%/yr after — crosses $5k/mo early-mid 30s, $7k entering 40s, $10k+ mid-40s on. Cap on Dashboard applies.</t>
+          <t>Yr 1 links to the Dashboard; every later year = prior year x (1 + its stage rate). Change the 13 yellow stage rates to reshape the whole ramp. Defaults honor the user's anchors: 35%/yr ages 26-28 (no kids), then tapering 15%-&gt;5%; crosses $5k/mo ~age 31, $7k ~34, cap ($25k, Dashboard) binds early 50s.</t>
         </is>
       </c>
     </row>

--- a/GrowthProjection.xlsx
+++ b/GrowthProjection.xlsx
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>25000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="10">
@@ -18262,7 +18262,7 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>Yr 1 links to the Dashboard; every later year = prior year x (1 + its stage rate). Change the 13 yellow stage rates to reshape the whole ramp. Defaults honor the user's anchors: 35%/yr ages 26-28 (no kids), then tapering 15%-&gt;5%; crosses $5k/mo ~age 31, $7k ~34, cap ($25k, Dashboard) binds early 50s.</t>
+          <t>Yr 1 links to the Dashboard; every later year = prior year x (1 + its stage rate). Change the 13 yellow stage rates to reshape the whole ramp. Defaults honor the user's anchors: 35%/yr ages 26-28 (no kids), then tapering 15%-&gt;5%; crosses $5k/mo ~age 31, $7k ~34; cap ($40k, Dashboard) leaves the entire 50s uncapped and binds only ~age 62+.</t>
         </is>
       </c>
     </row>
